--- a/output/2026/money/money.xlsx
+++ b/output/2026/money/money.xlsx
@@ -2414,7 +2414,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="805">
+  <cellXfs count="815">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3436,6 +3436,16 @@
     <xf numFmtId="0" fontId="0" fillId="61" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="61" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="62" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3818,7 +3828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V83"/>
+  <dimension ref="A2:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -7766,6 +7776,488 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="B84" s="669" t="inlineStr">
+        <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="670" t="n"/>
+      <c r="D84" s="671" t="n"/>
+      <c r="E84" s="672" t="n"/>
+      <c r="F84" s="673" t="n"/>
+      <c r="G84" s="674" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H84" s="675" t="inlineStr">
+        <is>
+          <t>58.51</t>
+        </is>
+      </c>
+      <c r="I84" s="676" t="n"/>
+      <c r="J84" s="677" t="n"/>
+      <c r="K84" s="805" t="inlineStr">
+        <is>
+          <t>58.51</t>
+        </is>
+      </c>
+      <c r="L84" s="806" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M84" s="807" t="n"/>
+      <c r="N84" s="808" t="n"/>
+      <c r="O84" s="682" t="n"/>
+      <c r="P84" s="683" t="n"/>
+      <c r="Q84" s="684" t="n"/>
+      <c r="R84" s="685" t="n"/>
+      <c r="S84" s="686" t="n"/>
+      <c r="T84" s="687" t="n"/>
+      <c r="U84" s="688" t="n"/>
+      <c r="V84" s="689" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="721" t="n"/>
+      <c r="C85" s="722" t="n"/>
+      <c r="D85" s="723" t="n"/>
+      <c r="E85" s="724" t="n"/>
+      <c r="F85" s="725" t="n"/>
+      <c r="G85" s="726" t="n"/>
+      <c r="H85" s="727" t="n"/>
+      <c r="I85" s="728" t="n"/>
+      <c r="J85" s="729" t="n"/>
+      <c r="K85" s="809" t="inlineStr">
+        <is>
+          <t>canva</t>
+        </is>
+      </c>
+      <c r="L85" s="810" t="inlineStr">
+        <is>
+          <t>58.51</t>
+        </is>
+      </c>
+      <c r="M85" s="811" t="n"/>
+      <c r="N85" s="812" t="n"/>
+      <c r="O85" s="734" t="n"/>
+      <c r="P85" s="735" t="n"/>
+      <c r="Q85" s="736" t="inlineStr">
+        <is>
+          <t>canva</t>
+        </is>
+      </c>
+      <c r="R85" s="737" t="inlineStr">
+        <is>
+          <t>58.51</t>
+        </is>
+      </c>
+      <c r="S85" s="738" t="inlineStr">
+        <is>
+          <t>canva</t>
+        </is>
+      </c>
+      <c r="T85" s="739" t="inlineStr">
+        <is>
+          <t>58.51</t>
+        </is>
+      </c>
+      <c r="U85" s="740" t="n"/>
+      <c r="V85" s="741" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C86" s="743" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="744" t="n"/>
+      <c r="E86" s="745" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F86" s="746" t="n"/>
+      <c r="G86" s="747" t="n">
+        <v>15965.49</v>
+      </c>
+      <c r="H86" s="748" t="n"/>
+      <c r="I86" s="749" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="J86" s="750" t="n"/>
+      <c r="K86" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="752" t="n"/>
+      <c r="M86" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="754" t="n"/>
+      <c r="O86" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="756" t="n"/>
+      <c r="Q86" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="758" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="S86" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="760" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="U86" s="761" t="n">
+        <v>16337.79</v>
+      </c>
+      <c r="V86" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C87" s="764" t="n"/>
+      <c r="D87" s="765" t="n"/>
+      <c r="E87" s="766" t="n"/>
+      <c r="F87" s="767" t="n"/>
+      <c r="G87" s="768" t="n"/>
+      <c r="H87" s="769" t="n"/>
+      <c r="I87" s="770" t="n"/>
+      <c r="J87" s="771" t="n"/>
+      <c r="K87" s="772" t="n"/>
+      <c r="L87" s="773" t="n"/>
+      <c r="M87" s="774" t="n"/>
+      <c r="N87" s="775" t="n"/>
+      <c r="O87" s="776" t="n"/>
+      <c r="P87" s="777" t="n"/>
+      <c r="Q87" s="778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="779" t="n">
+        <v>1220.41</v>
+      </c>
+      <c r="S87" s="780" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="781" t="n">
+        <v>1220.41</v>
+      </c>
+      <c r="U87" s="782" t="n"/>
+      <c r="V87" s="783" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="669" t="inlineStr">
+        <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="670" t="n"/>
+      <c r="D88" s="671" t="n"/>
+      <c r="E88" s="672" t="n"/>
+      <c r="F88" s="673" t="n"/>
+      <c r="G88" s="674" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H88" s="675" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I88" s="676" t="n"/>
+      <c r="J88" s="677" t="n"/>
+      <c r="K88" s="805" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L88" s="806" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M88" s="807" t="n"/>
+      <c r="N88" s="808" t="n"/>
+      <c r="O88" s="682" t="n"/>
+      <c r="P88" s="683" t="n"/>
+      <c r="Q88" s="684" t="n"/>
+      <c r="R88" s="685" t="n"/>
+      <c r="S88" s="686" t="n"/>
+      <c r="T88" s="687" t="n"/>
+      <c r="U88" s="688" t="n"/>
+      <c r="V88" s="689" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="690" t="n"/>
+      <c r="C89" s="691" t="n"/>
+      <c r="D89" s="692" t="n"/>
+      <c r="E89" s="693" t="n"/>
+      <c r="F89" s="694" t="n"/>
+      <c r="G89" s="695" t="n"/>
+      <c r="H89" s="696" t="n"/>
+      <c r="I89" s="713" t="n"/>
+      <c r="J89" s="714" t="n"/>
+      <c r="K89" s="715" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="L89" s="716" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M89" s="701" t="n"/>
+      <c r="N89" s="702" t="n"/>
+      <c r="O89" s="703" t="n"/>
+      <c r="P89" s="704" t="n"/>
+      <c r="Q89" s="705" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="R89" s="706" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="S89" s="707" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="T89" s="708" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="U89" s="709" t="n"/>
+      <c r="V89" s="710" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="721" t="n"/>
+      <c r="C90" s="722" t="n"/>
+      <c r="D90" s="723" t="n"/>
+      <c r="E90" s="724" t="n"/>
+      <c r="F90" s="725" t="n"/>
+      <c r="G90" s="726" t="n"/>
+      <c r="H90" s="727" t="n"/>
+      <c r="I90" s="813" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J90" s="814" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="K90" s="730" t="n"/>
+      <c r="L90" s="731" t="n"/>
+      <c r="M90" s="811" t="n"/>
+      <c r="N90" s="812" t="n"/>
+      <c r="O90" s="734" t="n"/>
+      <c r="P90" s="735" t="n"/>
+      <c r="Q90" s="736" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R90" s="737" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="S90" s="738" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T90" s="739" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="U90" s="740" t="n"/>
+      <c r="V90" s="741" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C91" s="743" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="744" t="n"/>
+      <c r="E91" s="745" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F91" s="746" t="n"/>
+      <c r="G91" s="747" t="n">
+        <v>15715.49</v>
+      </c>
+      <c r="H91" s="748" t="n"/>
+      <c r="I91" s="749" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="J91" s="750" t="n"/>
+      <c r="K91" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="752" t="n"/>
+      <c r="M91" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="754" t="n"/>
+      <c r="O91" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="756" t="n"/>
+      <c r="Q91" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="758" t="n">
+        <v>252.2</v>
+      </c>
+      <c r="S91" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="760" t="n">
+        <v>252.2</v>
+      </c>
+      <c r="U91" s="761" t="n">
+        <v>16085.59</v>
+      </c>
+      <c r="V91" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C92" s="764" t="n"/>
+      <c r="D92" s="765" t="n"/>
+      <c r="E92" s="766" t="n"/>
+      <c r="F92" s="767" t="n"/>
+      <c r="G92" s="768" t="n"/>
+      <c r="H92" s="769" t="n"/>
+      <c r="I92" s="770" t="n"/>
+      <c r="J92" s="771" t="n"/>
+      <c r="K92" s="772" t="n"/>
+      <c r="L92" s="773" t="n"/>
+      <c r="M92" s="774" t="n"/>
+      <c r="N92" s="775" t="n"/>
+      <c r="O92" s="776" t="n"/>
+      <c r="P92" s="777" t="n"/>
+      <c r="Q92" s="778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="779" t="n">
+        <v>1472.61</v>
+      </c>
+      <c r="S92" s="780" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="781" t="n">
+        <v>1472.61</v>
+      </c>
+      <c r="U92" s="782" t="n"/>
+      <c r="V92" s="783" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="784" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C93" s="785" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="786" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E93" s="787" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F93" s="788" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G93" s="789" t="n">
+        <v>15715.49</v>
+      </c>
+      <c r="H93" s="790" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I93" s="791" t="n">
+        <v>150.3</v>
+      </c>
+      <c r="J93" s="792" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K93" s="793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="794" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M93" s="795" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="796" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O93" s="797" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="798" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q93" s="799" t="n"/>
+      <c r="R93" s="800" t="n"/>
+      <c r="S93" s="801" t="n"/>
+      <c r="T93" s="802" t="n"/>
+      <c r="U93" s="803" t="n">
+        <v>16085.59</v>
+      </c>
+      <c r="V93" s="804" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="O2:P2"/>

--- a/output/2026/money/money.xlsx
+++ b/output/2026/money/money.xlsx
@@ -2414,7 +2414,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="815">
+  <cellXfs count="817">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3446,6 +3446,8 @@
     <xf numFmtId="0" fontId="0" fillId="58" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="56" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="56" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3828,7 +3830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V93"/>
+  <dimension ref="A2:V119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -8258,6 +8260,1184 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="B94" s="669" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="670" t="n"/>
+      <c r="D94" s="671" t="n"/>
+      <c r="E94" s="672" t="n"/>
+      <c r="F94" s="673" t="n"/>
+      <c r="G94" s="674" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H94" s="675" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="I94" s="676" t="n"/>
+      <c r="J94" s="677" t="n"/>
+      <c r="K94" s="805" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="L94" s="806" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M94" s="807" t="n"/>
+      <c r="N94" s="808" t="n"/>
+      <c r="O94" s="682" t="n"/>
+      <c r="P94" s="683" t="n"/>
+      <c r="Q94" s="684" t="n"/>
+      <c r="R94" s="685" t="n"/>
+      <c r="S94" s="686" t="n"/>
+      <c r="T94" s="687" t="n"/>
+      <c r="U94" s="688" t="n"/>
+      <c r="V94" s="689" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="690" t="n"/>
+      <c r="C95" s="691" t="n"/>
+      <c r="D95" s="692" t="n"/>
+      <c r="E95" s="693" t="n"/>
+      <c r="F95" s="694" t="n"/>
+      <c r="G95" s="695" t="n"/>
+      <c r="H95" s="696" t="n"/>
+      <c r="I95" s="713" t="n"/>
+      <c r="J95" s="714" t="n"/>
+      <c r="K95" s="715" t="inlineStr">
+        <is>
+          <t>Gundam</t>
+        </is>
+      </c>
+      <c r="L95" s="716" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="M95" s="701" t="n"/>
+      <c r="N95" s="702" t="n"/>
+      <c r="O95" s="703" t="n"/>
+      <c r="P95" s="704" t="n"/>
+      <c r="Q95" s="705" t="inlineStr">
+        <is>
+          <t>Gundam</t>
+        </is>
+      </c>
+      <c r="R95" s="706" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="S95" s="707" t="inlineStr">
+        <is>
+          <t>Gundam</t>
+        </is>
+      </c>
+      <c r="T95" s="708" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="U95" s="709" t="n"/>
+      <c r="V95" s="710" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="690" t="n"/>
+      <c r="C96" s="691" t="n"/>
+      <c r="D96" s="692" t="n"/>
+      <c r="E96" s="693" t="n"/>
+      <c r="F96" s="694" t="n"/>
+      <c r="G96" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H96" s="712" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="I96" s="713" t="n"/>
+      <c r="J96" s="714" t="n"/>
+      <c r="K96" s="715" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="L96" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M96" s="701" t="n"/>
+      <c r="N96" s="702" t="n"/>
+      <c r="O96" s="703" t="n"/>
+      <c r="P96" s="704" t="n"/>
+      <c r="Q96" s="717" t="n"/>
+      <c r="R96" s="718" t="n"/>
+      <c r="S96" s="719" t="n"/>
+      <c r="T96" s="720" t="n"/>
+      <c r="U96" s="709" t="n"/>
+      <c r="V96" s="710" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="690" t="n"/>
+      <c r="C97" s="691" t="n"/>
+      <c r="D97" s="692" t="n"/>
+      <c r="E97" s="693" t="n"/>
+      <c r="F97" s="694" t="n"/>
+      <c r="G97" s="695" t="n"/>
+      <c r="H97" s="696" t="n"/>
+      <c r="I97" s="713" t="n"/>
+      <c r="J97" s="714" t="n"/>
+      <c r="K97" s="715" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="L97" s="716" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="M97" s="701" t="n"/>
+      <c r="N97" s="702" t="n"/>
+      <c r="O97" s="703" t="n"/>
+      <c r="P97" s="704" t="n"/>
+      <c r="Q97" s="705" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="R97" s="706" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="S97" s="707" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="T97" s="708" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="U97" s="709" t="n"/>
+      <c r="V97" s="710" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="690" t="n"/>
+      <c r="C98" s="691" t="n"/>
+      <c r="D98" s="692" t="n"/>
+      <c r="E98" s="693" t="n"/>
+      <c r="F98" s="694" t="n"/>
+      <c r="G98" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H98" s="712" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I98" s="713" t="n"/>
+      <c r="J98" s="714" t="n"/>
+      <c r="K98" s="715" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L98" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M98" s="701" t="n"/>
+      <c r="N98" s="702" t="n"/>
+      <c r="O98" s="703" t="n"/>
+      <c r="P98" s="704" t="n"/>
+      <c r="Q98" s="717" t="n"/>
+      <c r="R98" s="718" t="n"/>
+      <c r="S98" s="719" t="n"/>
+      <c r="T98" s="720" t="n"/>
+      <c r="U98" s="709" t="n"/>
+      <c r="V98" s="710" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="690" t="n"/>
+      <c r="C99" s="691" t="n"/>
+      <c r="D99" s="692" t="n"/>
+      <c r="E99" s="693" t="n"/>
+      <c r="F99" s="694" t="n"/>
+      <c r="G99" s="695" t="n"/>
+      <c r="H99" s="696" t="n"/>
+      <c r="I99" s="713" t="n"/>
+      <c r="J99" s="714" t="n"/>
+      <c r="K99" s="715" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="L99" s="716" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="M99" s="701" t="n"/>
+      <c r="N99" s="702" t="n"/>
+      <c r="O99" s="703" t="n"/>
+      <c r="P99" s="704" t="n"/>
+      <c r="Q99" s="705" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="R99" s="706" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="S99" s="707" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="T99" s="708" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="U99" s="709" t="n"/>
+      <c r="V99" s="710" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="690" t="n"/>
+      <c r="C100" s="691" t="n"/>
+      <c r="D100" s="692" t="n"/>
+      <c r="E100" s="693" t="n"/>
+      <c r="F100" s="694" t="n"/>
+      <c r="G100" s="695" t="n"/>
+      <c r="H100" s="696" t="n"/>
+      <c r="I100" s="697" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J100" s="698" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="K100" s="699" t="n"/>
+      <c r="L100" s="700" t="n"/>
+      <c r="M100" s="701" t="n"/>
+      <c r="N100" s="702" t="n"/>
+      <c r="O100" s="703" t="n"/>
+      <c r="P100" s="704" t="n"/>
+      <c r="Q100" s="705" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R100" s="706" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="S100" s="707" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T100" s="708" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="U100" s="709" t="n"/>
+      <c r="V100" s="710" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="690" t="n"/>
+      <c r="C101" s="691" t="n"/>
+      <c r="D101" s="692" t="n"/>
+      <c r="E101" s="693" t="n"/>
+      <c r="F101" s="694" t="n"/>
+      <c r="G101" s="695" t="n"/>
+      <c r="H101" s="696" t="n"/>
+      <c r="I101" s="697" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="J101" s="698" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="K101" s="699" t="n"/>
+      <c r="L101" s="700" t="n"/>
+      <c r="M101" s="701" t="n"/>
+      <c r="N101" s="702" t="n"/>
+      <c r="O101" s="703" t="n"/>
+      <c r="P101" s="704" t="n"/>
+      <c r="Q101" s="705" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="R101" s="706" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="S101" s="707" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="T101" s="708" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="U101" s="709" t="n"/>
+      <c r="V101" s="710" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="690" t="n"/>
+      <c r="C102" s="691" t="n"/>
+      <c r="D102" s="692" t="n"/>
+      <c r="E102" s="693" t="n"/>
+      <c r="F102" s="694" t="n"/>
+      <c r="G102" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H102" s="712" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I102" s="713" t="n"/>
+      <c r="J102" s="714" t="n"/>
+      <c r="K102" s="715" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L102" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M102" s="701" t="n"/>
+      <c r="N102" s="702" t="n"/>
+      <c r="O102" s="703" t="n"/>
+      <c r="P102" s="704" t="n"/>
+      <c r="Q102" s="717" t="n"/>
+      <c r="R102" s="718" t="n"/>
+      <c r="S102" s="719" t="n"/>
+      <c r="T102" s="720" t="n"/>
+      <c r="U102" s="709" t="n"/>
+      <c r="V102" s="710" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="690" t="n"/>
+      <c r="C103" s="691" t="n"/>
+      <c r="D103" s="692" t="n"/>
+      <c r="E103" s="693" t="n"/>
+      <c r="F103" s="694" t="n"/>
+      <c r="G103" s="695" t="n"/>
+      <c r="H103" s="696" t="n"/>
+      <c r="I103" s="713" t="n"/>
+      <c r="J103" s="714" t="n"/>
+      <c r="K103" s="715" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="L103" s="716" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M103" s="701" t="n"/>
+      <c r="N103" s="702" t="n"/>
+      <c r="O103" s="703" t="n"/>
+      <c r="P103" s="704" t="n"/>
+      <c r="Q103" s="705" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="R103" s="706" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S103" s="707" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="T103" s="708" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U103" s="709" t="n"/>
+      <c r="V103" s="710" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="690" t="n"/>
+      <c r="C104" s="691" t="n"/>
+      <c r="D104" s="692" t="n"/>
+      <c r="E104" s="693" t="n"/>
+      <c r="F104" s="694" t="n"/>
+      <c r="G104" s="695" t="n"/>
+      <c r="H104" s="696" t="n"/>
+      <c r="I104" s="697" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="J104" s="698" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="K104" s="699" t="n"/>
+      <c r="L104" s="700" t="n"/>
+      <c r="M104" s="701" t="n"/>
+      <c r="N104" s="702" t="n"/>
+      <c r="O104" s="703" t="n"/>
+      <c r="P104" s="704" t="n"/>
+      <c r="Q104" s="705" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="R104" s="706" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="S104" s="707" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="T104" s="708" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="U104" s="709" t="n"/>
+      <c r="V104" s="710" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="690" t="n"/>
+      <c r="C105" s="691" t="n"/>
+      <c r="D105" s="692" t="n"/>
+      <c r="E105" s="693" t="n"/>
+      <c r="F105" s="694" t="n"/>
+      <c r="G105" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H105" s="712" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I105" s="713" t="n"/>
+      <c r="J105" s="714" t="n"/>
+      <c r="K105" s="715" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L105" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M105" s="701" t="n"/>
+      <c r="N105" s="702" t="n"/>
+      <c r="O105" s="703" t="n"/>
+      <c r="P105" s="704" t="n"/>
+      <c r="Q105" s="717" t="n"/>
+      <c r="R105" s="718" t="n"/>
+      <c r="S105" s="719" t="n"/>
+      <c r="T105" s="720" t="n"/>
+      <c r="U105" s="709" t="n"/>
+      <c r="V105" s="710" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="690" t="n"/>
+      <c r="C106" s="691" t="n"/>
+      <c r="D106" s="692" t="n"/>
+      <c r="E106" s="693" t="n"/>
+      <c r="F106" s="694" t="n"/>
+      <c r="G106" s="695" t="n"/>
+      <c r="H106" s="696" t="n"/>
+      <c r="I106" s="713" t="n"/>
+      <c r="J106" s="714" t="n"/>
+      <c r="K106" s="715" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="L106" s="716" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M106" s="701" t="n"/>
+      <c r="N106" s="702" t="n"/>
+      <c r="O106" s="703" t="n"/>
+      <c r="P106" s="704" t="n"/>
+      <c r="Q106" s="705" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="R106" s="706" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="S106" s="707" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="T106" s="708" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="U106" s="709" t="n"/>
+      <c r="V106" s="710" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="690" t="n"/>
+      <c r="C107" s="691" t="n"/>
+      <c r="D107" s="692" t="n"/>
+      <c r="E107" s="693" t="n"/>
+      <c r="F107" s="694" t="n"/>
+      <c r="G107" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H107" s="712" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="I107" s="713" t="n"/>
+      <c r="J107" s="714" t="n"/>
+      <c r="K107" s="715" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="L107" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M107" s="701" t="n"/>
+      <c r="N107" s="702" t="n"/>
+      <c r="O107" s="703" t="n"/>
+      <c r="P107" s="704" t="n"/>
+      <c r="Q107" s="717" t="n"/>
+      <c r="R107" s="718" t="n"/>
+      <c r="S107" s="719" t="n"/>
+      <c r="T107" s="720" t="n"/>
+      <c r="U107" s="709" t="n"/>
+      <c r="V107" s="710" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="690" t="n"/>
+      <c r="C108" s="691" t="n"/>
+      <c r="D108" s="692" t="n"/>
+      <c r="E108" s="693" t="n"/>
+      <c r="F108" s="694" t="n"/>
+      <c r="G108" s="695" t="n"/>
+      <c r="H108" s="696" t="n"/>
+      <c r="I108" s="713" t="n"/>
+      <c r="J108" s="714" t="n"/>
+      <c r="K108" s="715" t="inlineStr">
+        <is>
+          <t>Computer</t>
+        </is>
+      </c>
+      <c r="L108" s="716" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="M108" s="701" t="n"/>
+      <c r="N108" s="702" t="n"/>
+      <c r="O108" s="703" t="n"/>
+      <c r="P108" s="704" t="n"/>
+      <c r="Q108" s="705" t="inlineStr">
+        <is>
+          <t>Computer</t>
+        </is>
+      </c>
+      <c r="R108" s="706" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="S108" s="707" t="inlineStr">
+        <is>
+          <t>Computer</t>
+        </is>
+      </c>
+      <c r="T108" s="708" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="U108" s="709" t="n"/>
+      <c r="V108" s="710" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="721" t="n"/>
+      <c r="C109" s="722" t="n"/>
+      <c r="D109" s="723" t="n"/>
+      <c r="E109" s="724" t="n"/>
+      <c r="F109" s="725" t="n"/>
+      <c r="G109" s="726" t="n"/>
+      <c r="H109" s="727" t="n"/>
+      <c r="I109" s="813" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J109" s="814" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="K109" s="730" t="n"/>
+      <c r="L109" s="731" t="n"/>
+      <c r="M109" s="811" t="n"/>
+      <c r="N109" s="812" t="n"/>
+      <c r="O109" s="734" t="n"/>
+      <c r="P109" s="735" t="n"/>
+      <c r="Q109" s="736" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R109" s="737" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="S109" s="738" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T109" s="739" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="U109" s="740" t="n"/>
+      <c r="V109" s="741" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C110" s="743" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="744" t="n"/>
+      <c r="E110" s="745" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F110" s="746" t="n"/>
+      <c r="G110" s="747" t="n">
+        <v>15514.46</v>
+      </c>
+      <c r="H110" s="748" t="n"/>
+      <c r="I110" s="749" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="J110" s="750" t="n"/>
+      <c r="K110" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="752" t="n"/>
+      <c r="M110" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="754" t="n"/>
+      <c r="O110" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="756" t="n"/>
+      <c r="Q110" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="758" t="n">
+        <v>228.73</v>
+      </c>
+      <c r="S110" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" s="760" t="n">
+        <v>228.73</v>
+      </c>
+      <c r="U110" s="761" t="n">
+        <v>15856.86</v>
+      </c>
+      <c r="V110" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C111" s="764" t="n"/>
+      <c r="D111" s="765" t="n"/>
+      <c r="E111" s="766" t="n"/>
+      <c r="F111" s="767" t="n"/>
+      <c r="G111" s="768" t="n"/>
+      <c r="H111" s="769" t="n"/>
+      <c r="I111" s="770" t="n"/>
+      <c r="J111" s="771" t="n"/>
+      <c r="K111" s="772" t="n"/>
+      <c r="L111" s="773" t="n"/>
+      <c r="M111" s="774" t="n"/>
+      <c r="N111" s="775" t="n"/>
+      <c r="O111" s="776" t="n"/>
+      <c r="P111" s="777" t="n"/>
+      <c r="Q111" s="778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" s="779" t="n">
+        <v>1701.34</v>
+      </c>
+      <c r="S111" s="780" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" s="781" t="n">
+        <v>1701.34</v>
+      </c>
+      <c r="U111" s="782" t="n"/>
+      <c r="V111" s="783" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="669" t="inlineStr">
+        <is>
+          <t>20/6/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="670" t="n"/>
+      <c r="D112" s="671" t="n"/>
+      <c r="E112" s="672" t="n"/>
+      <c r="F112" s="673" t="n"/>
+      <c r="G112" s="674" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H112" s="675" t="inlineStr">
+        <is>
+          <t>Dad</t>
+        </is>
+      </c>
+      <c r="I112" s="676" t="n"/>
+      <c r="J112" s="677" t="n"/>
+      <c r="K112" s="678" t="n"/>
+      <c r="L112" s="679" t="n"/>
+      <c r="M112" s="807" t="n"/>
+      <c r="N112" s="808" t="n"/>
+      <c r="O112" s="682" t="n"/>
+      <c r="P112" s="683" t="n"/>
+      <c r="Q112" s="684" t="n"/>
+      <c r="R112" s="685" t="n"/>
+      <c r="S112" s="815" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="T112" s="816" t="inlineStr">
+        <is>
+          <t>Dad</t>
+        </is>
+      </c>
+      <c r="U112" s="688" t="n"/>
+      <c r="V112" s="689" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="690" t="n"/>
+      <c r="C113" s="691" t="n"/>
+      <c r="D113" s="692" t="n"/>
+      <c r="E113" s="693" t="n"/>
+      <c r="F113" s="694" t="n"/>
+      <c r="G113" s="711" t="inlineStr">
+        <is>
+          <t>Dad</t>
+        </is>
+      </c>
+      <c r="H113" s="712" t="inlineStr">
+        <is>
+          <t>1685.55</t>
+        </is>
+      </c>
+      <c r="I113" s="713" t="n"/>
+      <c r="J113" s="714" t="n"/>
+      <c r="K113" s="699" t="n"/>
+      <c r="L113" s="700" t="n"/>
+      <c r="M113" s="701" t="n"/>
+      <c r="N113" s="702" t="n"/>
+      <c r="O113" s="703" t="n"/>
+      <c r="P113" s="704" t="n"/>
+      <c r="Q113" s="717" t="n"/>
+      <c r="R113" s="718" t="n"/>
+      <c r="S113" s="707" t="inlineStr">
+        <is>
+          <t>Dad</t>
+        </is>
+      </c>
+      <c r="T113" s="708" t="inlineStr">
+        <is>
+          <t>1685.55</t>
+        </is>
+      </c>
+      <c r="U113" s="709" t="n"/>
+      <c r="V113" s="710" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="690" t="n"/>
+      <c r="C114" s="691" t="n"/>
+      <c r="D114" s="692" t="n"/>
+      <c r="E114" s="693" t="n"/>
+      <c r="F114" s="694" t="n"/>
+      <c r="G114" s="695" t="n"/>
+      <c r="H114" s="696" t="n"/>
+      <c r="I114" s="697" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J114" s="698" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="K114" s="699" t="n"/>
+      <c r="L114" s="700" t="n"/>
+      <c r="M114" s="701" t="n"/>
+      <c r="N114" s="702" t="n"/>
+      <c r="O114" s="703" t="n"/>
+      <c r="P114" s="704" t="n"/>
+      <c r="Q114" s="705" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R114" s="706" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="S114" s="707" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T114" s="708" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="U114" s="709" t="n"/>
+      <c r="V114" s="710" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="690" t="n"/>
+      <c r="C115" s="691" t="n"/>
+      <c r="D115" s="692" t="n"/>
+      <c r="E115" s="693" t="n"/>
+      <c r="F115" s="694" t="n"/>
+      <c r="G115" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H115" s="712" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="I115" s="713" t="n"/>
+      <c r="J115" s="714" t="n"/>
+      <c r="K115" s="715" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="L115" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M115" s="701" t="n"/>
+      <c r="N115" s="702" t="n"/>
+      <c r="O115" s="703" t="n"/>
+      <c r="P115" s="704" t="n"/>
+      <c r="Q115" s="717" t="n"/>
+      <c r="R115" s="718" t="n"/>
+      <c r="S115" s="719" t="n"/>
+      <c r="T115" s="720" t="n"/>
+      <c r="U115" s="709" t="n"/>
+      <c r="V115" s="710" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="721" t="n"/>
+      <c r="C116" s="722" t="n"/>
+      <c r="D116" s="723" t="n"/>
+      <c r="E116" s="724" t="n"/>
+      <c r="F116" s="725" t="n"/>
+      <c r="G116" s="726" t="n"/>
+      <c r="H116" s="727" t="n"/>
+      <c r="I116" s="728" t="n"/>
+      <c r="J116" s="729" t="n"/>
+      <c r="K116" s="809" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="L116" s="810" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="M116" s="811" t="n"/>
+      <c r="N116" s="812" t="n"/>
+      <c r="O116" s="734" t="n"/>
+      <c r="P116" s="735" t="n"/>
+      <c r="Q116" s="736" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="R116" s="737" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="S116" s="738" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="T116" s="739" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="U116" s="740" t="n"/>
+      <c r="V116" s="741" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C117" s="743" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="744" t="n"/>
+      <c r="E117" s="745" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F117" s="746" t="n"/>
+      <c r="G117" s="747" t="n">
+        <v>15789.41</v>
+      </c>
+      <c r="H117" s="748" t="n"/>
+      <c r="I117" s="749" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="J117" s="750" t="n"/>
+      <c r="K117" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="752" t="n"/>
+      <c r="M117" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="754" t="n"/>
+      <c r="O117" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="756" t="n"/>
+      <c r="Q117" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" s="758" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="S117" s="759" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T117" s="760" t="n">
+        <v>1728.85</v>
+      </c>
+      <c r="U117" s="761" t="n">
+        <v>16128.01</v>
+      </c>
+      <c r="V117" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C118" s="764" t="n"/>
+      <c r="D118" s="765" t="n"/>
+      <c r="E118" s="766" t="n"/>
+      <c r="F118" s="767" t="n"/>
+      <c r="G118" s="768" t="n"/>
+      <c r="H118" s="769" t="n"/>
+      <c r="I118" s="770" t="n"/>
+      <c r="J118" s="771" t="n"/>
+      <c r="K118" s="772" t="n"/>
+      <c r="L118" s="773" t="n"/>
+      <c r="M118" s="774" t="n"/>
+      <c r="N118" s="775" t="n"/>
+      <c r="O118" s="776" t="n"/>
+      <c r="P118" s="777" t="n"/>
+      <c r="Q118" s="778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" s="779" t="n">
+        <v>1744.64</v>
+      </c>
+      <c r="S118" s="780" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T118" s="781" t="n">
+        <v>3430.19</v>
+      </c>
+      <c r="U118" s="782" t="n"/>
+      <c r="V118" s="783" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="784" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C119" s="785" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="786" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E119" s="787" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F119" s="788" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G119" s="789" t="n">
+        <v>15789.41</v>
+      </c>
+      <c r="H119" s="790" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I119" s="791" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="J119" s="792" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K119" s="793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="794" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M119" s="795" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="796" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O119" s="797" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="798" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q119" s="799" t="n"/>
+      <c r="R119" s="800" t="n"/>
+      <c r="S119" s="801" t="n"/>
+      <c r="T119" s="802" t="n"/>
+      <c r="U119" s="803" t="n">
+        <v>16128.01</v>
+      </c>
+      <c r="V119" s="804" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="O2:P2"/>

--- a/output/2026/money/money.xlsx
+++ b/output/2026/money/money.xlsx
@@ -2414,7 +2414,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="817">
+  <cellXfs count="833">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3448,6 +3448,22 @@
     <xf numFmtId="0" fontId="6" fillId="56" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="61" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="61" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3830,7 +3846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V119"/>
+  <dimension ref="A2:V175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
@@ -9438,6 +9454,2602 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" s="669" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="670" t="n"/>
+      <c r="D120" s="671" t="n"/>
+      <c r="E120" s="672" t="n"/>
+      <c r="F120" s="673" t="n"/>
+      <c r="G120" s="817" t="n"/>
+      <c r="H120" s="818" t="n"/>
+      <c r="I120" s="819" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J120" s="820" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="K120" s="678" t="n"/>
+      <c r="L120" s="679" t="n"/>
+      <c r="M120" s="807" t="n"/>
+      <c r="N120" s="808" t="n"/>
+      <c r="O120" s="682" t="n"/>
+      <c r="P120" s="683" t="n"/>
+      <c r="Q120" s="821" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R120" s="822" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="S120" s="815" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T120" s="816" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="U120" s="688" t="n"/>
+      <c r="V120" s="689" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="690" t="n"/>
+      <c r="C121" s="691" t="n"/>
+      <c r="D121" s="692" t="n"/>
+      <c r="E121" s="693" t="n"/>
+      <c r="F121" s="694" t="n"/>
+      <c r="G121" s="695" t="n"/>
+      <c r="H121" s="696" t="n"/>
+      <c r="I121" s="697" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="J121" s="698" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="K121" s="699" t="n"/>
+      <c r="L121" s="700" t="n"/>
+      <c r="M121" s="701" t="n"/>
+      <c r="N121" s="702" t="n"/>
+      <c r="O121" s="703" t="n"/>
+      <c r="P121" s="704" t="n"/>
+      <c r="Q121" s="705" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="R121" s="706" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="S121" s="707" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="T121" s="708" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="U121" s="709" t="n"/>
+      <c r="V121" s="710" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="690" t="n"/>
+      <c r="C122" s="691" t="n"/>
+      <c r="D122" s="692" t="n"/>
+      <c r="E122" s="693" t="n"/>
+      <c r="F122" s="694" t="n"/>
+      <c r="G122" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H122" s="712" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I122" s="713" t="n"/>
+      <c r="J122" s="714" t="n"/>
+      <c r="K122" s="715" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L122" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M122" s="701" t="n"/>
+      <c r="N122" s="702" t="n"/>
+      <c r="O122" s="703" t="n"/>
+      <c r="P122" s="704" t="n"/>
+      <c r="Q122" s="717" t="n"/>
+      <c r="R122" s="718" t="n"/>
+      <c r="S122" s="719" t="n"/>
+      <c r="T122" s="720" t="n"/>
+      <c r="U122" s="709" t="n"/>
+      <c r="V122" s="710" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="690" t="n"/>
+      <c r="C123" s="691" t="n"/>
+      <c r="D123" s="692" t="n"/>
+      <c r="E123" s="693" t="n"/>
+      <c r="F123" s="694" t="n"/>
+      <c r="G123" s="695" t="n"/>
+      <c r="H123" s="696" t="n"/>
+      <c r="I123" s="713" t="n"/>
+      <c r="J123" s="714" t="n"/>
+      <c r="K123" s="715" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="L123" s="716" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M123" s="701" t="n"/>
+      <c r="N123" s="702" t="n"/>
+      <c r="O123" s="703" t="n"/>
+      <c r="P123" s="704" t="n"/>
+      <c r="Q123" s="705" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="R123" s="706" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="S123" s="707" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="T123" s="708" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="U123" s="709" t="n"/>
+      <c r="V123" s="710" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="690" t="n"/>
+      <c r="C124" s="691" t="n"/>
+      <c r="D124" s="692" t="n"/>
+      <c r="E124" s="693" t="n"/>
+      <c r="F124" s="694" t="n"/>
+      <c r="G124" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H124" s="712" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I124" s="713" t="n"/>
+      <c r="J124" s="714" t="n"/>
+      <c r="K124" s="715" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L124" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M124" s="701" t="n"/>
+      <c r="N124" s="702" t="n"/>
+      <c r="O124" s="703" t="n"/>
+      <c r="P124" s="704" t="n"/>
+      <c r="Q124" s="717" t="n"/>
+      <c r="R124" s="718" t="n"/>
+      <c r="S124" s="719" t="n"/>
+      <c r="T124" s="720" t="n"/>
+      <c r="U124" s="709" t="n"/>
+      <c r="V124" s="710" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="690" t="n"/>
+      <c r="C125" s="691" t="n"/>
+      <c r="D125" s="692" t="n"/>
+      <c r="E125" s="693" t="n"/>
+      <c r="F125" s="694" t="n"/>
+      <c r="G125" s="695" t="n"/>
+      <c r="H125" s="696" t="n"/>
+      <c r="I125" s="713" t="n"/>
+      <c r="J125" s="714" t="n"/>
+      <c r="K125" s="715" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="L125" s="716" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M125" s="701" t="n"/>
+      <c r="N125" s="702" t="n"/>
+      <c r="O125" s="703" t="n"/>
+      <c r="P125" s="704" t="n"/>
+      <c r="Q125" s="705" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="R125" s="706" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S125" s="707" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="T125" s="708" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U125" s="709" t="n"/>
+      <c r="V125" s="710" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="690" t="n"/>
+      <c r="C126" s="691" t="n"/>
+      <c r="D126" s="692" t="n"/>
+      <c r="E126" s="693" t="n"/>
+      <c r="F126" s="694" t="n"/>
+      <c r="G126" s="695" t="n"/>
+      <c r="H126" s="696" t="n"/>
+      <c r="I126" s="697" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="J126" s="698" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K126" s="699" t="n"/>
+      <c r="L126" s="700" t="n"/>
+      <c r="M126" s="701" t="n"/>
+      <c r="N126" s="702" t="n"/>
+      <c r="O126" s="703" t="n"/>
+      <c r="P126" s="704" t="n"/>
+      <c r="Q126" s="705" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="R126" s="706" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="S126" s="707" t="inlineStr">
+        <is>
+          <t>Bread</t>
+        </is>
+      </c>
+      <c r="T126" s="708" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="U126" s="709" t="n"/>
+      <c r="V126" s="710" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="690" t="n"/>
+      <c r="C127" s="691" t="n"/>
+      <c r="D127" s="692" t="n"/>
+      <c r="E127" s="693" t="n"/>
+      <c r="F127" s="694" t="n"/>
+      <c r="G127" s="695" t="n"/>
+      <c r="H127" s="696" t="n"/>
+      <c r="I127" s="697" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J127" s="698" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K127" s="699" t="n"/>
+      <c r="L127" s="700" t="n"/>
+      <c r="M127" s="701" t="n"/>
+      <c r="N127" s="702" t="n"/>
+      <c r="O127" s="703" t="n"/>
+      <c r="P127" s="704" t="n"/>
+      <c r="Q127" s="705" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R127" s="706" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S127" s="707" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T127" s="708" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U127" s="709" t="n"/>
+      <c r="V127" s="710" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="690" t="n"/>
+      <c r="C128" s="691" t="n"/>
+      <c r="D128" s="692" t="n"/>
+      <c r="E128" s="693" t="n"/>
+      <c r="F128" s="694" t="n"/>
+      <c r="G128" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H128" s="712" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="I128" s="713" t="n"/>
+      <c r="J128" s="714" t="n"/>
+      <c r="K128" s="715" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="L128" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M128" s="701" t="n"/>
+      <c r="N128" s="702" t="n"/>
+      <c r="O128" s="703" t="n"/>
+      <c r="P128" s="704" t="n"/>
+      <c r="Q128" s="717" t="n"/>
+      <c r="R128" s="718" t="n"/>
+      <c r="S128" s="719" t="n"/>
+      <c r="T128" s="720" t="n"/>
+      <c r="U128" s="709" t="n"/>
+      <c r="V128" s="710" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="690" t="n"/>
+      <c r="C129" s="691" t="n"/>
+      <c r="D129" s="692" t="n"/>
+      <c r="E129" s="693" t="n"/>
+      <c r="F129" s="694" t="n"/>
+      <c r="G129" s="695" t="n"/>
+      <c r="H129" s="696" t="n"/>
+      <c r="I129" s="713" t="n"/>
+      <c r="J129" s="714" t="n"/>
+      <c r="K129" s="715" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="L129" s="716" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="M129" s="701" t="n"/>
+      <c r="N129" s="702" t="n"/>
+      <c r="O129" s="703" t="n"/>
+      <c r="P129" s="704" t="n"/>
+      <c r="Q129" s="705" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="R129" s="706" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="S129" s="707" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="T129" s="708" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="U129" s="709" t="n"/>
+      <c r="V129" s="710" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="721" t="n"/>
+      <c r="C130" s="722" t="n"/>
+      <c r="D130" s="723" t="n"/>
+      <c r="E130" s="724" t="n"/>
+      <c r="F130" s="725" t="n"/>
+      <c r="G130" s="726" t="n"/>
+      <c r="H130" s="727" t="n"/>
+      <c r="I130" s="813" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J130" s="814" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="K130" s="730" t="n"/>
+      <c r="L130" s="731" t="n"/>
+      <c r="M130" s="811" t="n"/>
+      <c r="N130" s="812" t="n"/>
+      <c r="O130" s="734" t="n"/>
+      <c r="P130" s="735" t="n"/>
+      <c r="Q130" s="736" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R130" s="737" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="S130" s="738" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T130" s="739" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="U130" s="740" t="n"/>
+      <c r="V130" s="741" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C131" s="743" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="744" t="n"/>
+      <c r="E131" s="745" t="n">
+        <v>219.8</v>
+      </c>
+      <c r="F131" s="746" t="n"/>
+      <c r="G131" s="747" t="n">
+        <v>15599.41</v>
+      </c>
+      <c r="H131" s="748" t="n"/>
+      <c r="I131" s="749" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J131" s="750" t="n"/>
+      <c r="K131" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="752" t="n"/>
+      <c r="M131" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="754" t="n"/>
+      <c r="O131" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="756" t="n"/>
+      <c r="Q131" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" s="758" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="S131" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" s="760" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="U131" s="761" t="n">
+        <v>15870.41</v>
+      </c>
+      <c r="V131" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C132" s="764" t="n"/>
+      <c r="D132" s="765" t="n"/>
+      <c r="E132" s="766" t="n"/>
+      <c r="F132" s="767" t="n"/>
+      <c r="G132" s="768" t="n"/>
+      <c r="H132" s="769" t="n"/>
+      <c r="I132" s="770" t="n"/>
+      <c r="J132" s="771" t="n"/>
+      <c r="K132" s="772" t="n"/>
+      <c r="L132" s="773" t="n"/>
+      <c r="M132" s="774" t="n"/>
+      <c r="N132" s="775" t="n"/>
+      <c r="O132" s="776" t="n"/>
+      <c r="P132" s="777" t="n"/>
+      <c r="Q132" s="778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" s="779" t="n">
+        <v>2002.24</v>
+      </c>
+      <c r="S132" s="780" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T132" s="781" t="n">
+        <v>3687.79</v>
+      </c>
+      <c r="U132" s="782" t="n"/>
+      <c r="V132" s="783" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="669" t="inlineStr">
+        <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="670" t="n"/>
+      <c r="D133" s="671" t="n"/>
+      <c r="E133" s="672" t="n"/>
+      <c r="F133" s="673" t="n"/>
+      <c r="G133" s="674" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H133" s="675" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I133" s="676" t="n"/>
+      <c r="J133" s="677" t="n"/>
+      <c r="K133" s="805" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L133" s="806" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M133" s="807" t="n"/>
+      <c r="N133" s="808" t="n"/>
+      <c r="O133" s="682" t="n"/>
+      <c r="P133" s="683" t="n"/>
+      <c r="Q133" s="684" t="n"/>
+      <c r="R133" s="685" t="n"/>
+      <c r="S133" s="686" t="n"/>
+      <c r="T133" s="687" t="n"/>
+      <c r="U133" s="688" t="n"/>
+      <c r="V133" s="689" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="690" t="n"/>
+      <c r="C134" s="691" t="n"/>
+      <c r="D134" s="692" t="n"/>
+      <c r="E134" s="693" t="n"/>
+      <c r="F134" s="694" t="n"/>
+      <c r="G134" s="695" t="n"/>
+      <c r="H134" s="696" t="n"/>
+      <c r="I134" s="713" t="n"/>
+      <c r="J134" s="714" t="n"/>
+      <c r="K134" s="715" t="inlineStr">
+        <is>
+          <t>Hair cut</t>
+        </is>
+      </c>
+      <c r="L134" s="716" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M134" s="701" t="n"/>
+      <c r="N134" s="702" t="n"/>
+      <c r="O134" s="703" t="n"/>
+      <c r="P134" s="704" t="n"/>
+      <c r="Q134" s="705" t="inlineStr">
+        <is>
+          <t>Hair cut</t>
+        </is>
+      </c>
+      <c r="R134" s="706" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="S134" s="707" t="inlineStr">
+        <is>
+          <t>Hair cut</t>
+        </is>
+      </c>
+      <c r="T134" s="708" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U134" s="709" t="n"/>
+      <c r="V134" s="710" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="690" t="n"/>
+      <c r="C135" s="691" t="n"/>
+      <c r="D135" s="692" t="n"/>
+      <c r="E135" s="693" t="n"/>
+      <c r="F135" s="694" t="n"/>
+      <c r="G135" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H135" s="712" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="I135" s="713" t="n"/>
+      <c r="J135" s="714" t="n"/>
+      <c r="K135" s="715" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="L135" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M135" s="701" t="n"/>
+      <c r="N135" s="702" t="n"/>
+      <c r="O135" s="703" t="n"/>
+      <c r="P135" s="704" t="n"/>
+      <c r="Q135" s="717" t="n"/>
+      <c r="R135" s="718" t="n"/>
+      <c r="S135" s="719" t="n"/>
+      <c r="T135" s="720" t="n"/>
+      <c r="U135" s="709" t="n"/>
+      <c r="V135" s="710" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="690" t="n"/>
+      <c r="C136" s="691" t="n"/>
+      <c r="D136" s="692" t="n"/>
+      <c r="E136" s="693" t="n"/>
+      <c r="F136" s="694" t="n"/>
+      <c r="G136" s="695" t="n"/>
+      <c r="H136" s="696" t="n"/>
+      <c r="I136" s="713" t="n"/>
+      <c r="J136" s="714" t="n"/>
+      <c r="K136" s="715" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="L136" s="716" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="M136" s="701" t="n"/>
+      <c r="N136" s="702" t="n"/>
+      <c r="O136" s="703" t="n"/>
+      <c r="P136" s="704" t="n"/>
+      <c r="Q136" s="705" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="R136" s="706" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="S136" s="707" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="T136" s="708" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="U136" s="709" t="n"/>
+      <c r="V136" s="710" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="690" t="n"/>
+      <c r="C137" s="691" t="n"/>
+      <c r="D137" s="692" t="n"/>
+      <c r="E137" s="693" t="n"/>
+      <c r="F137" s="694" t="n"/>
+      <c r="G137" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H137" s="712" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I137" s="713" t="n"/>
+      <c r="J137" s="714" t="n"/>
+      <c r="K137" s="715" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L137" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M137" s="701" t="n"/>
+      <c r="N137" s="702" t="n"/>
+      <c r="O137" s="703" t="n"/>
+      <c r="P137" s="704" t="n"/>
+      <c r="Q137" s="717" t="n"/>
+      <c r="R137" s="718" t="n"/>
+      <c r="S137" s="719" t="n"/>
+      <c r="T137" s="720" t="n"/>
+      <c r="U137" s="709" t="n"/>
+      <c r="V137" s="710" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="690" t="n"/>
+      <c r="C138" s="691" t="n"/>
+      <c r="D138" s="692" t="n"/>
+      <c r="E138" s="693" t="n"/>
+      <c r="F138" s="694" t="n"/>
+      <c r="G138" s="695" t="n"/>
+      <c r="H138" s="696" t="n"/>
+      <c r="I138" s="713" t="n"/>
+      <c r="J138" s="714" t="n"/>
+      <c r="K138" s="715" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="L138" s="716" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M138" s="701" t="n"/>
+      <c r="N138" s="702" t="n"/>
+      <c r="O138" s="703" t="n"/>
+      <c r="P138" s="704" t="n"/>
+      <c r="Q138" s="705" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="R138" s="706" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="S138" s="707" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="T138" s="708" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="U138" s="709" t="n"/>
+      <c r="V138" s="710" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="721" t="n"/>
+      <c r="C139" s="823" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D139" s="824" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E139" s="825" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F139" s="826" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G139" s="726" t="n"/>
+      <c r="H139" s="727" t="n"/>
+      <c r="I139" s="728" t="n"/>
+      <c r="J139" s="729" t="n"/>
+      <c r="K139" s="730" t="n"/>
+      <c r="L139" s="731" t="n"/>
+      <c r="M139" s="811" t="n"/>
+      <c r="N139" s="812" t="n"/>
+      <c r="O139" s="734" t="n"/>
+      <c r="P139" s="735" t="n"/>
+      <c r="Q139" s="827" t="n"/>
+      <c r="R139" s="828" t="n"/>
+      <c r="S139" s="829" t="n"/>
+      <c r="T139" s="830" t="n"/>
+      <c r="U139" s="740" t="n"/>
+      <c r="V139" s="741" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C140" s="743" t="n">
+        <v>10</v>
+      </c>
+      <c r="D140" s="744" t="n"/>
+      <c r="E140" s="745" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F140" s="746" t="n"/>
+      <c r="G140" s="747" t="n">
+        <v>15343.91</v>
+      </c>
+      <c r="H140" s="748" t="n"/>
+      <c r="I140" s="749" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J140" s="750" t="n"/>
+      <c r="K140" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="752" t="n"/>
+      <c r="M140" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="754" t="n"/>
+      <c r="O140" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="756" t="n"/>
+      <c r="Q140" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="758" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="S140" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" s="760" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="U140" s="761" t="n">
+        <v>15614.91</v>
+      </c>
+      <c r="V140" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C141" s="764" t="n"/>
+      <c r="D141" s="765" t="n"/>
+      <c r="E141" s="766" t="n"/>
+      <c r="F141" s="767" t="n"/>
+      <c r="G141" s="768" t="n"/>
+      <c r="H141" s="769" t="n"/>
+      <c r="I141" s="770" t="n"/>
+      <c r="J141" s="771" t="n"/>
+      <c r="K141" s="772" t="n"/>
+      <c r="L141" s="773" t="n"/>
+      <c r="M141" s="774" t="n"/>
+      <c r="N141" s="775" t="n"/>
+      <c r="O141" s="776" t="n"/>
+      <c r="P141" s="777" t="n"/>
+      <c r="Q141" s="778" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" s="779" t="n">
+        <v>2257.74</v>
+      </c>
+      <c r="S141" s="780" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T141" s="781" t="n">
+        <v>3943.29</v>
+      </c>
+      <c r="U141" s="782" t="n"/>
+      <c r="V141" s="783" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="784" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C142" s="785" t="n">
+        <v>10</v>
+      </c>
+      <c r="D142" s="786" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E142" s="787" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F142" s="788" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G142" s="789" t="n">
+        <v>15343.91</v>
+      </c>
+      <c r="H142" s="790" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I142" s="791" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="J142" s="792" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K142" s="793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="794" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M142" s="795" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="796" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O142" s="797" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="798" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q142" s="799" t="n"/>
+      <c r="R142" s="800" t="n"/>
+      <c r="S142" s="801" t="n"/>
+      <c r="T142" s="802" t="n"/>
+      <c r="U142" s="803" t="n">
+        <v>15614.91</v>
+      </c>
+      <c r="V142" s="804" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="669" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="670" t="n"/>
+      <c r="D143" s="671" t="n"/>
+      <c r="E143" s="672" t="n"/>
+      <c r="F143" s="673" t="n"/>
+      <c r="G143" s="817" t="n"/>
+      <c r="H143" s="818" t="n"/>
+      <c r="I143" s="819" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J143" s="820" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="K143" s="678" t="n"/>
+      <c r="L143" s="679" t="n"/>
+      <c r="M143" s="807" t="n"/>
+      <c r="N143" s="808" t="n"/>
+      <c r="O143" s="682" t="n"/>
+      <c r="P143" s="683" t="n"/>
+      <c r="Q143" s="821" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R143" s="822" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="S143" s="815" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T143" s="816" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="U143" s="688" t="n"/>
+      <c r="V143" s="689" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="690" t="n"/>
+      <c r="C144" s="691" t="n"/>
+      <c r="D144" s="692" t="n"/>
+      <c r="E144" s="693" t="n"/>
+      <c r="F144" s="694" t="n"/>
+      <c r="G144" s="711" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H144" s="712" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I144" s="697" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J144" s="698" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="K144" s="699" t="n"/>
+      <c r="L144" s="700" t="n"/>
+      <c r="M144" s="701" t="n"/>
+      <c r="N144" s="702" t="n"/>
+      <c r="O144" s="703" t="n"/>
+      <c r="P144" s="704" t="n"/>
+      <c r="Q144" s="717" t="n"/>
+      <c r="R144" s="718" t="n"/>
+      <c r="S144" s="719" t="n"/>
+      <c r="T144" s="720" t="n"/>
+      <c r="U144" s="709" t="n"/>
+      <c r="V144" s="710" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="690" t="n"/>
+      <c r="C145" s="691" t="n"/>
+      <c r="D145" s="692" t="n"/>
+      <c r="E145" s="693" t="n"/>
+      <c r="F145" s="694" t="n"/>
+      <c r="G145" s="695" t="n"/>
+      <c r="H145" s="696" t="n"/>
+      <c r="I145" s="697" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="J145" s="698" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="K145" s="699" t="n"/>
+      <c r="L145" s="700" t="n"/>
+      <c r="M145" s="701" t="n"/>
+      <c r="N145" s="702" t="n"/>
+      <c r="O145" s="703" t="n"/>
+      <c r="P145" s="704" t="n"/>
+      <c r="Q145" s="705" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="R145" s="706" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="S145" s="707" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="T145" s="708" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="U145" s="709" t="n"/>
+      <c r="V145" s="710" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="690" t="n"/>
+      <c r="C146" s="691" t="n"/>
+      <c r="D146" s="692" t="n"/>
+      <c r="E146" s="693" t="n"/>
+      <c r="F146" s="694" t="n"/>
+      <c r="G146" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H146" s="712" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="I146" s="713" t="n"/>
+      <c r="J146" s="714" t="n"/>
+      <c r="K146" s="715" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="L146" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M146" s="701" t="n"/>
+      <c r="N146" s="702" t="n"/>
+      <c r="O146" s="703" t="n"/>
+      <c r="P146" s="704" t="n"/>
+      <c r="Q146" s="717" t="n"/>
+      <c r="R146" s="718" t="n"/>
+      <c r="S146" s="719" t="n"/>
+      <c r="T146" s="720" t="n"/>
+      <c r="U146" s="709" t="n"/>
+      <c r="V146" s="710" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="690" t="n"/>
+      <c r="C147" s="691" t="n"/>
+      <c r="D147" s="692" t="n"/>
+      <c r="E147" s="693" t="n"/>
+      <c r="F147" s="694" t="n"/>
+      <c r="G147" s="695" t="n"/>
+      <c r="H147" s="696" t="n"/>
+      <c r="I147" s="713" t="n"/>
+      <c r="J147" s="714" t="n"/>
+      <c r="K147" s="715" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="L147" s="716" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="M147" s="701" t="n"/>
+      <c r="N147" s="702" t="n"/>
+      <c r="O147" s="703" t="n"/>
+      <c r="P147" s="704" t="n"/>
+      <c r="Q147" s="705" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="R147" s="706" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="S147" s="707" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="T147" s="708" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="U147" s="709" t="n"/>
+      <c r="V147" s="710" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="690" t="n"/>
+      <c r="C148" s="691" t="n"/>
+      <c r="D148" s="692" t="n"/>
+      <c r="E148" s="693" t="n"/>
+      <c r="F148" s="694" t="n"/>
+      <c r="G148" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H148" s="712" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I148" s="713" t="n"/>
+      <c r="J148" s="714" t="n"/>
+      <c r="K148" s="715" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L148" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M148" s="701" t="n"/>
+      <c r="N148" s="702" t="n"/>
+      <c r="O148" s="703" t="n"/>
+      <c r="P148" s="704" t="n"/>
+      <c r="Q148" s="717" t="n"/>
+      <c r="R148" s="718" t="n"/>
+      <c r="S148" s="719" t="n"/>
+      <c r="T148" s="720" t="n"/>
+      <c r="U148" s="709" t="n"/>
+      <c r="V148" s="710" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="690" t="n"/>
+      <c r="C149" s="691" t="n"/>
+      <c r="D149" s="692" t="n"/>
+      <c r="E149" s="693" t="n"/>
+      <c r="F149" s="694" t="n"/>
+      <c r="G149" s="695" t="n"/>
+      <c r="H149" s="696" t="n"/>
+      <c r="I149" s="713" t="n"/>
+      <c r="J149" s="714" t="n"/>
+      <c r="K149" s="715" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="L149" s="716" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M149" s="701" t="n"/>
+      <c r="N149" s="702" t="n"/>
+      <c r="O149" s="703" t="n"/>
+      <c r="P149" s="704" t="n"/>
+      <c r="Q149" s="705" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="R149" s="706" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S149" s="707" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="T149" s="708" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="U149" s="709" t="n"/>
+      <c r="V149" s="710" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="690" t="n"/>
+      <c r="C150" s="691" t="n"/>
+      <c r="D150" s="692" t="n"/>
+      <c r="E150" s="693" t="n"/>
+      <c r="F150" s="694" t="n"/>
+      <c r="G150" s="695" t="n"/>
+      <c r="H150" s="696" t="n"/>
+      <c r="I150" s="697" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="J150" s="698" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K150" s="699" t="n"/>
+      <c r="L150" s="700" t="n"/>
+      <c r="M150" s="701" t="n"/>
+      <c r="N150" s="702" t="n"/>
+      <c r="O150" s="703" t="n"/>
+      <c r="P150" s="704" t="n"/>
+      <c r="Q150" s="705" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="R150" s="706" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S150" s="707" t="inlineStr">
+        <is>
+          <t>MTR</t>
+        </is>
+      </c>
+      <c r="T150" s="708" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="U150" s="709" t="n"/>
+      <c r="V150" s="710" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="690" t="n"/>
+      <c r="C151" s="691" t="n"/>
+      <c r="D151" s="692" t="n"/>
+      <c r="E151" s="693" t="n"/>
+      <c r="F151" s="694" t="n"/>
+      <c r="G151" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H151" s="712" t="inlineStr">
+        <is>
+          <t>146.4</t>
+        </is>
+      </c>
+      <c r="I151" s="713" t="n"/>
+      <c r="J151" s="714" t="n"/>
+      <c r="K151" s="715" t="inlineStr">
+        <is>
+          <t>146.4</t>
+        </is>
+      </c>
+      <c r="L151" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M151" s="701" t="n"/>
+      <c r="N151" s="702" t="n"/>
+      <c r="O151" s="703" t="n"/>
+      <c r="P151" s="704" t="n"/>
+      <c r="Q151" s="717" t="n"/>
+      <c r="R151" s="718" t="n"/>
+      <c r="S151" s="719" t="n"/>
+      <c r="T151" s="720" t="n"/>
+      <c r="U151" s="709" t="n"/>
+      <c r="V151" s="710" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="690" t="n"/>
+      <c r="C152" s="691" t="n"/>
+      <c r="D152" s="692" t="n"/>
+      <c r="E152" s="693" t="n"/>
+      <c r="F152" s="694" t="n"/>
+      <c r="G152" s="695" t="n"/>
+      <c r="H152" s="696" t="n"/>
+      <c r="I152" s="713" t="n"/>
+      <c r="J152" s="714" t="n"/>
+      <c r="K152" s="715" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="L152" s="716" t="inlineStr">
+        <is>
+          <t>146.4</t>
+        </is>
+      </c>
+      <c r="M152" s="701" t="n"/>
+      <c r="N152" s="702" t="n"/>
+      <c r="O152" s="703" t="n"/>
+      <c r="P152" s="704" t="n"/>
+      <c r="Q152" s="705" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="R152" s="706" t="inlineStr">
+        <is>
+          <t>146.4</t>
+        </is>
+      </c>
+      <c r="S152" s="707" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="T152" s="708" t="inlineStr">
+        <is>
+          <t>146.4</t>
+        </is>
+      </c>
+      <c r="U152" s="709" t="n"/>
+      <c r="V152" s="710" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="690" t="n"/>
+      <c r="C153" s="691" t="n"/>
+      <c r="D153" s="692" t="n"/>
+      <c r="E153" s="693" t="n"/>
+      <c r="F153" s="694" t="n"/>
+      <c r="G153" s="711" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="H153" s="712" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="I153" s="713" t="n"/>
+      <c r="J153" s="714" t="n"/>
+      <c r="K153" s="699" t="n"/>
+      <c r="L153" s="700" t="n"/>
+      <c r="M153" s="701" t="n"/>
+      <c r="N153" s="702" t="n"/>
+      <c r="O153" s="703" t="n"/>
+      <c r="P153" s="704" t="n"/>
+      <c r="Q153" s="705" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="R153" s="706" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="S153" s="707" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="T153" s="708" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="U153" s="709" t="n"/>
+      <c r="V153" s="710" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="721" t="n"/>
+      <c r="C154" s="722" t="n"/>
+      <c r="D154" s="723" t="n"/>
+      <c r="E154" s="724" t="n"/>
+      <c r="F154" s="725" t="n"/>
+      <c r="G154" s="831" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H154" s="832" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="I154" s="728" t="n"/>
+      <c r="J154" s="729" t="n"/>
+      <c r="K154" s="730" t="n"/>
+      <c r="L154" s="731" t="n"/>
+      <c r="M154" s="811" t="n"/>
+      <c r="N154" s="812" t="n"/>
+      <c r="O154" s="734" t="n"/>
+      <c r="P154" s="735" t="n"/>
+      <c r="Q154" s="736" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R154" s="737" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="S154" s="738" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="T154" s="739" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="U154" s="740" t="n"/>
+      <c r="V154" s="741" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C155" s="743" t="n">
+        <v>10</v>
+      </c>
+      <c r="D155" s="744" t="n"/>
+      <c r="E155" s="745" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F155" s="746" t="n"/>
+      <c r="G155" s="747" t="n">
+        <v>15071.71</v>
+      </c>
+      <c r="H155" s="748" t="n"/>
+      <c r="I155" s="749" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="J155" s="750" t="n"/>
+      <c r="K155" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="752" t="n"/>
+      <c r="M155" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" s="754" t="n"/>
+      <c r="O155" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="756" t="n"/>
+      <c r="Q155" s="757" t="n">
+        <v>200</v>
+      </c>
+      <c r="R155" s="758" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="S155" s="759" t="n">
+        <v>200</v>
+      </c>
+      <c r="T155" s="760" t="n">
+        <v>294.2</v>
+      </c>
+      <c r="U155" s="761" t="n">
+        <v>15520.71</v>
+      </c>
+      <c r="V155" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C156" s="764" t="n"/>
+      <c r="D156" s="765" t="n"/>
+      <c r="E156" s="766" t="n"/>
+      <c r="F156" s="767" t="n"/>
+      <c r="G156" s="768" t="n"/>
+      <c r="H156" s="769" t="n"/>
+      <c r="I156" s="770" t="n"/>
+      <c r="J156" s="771" t="n"/>
+      <c r="K156" s="772" t="n"/>
+      <c r="L156" s="773" t="n"/>
+      <c r="M156" s="774" t="n"/>
+      <c r="N156" s="775" t="n"/>
+      <c r="O156" s="776" t="n"/>
+      <c r="P156" s="777" t="n"/>
+      <c r="Q156" s="778" t="n">
+        <v>200</v>
+      </c>
+      <c r="R156" s="779" t="n">
+        <v>2551.94</v>
+      </c>
+      <c r="S156" s="780" t="n">
+        <v>2200</v>
+      </c>
+      <c r="T156" s="781" t="n">
+        <v>4237.49</v>
+      </c>
+      <c r="U156" s="782" t="n"/>
+      <c r="V156" s="783" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="669" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="670" t="n"/>
+      <c r="D157" s="671" t="n"/>
+      <c r="E157" s="672" t="n"/>
+      <c r="F157" s="673" t="n"/>
+      <c r="G157" s="674" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H157" s="675" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I157" s="676" t="n"/>
+      <c r="J157" s="677" t="n"/>
+      <c r="K157" s="805" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L157" s="806" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M157" s="807" t="n"/>
+      <c r="N157" s="808" t="n"/>
+      <c r="O157" s="682" t="n"/>
+      <c r="P157" s="683" t="n"/>
+      <c r="Q157" s="684" t="n"/>
+      <c r="R157" s="685" t="n"/>
+      <c r="S157" s="686" t="n"/>
+      <c r="T157" s="687" t="n"/>
+      <c r="U157" s="688" t="n"/>
+      <c r="V157" s="689" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="690" t="n"/>
+      <c r="C158" s="691" t="n"/>
+      <c r="D158" s="692" t="n"/>
+      <c r="E158" s="693" t="n"/>
+      <c r="F158" s="694" t="n"/>
+      <c r="G158" s="695" t="n"/>
+      <c r="H158" s="696" t="n"/>
+      <c r="I158" s="713" t="n"/>
+      <c r="J158" s="714" t="n"/>
+      <c r="K158" s="715" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="L158" s="716" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M158" s="701" t="n"/>
+      <c r="N158" s="702" t="n"/>
+      <c r="O158" s="703" t="n"/>
+      <c r="P158" s="704" t="n"/>
+      <c r="Q158" s="705" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="R158" s="706" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="S158" s="707" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="T158" s="708" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="U158" s="709" t="n"/>
+      <c r="V158" s="710" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="690" t="n"/>
+      <c r="C159" s="691" t="n"/>
+      <c r="D159" s="692" t="n"/>
+      <c r="E159" s="693" t="n"/>
+      <c r="F159" s="694" t="n"/>
+      <c r="G159" s="695" t="n"/>
+      <c r="H159" s="696" t="n"/>
+      <c r="I159" s="697" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J159" s="698" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="K159" s="699" t="n"/>
+      <c r="L159" s="700" t="n"/>
+      <c r="M159" s="701" t="n"/>
+      <c r="N159" s="702" t="n"/>
+      <c r="O159" s="703" t="n"/>
+      <c r="P159" s="704" t="n"/>
+      <c r="Q159" s="705" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R159" s="706" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="S159" s="707" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T159" s="708" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="U159" s="709" t="n"/>
+      <c r="V159" s="710" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="690" t="n"/>
+      <c r="C160" s="691" t="n"/>
+      <c r="D160" s="692" t="n"/>
+      <c r="E160" s="693" t="n"/>
+      <c r="F160" s="694" t="n"/>
+      <c r="G160" s="695" t="n"/>
+      <c r="H160" s="696" t="n"/>
+      <c r="I160" s="697" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J160" s="698" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="K160" s="699" t="n"/>
+      <c r="L160" s="700" t="n"/>
+      <c r="M160" s="701" t="n"/>
+      <c r="N160" s="702" t="n"/>
+      <c r="O160" s="703" t="n"/>
+      <c r="P160" s="704" t="n"/>
+      <c r="Q160" s="705" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R160" s="706" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="S160" s="707" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T160" s="708" t="inlineStr">
+        <is>
+          <t>14.6</t>
+        </is>
+      </c>
+      <c r="U160" s="709" t="n"/>
+      <c r="V160" s="710" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="690" t="n"/>
+      <c r="C161" s="691" t="n"/>
+      <c r="D161" s="692" t="n"/>
+      <c r="E161" s="693" t="n"/>
+      <c r="F161" s="694" t="n"/>
+      <c r="G161" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H161" s="712" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I161" s="713" t="n"/>
+      <c r="J161" s="714" t="n"/>
+      <c r="K161" s="715" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L161" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M161" s="701" t="n"/>
+      <c r="N161" s="702" t="n"/>
+      <c r="O161" s="703" t="n"/>
+      <c r="P161" s="704" t="n"/>
+      <c r="Q161" s="717" t="n"/>
+      <c r="R161" s="718" t="n"/>
+      <c r="S161" s="719" t="n"/>
+      <c r="T161" s="720" t="n"/>
+      <c r="U161" s="709" t="n"/>
+      <c r="V161" s="710" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="690" t="n"/>
+      <c r="C162" s="691" t="n"/>
+      <c r="D162" s="692" t="n"/>
+      <c r="E162" s="693" t="n"/>
+      <c r="F162" s="694" t="n"/>
+      <c r="G162" s="695" t="n"/>
+      <c r="H162" s="696" t="n"/>
+      <c r="I162" s="713" t="n"/>
+      <c r="J162" s="714" t="n"/>
+      <c r="K162" s="715" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="L162" s="716" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M162" s="701" t="n"/>
+      <c r="N162" s="702" t="n"/>
+      <c r="O162" s="703" t="n"/>
+      <c r="P162" s="704" t="n"/>
+      <c r="Q162" s="705" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="R162" s="706" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S162" s="707" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+      <c r="T162" s="708" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="U162" s="709" t="n"/>
+      <c r="V162" s="710" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="721" t="n"/>
+      <c r="C163" s="722" t="n"/>
+      <c r="D163" s="723" t="n"/>
+      <c r="E163" s="724" t="n"/>
+      <c r="F163" s="725" t="n"/>
+      <c r="G163" s="726" t="n"/>
+      <c r="H163" s="727" t="n"/>
+      <c r="I163" s="813" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J163" s="814" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="K163" s="730" t="n"/>
+      <c r="L163" s="731" t="n"/>
+      <c r="M163" s="811" t="n"/>
+      <c r="N163" s="812" t="n"/>
+      <c r="O163" s="734" t="n"/>
+      <c r="P163" s="735" t="n"/>
+      <c r="Q163" s="736" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R163" s="737" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="S163" s="738" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T163" s="739" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="U163" s="740" t="n"/>
+      <c r="V163" s="741" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C164" s="743" t="n">
+        <v>10</v>
+      </c>
+      <c r="D164" s="744" t="n"/>
+      <c r="E164" s="745" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F164" s="746" t="n"/>
+      <c r="G164" s="747" t="n">
+        <v>14805.71</v>
+      </c>
+      <c r="H164" s="748" t="n"/>
+      <c r="I164" s="749" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="J164" s="750" t="n"/>
+      <c r="K164" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" s="752" t="n"/>
+      <c r="M164" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" s="754" t="n"/>
+      <c r="O164" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" s="756" t="n"/>
+      <c r="Q164" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" s="758" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="S164" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" s="760" t="n">
+        <v>290.1</v>
+      </c>
+      <c r="U164" s="761" t="n">
+        <v>15230.61</v>
+      </c>
+      <c r="V164" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C165" s="764" t="n"/>
+      <c r="D165" s="765" t="n"/>
+      <c r="E165" s="766" t="n"/>
+      <c r="F165" s="767" t="n"/>
+      <c r="G165" s="768" t="n"/>
+      <c r="H165" s="769" t="n"/>
+      <c r="I165" s="770" t="n"/>
+      <c r="J165" s="771" t="n"/>
+      <c r="K165" s="772" t="n"/>
+      <c r="L165" s="773" t="n"/>
+      <c r="M165" s="774" t="n"/>
+      <c r="N165" s="775" t="n"/>
+      <c r="O165" s="776" t="n"/>
+      <c r="P165" s="777" t="n"/>
+      <c r="Q165" s="778" t="n">
+        <v>200</v>
+      </c>
+      <c r="R165" s="779" t="n">
+        <v>2842.04</v>
+      </c>
+      <c r="S165" s="780" t="n">
+        <v>2200</v>
+      </c>
+      <c r="T165" s="781" t="n">
+        <v>4527.59</v>
+      </c>
+      <c r="U165" s="782" t="n"/>
+      <c r="V165" s="783" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="784" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C166" s="785" t="n">
+        <v>10</v>
+      </c>
+      <c r="D166" s="786" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E166" s="787" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F166" s="788" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G166" s="789" t="n">
+        <v>14805.71</v>
+      </c>
+      <c r="H166" s="790" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I166" s="791" t="n">
+        <v>205.1</v>
+      </c>
+      <c r="J166" s="792" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K166" s="793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" s="794" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M166" s="795" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" s="796" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O166" s="797" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" s="798" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q166" s="799" t="n"/>
+      <c r="R166" s="800" t="n"/>
+      <c r="S166" s="801" t="n"/>
+      <c r="T166" s="802" t="n"/>
+      <c r="U166" s="803" t="n">
+        <v>15230.61</v>
+      </c>
+      <c r="V166" s="804" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="669" t="inlineStr">
+        <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="670" t="n"/>
+      <c r="D167" s="671" t="n"/>
+      <c r="E167" s="672" t="n"/>
+      <c r="F167" s="673" t="n"/>
+      <c r="G167" s="674" t="inlineStr">
+        <is>
+          <t>Turnitin</t>
+        </is>
+      </c>
+      <c r="H167" s="675" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I167" s="676" t="n"/>
+      <c r="J167" s="677" t="n"/>
+      <c r="K167" s="678" t="n"/>
+      <c r="L167" s="679" t="n"/>
+      <c r="M167" s="807" t="n"/>
+      <c r="N167" s="808" t="n"/>
+      <c r="O167" s="682" t="n"/>
+      <c r="P167" s="683" t="n"/>
+      <c r="Q167" s="821" t="inlineStr">
+        <is>
+          <t>Turnitin</t>
+        </is>
+      </c>
+      <c r="R167" s="822" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="S167" s="815" t="inlineStr">
+        <is>
+          <t>Turnitin</t>
+        </is>
+      </c>
+      <c r="T167" s="816" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="U167" s="688" t="n"/>
+      <c r="V167" s="689" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="690" t="n"/>
+      <c r="C168" s="691" t="n"/>
+      <c r="D168" s="692" t="n"/>
+      <c r="E168" s="693" t="n"/>
+      <c r="F168" s="694" t="n"/>
+      <c r="G168" s="695" t="n"/>
+      <c r="H168" s="696" t="n"/>
+      <c r="I168" s="697" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J168" s="698" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="K168" s="699" t="n"/>
+      <c r="L168" s="700" t="n"/>
+      <c r="M168" s="701" t="n"/>
+      <c r="N168" s="702" t="n"/>
+      <c r="O168" s="703" t="n"/>
+      <c r="P168" s="704" t="n"/>
+      <c r="Q168" s="705" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R168" s="706" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="S168" s="707" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T168" s="708" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="U168" s="709" t="n"/>
+      <c r="V168" s="710" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="690" t="n"/>
+      <c r="C169" s="691" t="n"/>
+      <c r="D169" s="692" t="n"/>
+      <c r="E169" s="693" t="n"/>
+      <c r="F169" s="694" t="n"/>
+      <c r="G169" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H169" s="712" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I169" s="713" t="n"/>
+      <c r="J169" s="714" t="n"/>
+      <c r="K169" s="715" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="L169" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M169" s="701" t="n"/>
+      <c r="N169" s="702" t="n"/>
+      <c r="O169" s="703" t="n"/>
+      <c r="P169" s="704" t="n"/>
+      <c r="Q169" s="717" t="n"/>
+      <c r="R169" s="718" t="n"/>
+      <c r="S169" s="719" t="n"/>
+      <c r="T169" s="720" t="n"/>
+      <c r="U169" s="709" t="n"/>
+      <c r="V169" s="710" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="690" t="n"/>
+      <c r="C170" s="691" t="n"/>
+      <c r="D170" s="692" t="n"/>
+      <c r="E170" s="693" t="n"/>
+      <c r="F170" s="694" t="n"/>
+      <c r="G170" s="695" t="n"/>
+      <c r="H170" s="696" t="n"/>
+      <c r="I170" s="713" t="n"/>
+      <c r="J170" s="714" t="n"/>
+      <c r="K170" s="715" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="L170" s="716" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="M170" s="701" t="n"/>
+      <c r="N170" s="702" t="n"/>
+      <c r="O170" s="703" t="n"/>
+      <c r="P170" s="704" t="n"/>
+      <c r="Q170" s="705" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="R170" s="706" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="S170" s="707" t="inlineStr">
+        <is>
+          <t>Heal care</t>
+        </is>
+      </c>
+      <c r="T170" s="708" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="U170" s="709" t="n"/>
+      <c r="V170" s="710" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="690" t="n"/>
+      <c r="C171" s="691" t="n"/>
+      <c r="D171" s="692" t="n"/>
+      <c r="E171" s="693" t="n"/>
+      <c r="F171" s="694" t="n"/>
+      <c r="G171" s="711" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H171" s="712" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I171" s="713" t="n"/>
+      <c r="J171" s="714" t="n"/>
+      <c r="K171" s="715" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L171" s="716" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M171" s="701" t="n"/>
+      <c r="N171" s="702" t="n"/>
+      <c r="O171" s="703" t="n"/>
+      <c r="P171" s="704" t="n"/>
+      <c r="Q171" s="717" t="n"/>
+      <c r="R171" s="718" t="n"/>
+      <c r="S171" s="719" t="n"/>
+      <c r="T171" s="720" t="n"/>
+      <c r="U171" s="709" t="n"/>
+      <c r="V171" s="710" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="721" t="n"/>
+      <c r="C172" s="722" t="n"/>
+      <c r="D172" s="723" t="n"/>
+      <c r="E172" s="724" t="n"/>
+      <c r="F172" s="725" t="n"/>
+      <c r="G172" s="726" t="n"/>
+      <c r="H172" s="727" t="n"/>
+      <c r="I172" s="728" t="n"/>
+      <c r="J172" s="729" t="n"/>
+      <c r="K172" s="809" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="L172" s="810" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="M172" s="811" t="n"/>
+      <c r="N172" s="812" t="n"/>
+      <c r="O172" s="734" t="n"/>
+      <c r="P172" s="735" t="n"/>
+      <c r="Q172" s="736" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="R172" s="737" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="S172" s="738" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="T172" s="739" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="U172" s="740" t="n"/>
+      <c r="V172" s="741" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="742" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C173" s="743" t="n">
+        <v>10</v>
+      </c>
+      <c r="D173" s="744" t="n"/>
+      <c r="E173" s="745" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F173" s="746" t="n"/>
+      <c r="G173" s="747" t="n">
+        <v>14439.71</v>
+      </c>
+      <c r="H173" s="748" t="n"/>
+      <c r="I173" s="749" t="n">
+        <v>201.3</v>
+      </c>
+      <c r="J173" s="750" t="n"/>
+      <c r="K173" s="751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" s="752" t="n"/>
+      <c r="M173" s="753" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" s="754" t="n"/>
+      <c r="O173" s="755" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" s="756" t="n"/>
+      <c r="Q173" s="757" t="n">
+        <v>0</v>
+      </c>
+      <c r="R173" s="758" t="n">
+        <v>369.8</v>
+      </c>
+      <c r="S173" s="759" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" s="760" t="n">
+        <v>369.8</v>
+      </c>
+      <c r="U173" s="761" t="n">
+        <v>14860.81</v>
+      </c>
+      <c r="V173" s="762" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="763" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C174" s="764" t="n"/>
+      <c r="D174" s="765" t="n"/>
+      <c r="E174" s="766" t="n"/>
+      <c r="F174" s="767" t="n"/>
+      <c r="G174" s="768" t="n"/>
+      <c r="H174" s="769" t="n"/>
+      <c r="I174" s="770" t="n"/>
+      <c r="J174" s="771" t="n"/>
+      <c r="K174" s="772" t="n"/>
+      <c r="L174" s="773" t="n"/>
+      <c r="M174" s="774" t="n"/>
+      <c r="N174" s="775" t="n"/>
+      <c r="O174" s="776" t="n"/>
+      <c r="P174" s="777" t="n"/>
+      <c r="Q174" s="778" t="n">
+        <v>200</v>
+      </c>
+      <c r="R174" s="779" t="n">
+        <v>3211.84</v>
+      </c>
+      <c r="S174" s="780" t="n">
+        <v>2200</v>
+      </c>
+      <c r="T174" s="781" t="n">
+        <v>4897.39</v>
+      </c>
+      <c r="U174" s="782" t="n"/>
+      <c r="V174" s="783" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="784" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C175" s="785" t="n">
+        <v>10</v>
+      </c>
+      <c r="D175" s="786" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E175" s="787" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="F175" s="788" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G175" s="789" t="n">
+        <v>14439.71</v>
+      </c>
+      <c r="H175" s="790" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I175" s="791" t="n">
+        <v>201.3</v>
+      </c>
+      <c r="J175" s="792" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K175" s="793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" s="794" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M175" s="795" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" s="796" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O175" s="797" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" s="798" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q175" s="799" t="n"/>
+      <c r="R175" s="800" t="n"/>
+      <c r="S175" s="801" t="n"/>
+      <c r="T175" s="802" t="n"/>
+      <c r="U175" s="803" t="n">
+        <v>14860.81</v>
+      </c>
+      <c r="V175" s="804" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="O2:P2"/>

--- a/output/2026/money/money.xlsx
+++ b/output/2026/money/money.xlsx
@@ -3,11 +3,12 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="total" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Jun" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Jul" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -61,7 +62,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="83">
+  <fills count="93">
     <fill>
       <patternFill/>
     </fill>
@@ -436,6 +437,56 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EBF1DE"/>
       </patternFill>
     </fill>
@@ -485,7 +536,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="199">
+  <borders count="223">
     <border>
       <left/>
       <right/>
@@ -524,6 +575,2884 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dotted">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="medium">
         <color auto="1"/>
@@ -539,2524 +3468,6 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dotted">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="dashed">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="dashed">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dashed">
-        <color auto="1"/>
-      </left>
-      <right style="dashed">
-        <color auto="1"/>
-      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -3234,7 +3645,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1107">
+  <cellXfs count="1276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3246,1192 +3657,1194 @@
     <xf numFmtId="49" fontId="4" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="22" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="22" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="22" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="22" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="22" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="22" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="9" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="22" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="22" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="22" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="22" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="22" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="22" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="7" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="8" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="9" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="22" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="22" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="10" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="10" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="41" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="43" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="55" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="56" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="57" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="58" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="62" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="61" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="68" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="67" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="72" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="74" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="73" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="71" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="76" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="78" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="75" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="77" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="79" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="81" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="82" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="83" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="38" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="39" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="90" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="87" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="35" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="37" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="38" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="40" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="92" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="41" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="89" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="40" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="41" borderId="94" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="41" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="36" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="37" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="38" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="38" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="39" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="39" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="93" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="42" borderId="91" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="36" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="37" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="38" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="39" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="40" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="96" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="41" borderId="98" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="41" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="42" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="41" borderId="97" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="42" borderId="95" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="52" borderId="99" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="52" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="52" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="52" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="52" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="48" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="112" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="52" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="44" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="48" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="49" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="114" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="43" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="44" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="45" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="48" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="49" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="50" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="51" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="52" borderId="113" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="48" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="49" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="50" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="51" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="51" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="52" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="103" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="52" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="46" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="101" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="100" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="51" borderId="102" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="110" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="111" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="43" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="44" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="44" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="45" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="47" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="48" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="48" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="49" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="49" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="50" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="108" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="109" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="43" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="44" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="45" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="48" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="48" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="50" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="51" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="51" borderId="122" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="51" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="51" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="52" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="106" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="46" borderId="107" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="121" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="47" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="104" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="46" borderId="105" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="61" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="123" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="61" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="62" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="61" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="62" borderId="129" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="131" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="59" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="62" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="59" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="62" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="58" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="59" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="59" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="61" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="62" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="57" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="58" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="61" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="56" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="60" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="53" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="54" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="60" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="61" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="62" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="53" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="54" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="59" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="139" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="62" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="54" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="56" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="57" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="59" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="143" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="62" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="53" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="53" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="54" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="54" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="58" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="59" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="59" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="146" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="62" borderId="145" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="57" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="58" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="61" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="55" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="56" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="126" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="60" borderId="127" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="53" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="53" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="54" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="54" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="60" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="61" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="61" borderId="136" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="134" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="55" borderId="135" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="60" borderId="130" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="132" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="55" borderId="133" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="60" borderId="128" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="148" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="71" borderId="150" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="147" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="71" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="72" borderId="149" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="71" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="151" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="65" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="65" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="67" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="67" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="71" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="72" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="65" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="65" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="67" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="67" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="64" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="65" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="67" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="68" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="69" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="72" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="63" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="64" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="65" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="67" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="69" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="70" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="72" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="152" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="153" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="64" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="64" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="66" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="71" borderId="156" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="72" borderId="157" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="64" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="65" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="67" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="68" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="69" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="162" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="164" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="163" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="72" borderId="161" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="63" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="64" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="65" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="67" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="68" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="69" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="70" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="166" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="72" borderId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="154" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="155" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="64" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="64" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="66" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="159" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="71" borderId="158" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="160" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="63" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="64" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="64" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="65" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="65" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="66" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="67" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="67" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="68" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="68" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="69" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="69" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="70" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="63" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="64" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="64" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="65" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="65" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="66" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="67" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="67" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="68" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="68" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="69" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="69" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="70" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="71" borderId="168" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="71" borderId="170" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="71" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="71" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="72" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="22" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="169" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="71" borderId="169" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="72" borderId="167" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="80" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="80" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="174" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="82" borderId="171" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="73" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="73" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="74" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="74" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="77" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="77" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="82" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="75" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="75" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="80" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="80" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="76" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="76" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="77" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="77" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="78" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="78" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="79" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="79" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="80" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="80" borderId="177" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="81" borderId="176" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="81" borderId="178" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="82" borderId="175" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="73" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="73" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="74" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="74" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="75" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="75" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="76" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="76" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="77" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4440,106 +4853,291 @@
     <xf numFmtId="0" fontId="0" fillId="78" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="79" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="79" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="80" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="80" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="82" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="75" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="75" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="182" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="76" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="76" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="77" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="77" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="73" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="82" borderId="179" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="73" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="73" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="74" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="74" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="74" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="75" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="75" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="76" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="76" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="77" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="77" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="78" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="78" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="78" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="79" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="79" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="79" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="184" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="186" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="82" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="185" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="82" borderId="183" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="73" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="73" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="74" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="74" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="75" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="75" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="76" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="76" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="77" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="77" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="78" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="78" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="79" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="79" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="188" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="190" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="81" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="82" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="189" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="82" borderId="187" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="73" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="73" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="74" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="74" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="75" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="75" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="76" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="76" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="77" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="77" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="78" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="78" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="79" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="79" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="73" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="73" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="74" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="74" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="77" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="77" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="78" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="78" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="79" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="79" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="81" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="82" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="80" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="192" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="194" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="82" borderId="191" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="73" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="73" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="74" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="74" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="75" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="75" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="76" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="76" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="77" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="77" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="78" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="78" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="79" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="79" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="80" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="80" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="81" borderId="198" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="81" borderId="197" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="82" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="73" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="74" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="75" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="78" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="193" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="76" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="172" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="80" borderId="173" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="180" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="77" borderId="181" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="196" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="195" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="22" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="81" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="79" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="78" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="80" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="73" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="75" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="74" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="77" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="76" borderId="191" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="201" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="200" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="202" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="199" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="203" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="86" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="86" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="205" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="204" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="206" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="207" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="208" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="210" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="209" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="207" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="211" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="83" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="84" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="86" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="88" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="212" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="214" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="213" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="92" borderId="211" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="83" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="84" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="85" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="86" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="87" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="88" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="89" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="90" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="216" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="218" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="217" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="92" borderId="215" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="219" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="83" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="83" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="84" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="84" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="85" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="86" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="86" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="87" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="88" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="88" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="89" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="90" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="220" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="91" borderId="222" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="91" borderId="221" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="92" borderId="219" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -4922,13 +5520,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:V224"/>
+  <dimension ref="B2:V224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75" outlineLevelCol="0"/>
   <cols>
     <col width="9" customWidth="1" style="2" min="1" max="1"/>
     <col width="13.125" customWidth="1" style="2" min="2" max="2"/>
-    <col width="9" customWidth="1" style="2" min="3" max="9"/>
-    <col width="9" customWidth="1" style="2" min="10" max="16384"/>
+    <col width="9" customWidth="1" style="2" min="3" max="12"/>
+    <col width="9" customWidth="1" style="2" min="13" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" thickBot="1"/>
@@ -4938,61 +5536,61 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="C2" s="966" t="inlineStr">
+      <c r="C2" s="1124" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="D2" s="962" t="n"/>
-      <c r="E2" s="968" t="inlineStr">
+      <c r="D2" s="1120" t="n"/>
+      <c r="E2" s="1126" t="inlineStr">
         <is>
           <t>Coin-hold</t>
         </is>
       </c>
-      <c r="F2" s="962" t="n"/>
-      <c r="G2" s="967" t="inlineStr">
+      <c r="F2" s="1120" t="n"/>
+      <c r="G2" s="1125" t="inlineStr">
         <is>
           <t>HSBC</t>
         </is>
       </c>
-      <c r="H2" s="962" t="n"/>
-      <c r="I2" s="970" t="inlineStr">
+      <c r="H2" s="1120" t="n"/>
+      <c r="I2" s="1128" t="inlineStr">
         <is>
           <t>Octopus</t>
         </is>
       </c>
-      <c r="J2" s="962" t="n"/>
-      <c r="K2" s="969" t="inlineStr">
+      <c r="J2" s="1120" t="n"/>
+      <c r="K2" s="1127" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="L2" s="962" t="n"/>
-      <c r="M2" s="964" t="inlineStr">
+      <c r="L2" s="1120" t="n"/>
+      <c r="M2" s="1122" t="inlineStr">
         <is>
           <t>Tap and Go</t>
         </is>
       </c>
-      <c r="N2" s="962" t="n"/>
-      <c r="O2" s="963" t="inlineStr">
+      <c r="N2" s="1120" t="n"/>
+      <c r="O2" s="1121" t="inlineStr">
         <is>
           <t>Payme</t>
         </is>
       </c>
-      <c r="P2" s="962" t="n"/>
-      <c r="Q2" s="965" t="inlineStr">
+      <c r="P2" s="1120" t="n"/>
+      <c r="Q2" s="1123" t="inlineStr">
         <is>
           <t>Countable Total</t>
         </is>
       </c>
-      <c r="R2" s="962" t="n"/>
-      <c r="S2" s="960" t="inlineStr">
+      <c r="R2" s="1120" t="n"/>
+      <c r="S2" s="1118" t="inlineStr">
         <is>
           <t>Real Total</t>
         </is>
       </c>
-      <c r="T2" s="961" t="n"/>
-      <c r="U2" s="962" t="n"/>
+      <c r="T2" s="1119" t="n"/>
+      <c r="U2" s="1120" t="n"/>
       <c r="V2" s="4" t="inlineStr">
         <is>
           <t>Correct</t>
@@ -14950,436 +15548,436 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="B216" s="971" t="inlineStr">
+    <row r="216" ht="16.5" customHeight="1">
+      <c r="B216" s="960" t="inlineStr">
         <is>
           <t>30/06/2026</t>
         </is>
       </c>
-      <c r="C216" s="972" t="n"/>
-      <c r="D216" s="973" t="n"/>
-      <c r="E216" s="974" t="n"/>
-      <c r="F216" s="975" t="n"/>
-      <c r="G216" s="976" t="n"/>
-      <c r="H216" s="977" t="n"/>
-      <c r="I216" s="978" t="inlineStr">
+      <c r="C216" s="961" t="n"/>
+      <c r="D216" s="962" t="n"/>
+      <c r="E216" s="963" t="n"/>
+      <c r="F216" s="964" t="n"/>
+      <c r="G216" s="965" t="n"/>
+      <c r="H216" s="966" t="n"/>
+      <c r="I216" s="967" t="inlineStr">
         <is>
           <t>LRT</t>
         </is>
       </c>
-      <c r="J216" s="979" t="inlineStr">
+      <c r="J216" s="968" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K216" s="980" t="n"/>
-      <c r="L216" s="981" t="n"/>
-      <c r="M216" s="982" t="n"/>
-      <c r="N216" s="983" t="n"/>
-      <c r="O216" s="984" t="n"/>
-      <c r="P216" s="985" t="n"/>
-      <c r="Q216" s="986" t="inlineStr">
+      <c r="K216" s="969" t="n"/>
+      <c r="L216" s="970" t="n"/>
+      <c r="M216" s="971" t="n"/>
+      <c r="N216" s="972" t="n"/>
+      <c r="O216" s="973" t="n"/>
+      <c r="P216" s="974" t="n"/>
+      <c r="Q216" s="975" t="inlineStr">
         <is>
           <t>LRT</t>
         </is>
       </c>
-      <c r="R216" s="987" t="inlineStr">
+      <c r="R216" s="976" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="S216" s="988" t="inlineStr">
+      <c r="S216" s="977" t="inlineStr">
         <is>
           <t>LRT</t>
         </is>
       </c>
-      <c r="T216" s="989" t="inlineStr">
+      <c r="T216" s="978" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="U216" s="990" t="n"/>
-      <c r="V216" s="991" t="n"/>
-    </row>
-    <row r="217">
-      <c r="B217" s="992" t="n"/>
-      <c r="C217" s="993" t="n"/>
-      <c r="D217" s="994" t="n"/>
-      <c r="E217" s="995" t="n"/>
-      <c r="F217" s="996" t="n"/>
-      <c r="G217" s="997" t="inlineStr">
+      <c r="U216" s="979" t="n"/>
+      <c r="V216" s="980" t="n"/>
+    </row>
+    <row r="217" ht="16.5" customHeight="1">
+      <c r="B217" s="981" t="n"/>
+      <c r="C217" s="982" t="n"/>
+      <c r="D217" s="983" t="n"/>
+      <c r="E217" s="984" t="n"/>
+      <c r="F217" s="985" t="n"/>
+      <c r="G217" s="986" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="H217" s="998" t="inlineStr">
+      <c r="H217" s="987" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="I217" s="999" t="n"/>
-      <c r="J217" s="1000" t="n"/>
-      <c r="K217" s="1001" t="inlineStr">
+      <c r="I217" s="988" t="n"/>
+      <c r="J217" s="989" t="n"/>
+      <c r="K217" s="990" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="L217" s="1002" t="inlineStr">
+      <c r="L217" s="991" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="M217" s="1003" t="n"/>
-      <c r="N217" s="1004" t="n"/>
-      <c r="O217" s="1005" t="n"/>
-      <c r="P217" s="1006" t="n"/>
-      <c r="Q217" s="1007" t="n"/>
-      <c r="R217" s="1008" t="n"/>
-      <c r="S217" s="1009" t="n"/>
-      <c r="T217" s="1010" t="n"/>
-      <c r="U217" s="1011" t="n"/>
-      <c r="V217" s="1012" t="n"/>
-    </row>
-    <row r="218">
-      <c r="B218" s="992" t="n"/>
-      <c r="C218" s="993" t="n"/>
-      <c r="D218" s="994" t="n"/>
-      <c r="E218" s="995" t="n"/>
-      <c r="F218" s="996" t="n"/>
-      <c r="G218" s="1013" t="n"/>
-      <c r="H218" s="1014" t="n"/>
-      <c r="I218" s="999" t="n"/>
-      <c r="J218" s="1000" t="n"/>
-      <c r="K218" s="1001" t="inlineStr">
+      <c r="M217" s="992" t="n"/>
+      <c r="N217" s="993" t="n"/>
+      <c r="O217" s="994" t="n"/>
+      <c r="P217" s="995" t="n"/>
+      <c r="Q217" s="996" t="n"/>
+      <c r="R217" s="997" t="n"/>
+      <c r="S217" s="998" t="n"/>
+      <c r="T217" s="999" t="n"/>
+      <c r="U217" s="1000" t="n"/>
+      <c r="V217" s="1001" t="n"/>
+    </row>
+    <row r="218" ht="16.5" customHeight="1">
+      <c r="B218" s="981" t="n"/>
+      <c r="C218" s="982" t="n"/>
+      <c r="D218" s="983" t="n"/>
+      <c r="E218" s="984" t="n"/>
+      <c r="F218" s="985" t="n"/>
+      <c r="G218" s="1002" t="n"/>
+      <c r="H218" s="1003" t="n"/>
+      <c r="I218" s="988" t="n"/>
+      <c r="J218" s="989" t="n"/>
+      <c r="K218" s="990" t="inlineStr">
         <is>
           <t>heal care</t>
         </is>
       </c>
-      <c r="L218" s="1002" t="inlineStr">
+      <c r="L218" s="991" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="M218" s="1003" t="n"/>
-      <c r="N218" s="1004" t="n"/>
-      <c r="O218" s="1005" t="n"/>
-      <c r="P218" s="1006" t="n"/>
-      <c r="Q218" s="1015" t="inlineStr">
+      <c r="M218" s="992" t="n"/>
+      <c r="N218" s="993" t="n"/>
+      <c r="O218" s="994" t="n"/>
+      <c r="P218" s="995" t="n"/>
+      <c r="Q218" s="1004" t="inlineStr">
         <is>
           <t>heal care</t>
         </is>
       </c>
-      <c r="R218" s="1016" t="inlineStr">
+      <c r="R218" s="1005" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="S218" s="1017" t="inlineStr">
+      <c r="S218" s="1006" t="inlineStr">
         <is>
           <t>heal care</t>
         </is>
       </c>
-      <c r="T218" s="1018" t="inlineStr">
+      <c r="T218" s="1007" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="U218" s="1011" t="n"/>
-      <c r="V218" s="1012" t="n"/>
-    </row>
-    <row r="219">
-      <c r="B219" s="992" t="n"/>
-      <c r="C219" s="993" t="n"/>
-      <c r="D219" s="994" t="n"/>
-      <c r="E219" s="995" t="n"/>
-      <c r="F219" s="996" t="n"/>
-      <c r="G219" s="1013" t="n"/>
-      <c r="H219" s="1014" t="n"/>
-      <c r="I219" s="1019" t="inlineStr">
+      <c r="U218" s="1000" t="n"/>
+      <c r="V218" s="1001" t="n"/>
+    </row>
+    <row r="219" ht="16.5" customHeight="1">
+      <c r="B219" s="981" t="n"/>
+      <c r="C219" s="982" t="n"/>
+      <c r="D219" s="983" t="n"/>
+      <c r="E219" s="984" t="n"/>
+      <c r="F219" s="985" t="n"/>
+      <c r="G219" s="1002" t="n"/>
+      <c r="H219" s="1003" t="n"/>
+      <c r="I219" s="1008" t="inlineStr">
         <is>
           <t>LRT</t>
         </is>
       </c>
-      <c r="J219" s="1020" t="inlineStr">
+      <c r="J219" s="1009" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="K219" s="1021" t="n"/>
-      <c r="L219" s="1022" t="n"/>
-      <c r="M219" s="1003" t="n"/>
-      <c r="N219" s="1004" t="n"/>
-      <c r="O219" s="1005" t="n"/>
-      <c r="P219" s="1006" t="n"/>
-      <c r="Q219" s="1015" t="inlineStr">
+      <c r="K219" s="1010" t="n"/>
+      <c r="L219" s="1011" t="n"/>
+      <c r="M219" s="992" t="n"/>
+      <c r="N219" s="993" t="n"/>
+      <c r="O219" s="994" t="n"/>
+      <c r="P219" s="995" t="n"/>
+      <c r="Q219" s="1004" t="inlineStr">
         <is>
           <t>LRT</t>
         </is>
       </c>
-      <c r="R219" s="1016" t="inlineStr">
+      <c r="R219" s="1005" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="S219" s="1017" t="inlineStr">
+      <c r="S219" s="1006" t="inlineStr">
         <is>
           <t>LRT</t>
         </is>
       </c>
-      <c r="T219" s="1018" t="inlineStr">
+      <c r="T219" s="1007" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
       </c>
-      <c r="U219" s="1011" t="n"/>
-      <c r="V219" s="1012" t="n"/>
-    </row>
-    <row r="220">
-      <c r="B220" s="992" t="n"/>
-      <c r="C220" s="993" t="n"/>
-      <c r="D220" s="994" t="n"/>
-      <c r="E220" s="995" t="n"/>
-      <c r="F220" s="996" t="n"/>
-      <c r="G220" s="997" t="inlineStr">
+      <c r="U219" s="1000" t="n"/>
+      <c r="V219" s="1001" t="n"/>
+    </row>
+    <row r="220" ht="16.5" customHeight="1">
+      <c r="B220" s="981" t="n"/>
+      <c r="C220" s="982" t="n"/>
+      <c r="D220" s="983" t="n"/>
+      <c r="E220" s="984" t="n"/>
+      <c r="F220" s="985" t="n"/>
+      <c r="G220" s="986" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="H220" s="998" t="inlineStr">
+      <c r="H220" s="987" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="I220" s="999" t="n"/>
-      <c r="J220" s="1000" t="n"/>
-      <c r="K220" s="1001" t="inlineStr">
+      <c r="I220" s="988" t="n"/>
+      <c r="J220" s="989" t="n"/>
+      <c r="K220" s="990" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="L220" s="1002" t="inlineStr">
+      <c r="L220" s="991" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="M220" s="1003" t="n"/>
-      <c r="N220" s="1004" t="n"/>
-      <c r="O220" s="1005" t="n"/>
-      <c r="P220" s="1006" t="n"/>
-      <c r="Q220" s="1007" t="n"/>
-      <c r="R220" s="1008" t="n"/>
-      <c r="S220" s="1009" t="n"/>
-      <c r="T220" s="1010" t="n"/>
-      <c r="U220" s="1011" t="n"/>
-      <c r="V220" s="1012" t="n"/>
-    </row>
-    <row r="221">
-      <c r="B221" s="1023" t="n"/>
-      <c r="C221" s="1024" t="n"/>
-      <c r="D221" s="1025" t="n"/>
-      <c r="E221" s="1026" t="n"/>
-      <c r="F221" s="1027" t="n"/>
-      <c r="G221" s="1028" t="n"/>
-      <c r="H221" s="1029" t="n"/>
-      <c r="I221" s="1030" t="n"/>
-      <c r="J221" s="1031" t="n"/>
-      <c r="K221" s="1032" t="inlineStr">
+      <c r="M220" s="992" t="n"/>
+      <c r="N220" s="993" t="n"/>
+      <c r="O220" s="994" t="n"/>
+      <c r="P220" s="995" t="n"/>
+      <c r="Q220" s="996" t="n"/>
+      <c r="R220" s="997" t="n"/>
+      <c r="S220" s="998" t="n"/>
+      <c r="T220" s="999" t="n"/>
+      <c r="U220" s="1000" t="n"/>
+      <c r="V220" s="1001" t="n"/>
+    </row>
+    <row r="221" ht="16.5" customHeight="1">
+      <c r="B221" s="1012" t="n"/>
+      <c r="C221" s="1013" t="n"/>
+      <c r="D221" s="1014" t="n"/>
+      <c r="E221" s="1015" t="n"/>
+      <c r="F221" s="1016" t="n"/>
+      <c r="G221" s="1017" t="n"/>
+      <c r="H221" s="1018" t="n"/>
+      <c r="I221" s="1019" t="n"/>
+      <c r="J221" s="1020" t="n"/>
+      <c r="K221" s="1021" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="L221" s="1033" t="inlineStr">
+      <c r="L221" s="1022" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="M221" s="1034" t="n"/>
-      <c r="N221" s="1035" t="n"/>
-      <c r="O221" s="1036" t="n"/>
-      <c r="P221" s="1037" t="n"/>
-      <c r="Q221" s="1038" t="inlineStr">
+      <c r="M221" s="1023" t="n"/>
+      <c r="N221" s="1024" t="n"/>
+      <c r="O221" s="1025" t="n"/>
+      <c r="P221" s="1026" t="n"/>
+      <c r="Q221" s="1027" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="R221" s="1039" t="inlineStr">
+      <c r="R221" s="1028" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="S221" s="1040" t="inlineStr">
+      <c r="S221" s="1029" t="inlineStr">
         <is>
           <t>Lunch</t>
         </is>
       </c>
-      <c r="T221" s="1041" t="inlineStr">
+      <c r="T221" s="1030" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="U221" s="1042" t="n"/>
-      <c r="V221" s="1043" t="n"/>
-    </row>
-    <row r="222">
-      <c r="B222" s="1044" t="inlineStr">
+      <c r="U221" s="1031" t="n"/>
+      <c r="V221" s="1032" t="n"/>
+    </row>
+    <row r="222" ht="16.5" customHeight="1">
+      <c r="B222" s="1033" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="C222" s="1045" t="n">
+      <c r="C222" s="1034" t="n">
         <v>55</v>
       </c>
-      <c r="D222" s="1046" t="n"/>
-      <c r="E222" s="1047" t="n">
+      <c r="D222" s="1035" t="n"/>
+      <c r="E222" s="1036" t="n">
         <v>120.8</v>
       </c>
-      <c r="F222" s="1048" t="n"/>
-      <c r="G222" s="1049" t="n">
+      <c r="F222" s="1037" t="n"/>
+      <c r="G222" s="1038" t="n">
         <v>10836.63</v>
       </c>
-      <c r="H222" s="1050" t="n"/>
-      <c r="I222" s="1051" t="n">
+      <c r="H222" s="1039" t="n"/>
+      <c r="I222" s="1040" t="n">
         <v>108.4</v>
       </c>
-      <c r="J222" s="1052" t="n"/>
-      <c r="K222" s="1053" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" s="1054" t="n"/>
-      <c r="M222" s="1055" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" s="1056" t="n"/>
-      <c r="O222" s="1057" t="n">
-        <v>0</v>
-      </c>
-      <c r="P222" s="1058" t="n"/>
-      <c r="Q222" s="1059" t="n">
-        <v>0</v>
-      </c>
-      <c r="R222" s="1060" t="n">
+      <c r="J222" s="1041" t="n"/>
+      <c r="K222" s="1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" s="1043" t="n"/>
+      <c r="M222" s="1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" s="1045" t="n"/>
+      <c r="O222" s="1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" s="1047" t="n"/>
+      <c r="Q222" s="1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="R222" s="1049" t="n">
         <v>312.4</v>
       </c>
-      <c r="S222" s="1061" t="n">
-        <v>0</v>
-      </c>
-      <c r="T222" s="1062" t="n">
+      <c r="S222" s="1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" s="1051" t="n">
         <v>312.4</v>
       </c>
-      <c r="U222" s="1063" t="n">
+      <c r="U222" s="1052" t="n">
         <v>11120.83</v>
       </c>
-      <c r="V222" s="1064" t="inlineStr">
+      <c r="V222" s="1053" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="B223" s="1065" t="inlineStr">
+    <row r="223" ht="16.5" customHeight="1">
+      <c r="B223" s="1054" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="C223" s="1066" t="n"/>
-      <c r="D223" s="1067" t="n"/>
-      <c r="E223" s="1068" t="n"/>
-      <c r="F223" s="1069" t="n"/>
-      <c r="G223" s="1070" t="n"/>
-      <c r="H223" s="1071" t="n"/>
-      <c r="I223" s="1072" t="n"/>
-      <c r="J223" s="1073" t="n"/>
-      <c r="K223" s="1074" t="n"/>
-      <c r="L223" s="1075" t="n"/>
-      <c r="M223" s="1076" t="n"/>
-      <c r="N223" s="1077" t="n"/>
-      <c r="O223" s="1078" t="n"/>
-      <c r="P223" s="1079" t="n"/>
-      <c r="Q223" s="1080" t="n">
+      <c r="C223" s="1055" t="n"/>
+      <c r="D223" s="1056" t="n"/>
+      <c r="E223" s="1057" t="n"/>
+      <c r="F223" s="1058" t="n"/>
+      <c r="G223" s="1059" t="n"/>
+      <c r="H223" s="1060" t="n"/>
+      <c r="I223" s="1061" t="n"/>
+      <c r="J223" s="1062" t="n"/>
+      <c r="K223" s="1063" t="n"/>
+      <c r="L223" s="1064" t="n"/>
+      <c r="M223" s="1065" t="n"/>
+      <c r="N223" s="1066" t="n"/>
+      <c r="O223" s="1067" t="n"/>
+      <c r="P223" s="1068" t="n"/>
+      <c r="Q223" s="1069" t="n">
         <v>0.02</v>
       </c>
-      <c r="R223" s="1081" t="n">
+      <c r="R223" s="1070" t="n">
         <v>3920.34</v>
       </c>
-      <c r="S223" s="1082" t="n">
+      <c r="S223" s="1071" t="n">
         <v>2200.02</v>
       </c>
-      <c r="T223" s="1083" t="n">
+      <c r="T223" s="1072" t="n">
         <v>8637.389999999999</v>
       </c>
-      <c r="U223" s="1084" t="n"/>
-      <c r="V223" s="1085" t="n"/>
-    </row>
-    <row r="224">
-      <c r="B224" s="1086" t="inlineStr">
+      <c r="U223" s="1073" t="n"/>
+      <c r="V223" s="1074" t="n"/>
+    </row>
+    <row r="224" ht="16.5" customHeight="1">
+      <c r="B224" s="1075" t="inlineStr">
         <is>
           <t>current have</t>
         </is>
       </c>
-      <c r="C224" s="1087" t="n">
+      <c r="C224" s="1076" t="n">
         <v>55</v>
       </c>
-      <c r="D224" s="1088" t="inlineStr">
+      <c r="D224" s="1077" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E224" s="1089" t="n">
+      <c r="E224" s="1078" t="n">
         <v>120.8</v>
       </c>
-      <c r="F224" s="1090" t="inlineStr">
+      <c r="F224" s="1079" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="G224" s="1091" t="n">
+      <c r="G224" s="1080" t="n">
         <v>10836.63</v>
       </c>
-      <c r="H224" s="1092" t="inlineStr">
+      <c r="H224" s="1081" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="I224" s="1093" t="n">
+      <c r="I224" s="1082" t="n">
         <v>108.4</v>
       </c>
-      <c r="J224" s="1094" t="inlineStr">
+      <c r="J224" s="1083" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K224" s="1095" t="n">
-        <v>0</v>
-      </c>
-      <c r="L224" s="1096" t="inlineStr">
+      <c r="K224" s="1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="1085" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="M224" s="1097" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" s="1098" t="inlineStr">
+      <c r="M224" s="1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" s="1087" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="O224" s="1099" t="n">
-        <v>0</v>
-      </c>
-      <c r="P224" s="1100" t="inlineStr">
+      <c r="O224" s="1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" s="1089" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="Q224" s="1101" t="n"/>
-      <c r="R224" s="1102" t="n"/>
-      <c r="S224" s="1103" t="n"/>
-      <c r="T224" s="1104" t="n"/>
-      <c r="U224" s="1105" t="n">
+      <c r="Q224" s="1090" t="n"/>
+      <c r="R224" s="1091" t="n"/>
+      <c r="S224" s="1092" t="n"/>
+      <c r="T224" s="1093" t="n"/>
+      <c r="U224" s="1094" t="n">
         <v>11120.83</v>
       </c>
-      <c r="V224" s="1106" t="inlineStr">
+      <c r="V224" s="1095" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15400,4 +15998,1202 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="4294967293" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:V24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" outlineLevelCol="0"/>
+  <cols>
+    <col width="14.5" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1075" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C2" s="1133" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D2" s="1120" t="n"/>
+      <c r="E2" s="1135" t="inlineStr">
+        <is>
+          <t>Coin-hold</t>
+        </is>
+      </c>
+      <c r="F2" s="1120" t="n"/>
+      <c r="G2" s="1134" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="H2" s="1120" t="n"/>
+      <c r="I2" s="1137" t="inlineStr">
+        <is>
+          <t>Octopus</t>
+        </is>
+      </c>
+      <c r="J2" s="1120" t="n"/>
+      <c r="K2" s="1136" t="inlineStr">
+        <is>
+          <t>AliPay</t>
+        </is>
+      </c>
+      <c r="L2" s="1120" t="n"/>
+      <c r="M2" s="1131" t="inlineStr">
+        <is>
+          <t>Tap and Go</t>
+        </is>
+      </c>
+      <c r="N2" s="1120" t="n"/>
+      <c r="O2" s="1130" t="inlineStr">
+        <is>
+          <t>Payme</t>
+        </is>
+      </c>
+      <c r="P2" s="1120" t="n"/>
+      <c r="Q2" s="1132" t="inlineStr">
+        <is>
+          <t>Countable Total</t>
+        </is>
+      </c>
+      <c r="R2" s="1120" t="n"/>
+      <c r="S2" s="1129" t="inlineStr">
+        <is>
+          <t>Real Total</t>
+        </is>
+      </c>
+      <c r="T2" s="1119" t="n"/>
+      <c r="U2" s="1120" t="n"/>
+      <c r="V2" s="1095" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="1075" t="inlineStr">
+        <is>
+          <t>DD/MM/YY</t>
+        </is>
+      </c>
+      <c r="C3" s="1076" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D3" s="1077" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E3" s="1078" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F3" s="1079" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G3" s="1080" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H3" s="1081" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="I3" s="1082" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J3" s="1083" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K3" s="1084" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L3" s="1085" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" s="1086" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="N3" s="1087" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O3" s="1088" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="P3" s="1089" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="Q3" s="1096" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R3" s="1097" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="S3" s="1098" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="T3" s="1099" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="U3" s="1094" t="inlineStr">
+        <is>
+          <t>Have</t>
+        </is>
+      </c>
+      <c r="V3" s="1100" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="1075" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="C4" s="1076" t="n">
+        <v>55</v>
+      </c>
+      <c r="D4" s="1101" t="n"/>
+      <c r="E4" s="1078" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="F4" s="1102" t="n"/>
+      <c r="G4" s="1080" t="n">
+        <v>10836.63</v>
+      </c>
+      <c r="H4" s="1103" t="n"/>
+      <c r="I4" s="1082" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="J4" s="1104" t="n"/>
+      <c r="K4" s="1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1105" t="n"/>
+      <c r="M4" s="1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1106" t="n"/>
+      <c r="O4" s="1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1107" t="n"/>
+      <c r="Q4" s="1090" t="n"/>
+      <c r="R4" s="1091" t="n"/>
+      <c r="S4" s="1092" t="n"/>
+      <c r="T4" s="1093" t="n"/>
+      <c r="U4" s="1094" t="n">
+        <v>11120.83</v>
+      </c>
+      <c r="V4" s="1100" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="960" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="961" t="n"/>
+      <c r="D5" s="962" t="n"/>
+      <c r="E5" s="963" t="n"/>
+      <c r="F5" s="964" t="n"/>
+      <c r="G5" s="1108" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H5" s="1109" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="I5" s="1110" t="n"/>
+      <c r="J5" s="1111" t="n"/>
+      <c r="K5" s="969" t="n"/>
+      <c r="L5" s="970" t="n"/>
+      <c r="M5" s="971" t="n"/>
+      <c r="N5" s="972" t="n"/>
+      <c r="O5" s="973" t="n"/>
+      <c r="P5" s="974" t="n"/>
+      <c r="Q5" s="1112" t="n"/>
+      <c r="R5" s="1113" t="n"/>
+      <c r="S5" s="977" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="T5" s="978" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="U5" s="979" t="n"/>
+      <c r="V5" s="980" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="981" t="n"/>
+      <c r="C6" s="982" t="n"/>
+      <c r="D6" s="983" t="n"/>
+      <c r="E6" s="984" t="n"/>
+      <c r="F6" s="985" t="n"/>
+      <c r="G6" s="986" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H6" s="987" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="I6" s="988" t="n"/>
+      <c r="J6" s="989" t="n"/>
+      <c r="K6" s="990" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="L6" s="991" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M6" s="992" t="n"/>
+      <c r="N6" s="993" t="n"/>
+      <c r="O6" s="994" t="n"/>
+      <c r="P6" s="995" t="n"/>
+      <c r="Q6" s="996" t="n"/>
+      <c r="R6" s="997" t="n"/>
+      <c r="S6" s="998" t="n"/>
+      <c r="T6" s="999" t="n"/>
+      <c r="U6" s="1000" t="n"/>
+      <c r="V6" s="1001" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="981" t="n"/>
+      <c r="C7" s="982" t="n"/>
+      <c r="D7" s="983" t="n"/>
+      <c r="E7" s="984" t="n"/>
+      <c r="F7" s="985" t="n"/>
+      <c r="G7" s="1002" t="n"/>
+      <c r="H7" s="1003" t="n"/>
+      <c r="I7" s="988" t="n"/>
+      <c r="J7" s="989" t="n"/>
+      <c r="K7" s="990" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="L7" s="991" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="M7" s="992" t="n"/>
+      <c r="N7" s="993" t="n"/>
+      <c r="O7" s="994" t="n"/>
+      <c r="P7" s="995" t="n"/>
+      <c r="Q7" s="1004" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="R7" s="1005" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="S7" s="1006" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="T7" s="1007" t="inlineStr">
+        <is>
+          <t>42.5</t>
+        </is>
+      </c>
+      <c r="U7" s="1000" t="n"/>
+      <c r="V7" s="1001" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="981" t="n"/>
+      <c r="C8" s="982" t="n"/>
+      <c r="D8" s="983" t="n"/>
+      <c r="E8" s="984" t="n"/>
+      <c r="F8" s="985" t="n"/>
+      <c r="G8" s="1002" t="n"/>
+      <c r="H8" s="1003" t="n"/>
+      <c r="I8" s="1008" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J8" s="1009" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="K8" s="1010" t="n"/>
+      <c r="L8" s="1011" t="n"/>
+      <c r="M8" s="992" t="n"/>
+      <c r="N8" s="993" t="n"/>
+      <c r="O8" s="994" t="n"/>
+      <c r="P8" s="995" t="n"/>
+      <c r="Q8" s="1004" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R8" s="1005" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="S8" s="1006" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T8" s="1007" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="U8" s="1000" t="n"/>
+      <c r="V8" s="1001" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="981" t="n"/>
+      <c r="C9" s="982" t="n"/>
+      <c r="D9" s="983" t="n"/>
+      <c r="E9" s="984" t="n"/>
+      <c r="F9" s="985" t="n"/>
+      <c r="G9" s="1002" t="n"/>
+      <c r="H9" s="1003" t="n"/>
+      <c r="I9" s="1008" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J9" s="1009" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="K9" s="1010" t="n"/>
+      <c r="L9" s="1011" t="n"/>
+      <c r="M9" s="992" t="n"/>
+      <c r="N9" s="993" t="n"/>
+      <c r="O9" s="994" t="n"/>
+      <c r="P9" s="995" t="n"/>
+      <c r="Q9" s="1004" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R9" s="1005" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="S9" s="1006" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T9" s="1007" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="U9" s="1000" t="n"/>
+      <c r="V9" s="1001" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="1012" t="n"/>
+      <c r="C10" s="1013" t="n"/>
+      <c r="D10" s="1014" t="n"/>
+      <c r="E10" s="1015" t="n"/>
+      <c r="F10" s="1016" t="n"/>
+      <c r="G10" s="1017" t="n"/>
+      <c r="H10" s="1018" t="n"/>
+      <c r="I10" s="1114" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="J10" s="1115" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="K10" s="1116" t="n"/>
+      <c r="L10" s="1117" t="n"/>
+      <c r="M10" s="1023" t="n"/>
+      <c r="N10" s="1024" t="n"/>
+      <c r="O10" s="1025" t="n"/>
+      <c r="P10" s="1026" t="n"/>
+      <c r="Q10" s="1027" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="R10" s="1028" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="S10" s="1029" t="inlineStr">
+        <is>
+          <t>LRT</t>
+        </is>
+      </c>
+      <c r="T10" s="1030" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="U10" s="1031" t="n"/>
+      <c r="V10" s="1032" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="1033" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C11" s="1034" t="n">
+        <v>55</v>
+      </c>
+      <c r="D11" s="1035" t="n"/>
+      <c r="E11" s="1036" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="F11" s="1037" t="n"/>
+      <c r="G11" s="1038" t="n">
+        <v>10994.13</v>
+      </c>
+      <c r="H11" s="1039" t="n"/>
+      <c r="I11" s="1040" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="J11" s="1041" t="n"/>
+      <c r="K11" s="1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1043" t="n"/>
+      <c r="M11" s="1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1045" t="n"/>
+      <c r="O11" s="1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1047" t="n"/>
+      <c r="Q11" s="1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1049" t="n">
+        <v>80</v>
+      </c>
+      <c r="S11" s="1050" t="n">
+        <v>200</v>
+      </c>
+      <c r="T11" s="1051" t="n">
+        <v>80</v>
+      </c>
+      <c r="U11" s="1052" t="n">
+        <v>11240.83</v>
+      </c>
+      <c r="V11" s="1053" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="1054" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C12" s="1055" t="n"/>
+      <c r="D12" s="1056" t="n"/>
+      <c r="E12" s="1057" t="n"/>
+      <c r="F12" s="1058" t="n"/>
+      <c r="G12" s="1059" t="n"/>
+      <c r="H12" s="1060" t="n"/>
+      <c r="I12" s="1061" t="n"/>
+      <c r="J12" s="1062" t="n"/>
+      <c r="K12" s="1063" t="n"/>
+      <c r="L12" s="1064" t="n"/>
+      <c r="M12" s="1065" t="n"/>
+      <c r="N12" s="1066" t="n"/>
+      <c r="O12" s="1067" t="n"/>
+      <c r="P12" s="1068" t="n"/>
+      <c r="Q12" s="1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1070" t="n">
+        <v>80</v>
+      </c>
+      <c r="S12" s="1071" t="n">
+        <v>200</v>
+      </c>
+      <c r="T12" s="1072" t="n">
+        <v>80</v>
+      </c>
+      <c r="U12" s="1073" t="n"/>
+      <c r="V12" s="1074" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="1075" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C13" s="1076" t="n">
+        <v>55</v>
+      </c>
+      <c r="D13" s="1077" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E13" s="1078" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="F13" s="1079" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G13" s="1080" t="n">
+        <v>10994.13</v>
+      </c>
+      <c r="H13" s="1081" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I13" s="1082" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="J13" s="1083" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K13" s="1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1085" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M13" s="1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1087" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O13" s="1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1089" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q13" s="1090" t="n"/>
+      <c r="R13" s="1091" t="n"/>
+      <c r="S13" s="1092" t="n"/>
+      <c r="T13" s="1093" t="n"/>
+      <c r="U13" s="1094" t="n">
+        <v>11240.83</v>
+      </c>
+      <c r="V13" s="1095" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1138" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="1139" t="n"/>
+      <c r="D14" s="1140" t="n"/>
+      <c r="E14" s="1141" t="n"/>
+      <c r="F14" s="1142" t="n"/>
+      <c r="G14" s="1143" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H14" s="1144" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I14" s="1145" t="n"/>
+      <c r="J14" s="1146" t="n"/>
+      <c r="K14" s="1147" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="L14" s="1148" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M14" s="1149" t="n"/>
+      <c r="N14" s="1150" t="n"/>
+      <c r="O14" s="1151" t="n"/>
+      <c r="P14" s="1152" t="n"/>
+      <c r="Q14" s="1153" t="n"/>
+      <c r="R14" s="1154" t="n"/>
+      <c r="S14" s="1155" t="n"/>
+      <c r="T14" s="1156" t="n"/>
+      <c r="U14" s="1157" t="n"/>
+      <c r="V14" s="1158" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="1159" t="n"/>
+      <c r="C15" s="1160" t="n"/>
+      <c r="D15" s="1161" t="n"/>
+      <c r="E15" s="1162" t="n"/>
+      <c r="F15" s="1163" t="n"/>
+      <c r="G15" s="1164" t="n"/>
+      <c r="H15" s="1165" t="n"/>
+      <c r="I15" s="1166" t="n"/>
+      <c r="J15" s="1167" t="n"/>
+      <c r="K15" s="1168" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="L15" s="1169" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M15" s="1170" t="n"/>
+      <c r="N15" s="1171" t="n"/>
+      <c r="O15" s="1172" t="n"/>
+      <c r="P15" s="1173" t="n"/>
+      <c r="Q15" s="1174" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="R15" s="1175" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="S15" s="1176" t="inlineStr">
+        <is>
+          <t>Breakfast</t>
+        </is>
+      </c>
+      <c r="T15" s="1177" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="U15" s="1178" t="n"/>
+      <c r="V15" s="1179" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1159" t="n"/>
+      <c r="C16" s="1160" t="n"/>
+      <c r="D16" s="1161" t="n"/>
+      <c r="E16" s="1162" t="n"/>
+      <c r="F16" s="1163" t="n"/>
+      <c r="G16" s="1164" t="n"/>
+      <c r="H16" s="1165" t="n"/>
+      <c r="I16" s="1180" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J16" s="1181" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="K16" s="1182" t="n"/>
+      <c r="L16" s="1183" t="n"/>
+      <c r="M16" s="1170" t="n"/>
+      <c r="N16" s="1171" t="n"/>
+      <c r="O16" s="1172" t="n"/>
+      <c r="P16" s="1173" t="n"/>
+      <c r="Q16" s="1174" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R16" s="1175" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="S16" s="1176" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T16" s="1177" t="inlineStr">
+        <is>
+          <t>17.7</t>
+        </is>
+      </c>
+      <c r="U16" s="1178" t="n"/>
+      <c r="V16" s="1179" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1159" t="n"/>
+      <c r="C17" s="1160" t="n"/>
+      <c r="D17" s="1161" t="n"/>
+      <c r="E17" s="1162" t="n"/>
+      <c r="F17" s="1163" t="n"/>
+      <c r="G17" s="1184" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="H17" s="1185" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="I17" s="1166" t="n"/>
+      <c r="J17" s="1167" t="n"/>
+      <c r="K17" s="1182" t="n"/>
+      <c r="L17" s="1183" t="n"/>
+      <c r="M17" s="1170" t="n"/>
+      <c r="N17" s="1171" t="n"/>
+      <c r="O17" s="1186" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="P17" s="1187" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="Q17" s="1188" t="n"/>
+      <c r="R17" s="1189" t="n"/>
+      <c r="S17" s="1190" t="n"/>
+      <c r="T17" s="1191" t="n"/>
+      <c r="U17" s="1178" t="n"/>
+      <c r="V17" s="1179" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1159" t="n"/>
+      <c r="C18" s="1160" t="n"/>
+      <c r="D18" s="1161" t="n"/>
+      <c r="E18" s="1162" t="n"/>
+      <c r="F18" s="1163" t="n"/>
+      <c r="G18" s="1164" t="n"/>
+      <c r="H18" s="1165" t="n"/>
+      <c r="I18" s="1166" t="n"/>
+      <c r="J18" s="1167" t="n"/>
+      <c r="K18" s="1182" t="n"/>
+      <c r="L18" s="1183" t="n"/>
+      <c r="M18" s="1170" t="n"/>
+      <c r="N18" s="1171" t="n"/>
+      <c r="O18" s="1186" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="P18" s="1187" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="Q18" s="1174" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="R18" s="1175" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="S18" s="1176" t="inlineStr">
+        <is>
+          <t>Lunch</t>
+        </is>
+      </c>
+      <c r="T18" s="1177" t="inlineStr">
+        <is>
+          <t>34.5</t>
+        </is>
+      </c>
+      <c r="U18" s="1178" t="n"/>
+      <c r="V18" s="1179" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1159" t="n"/>
+      <c r="C19" s="1160" t="n"/>
+      <c r="D19" s="1161" t="n"/>
+      <c r="E19" s="1162" t="n"/>
+      <c r="F19" s="1163" t="n"/>
+      <c r="G19" s="1164" t="n"/>
+      <c r="H19" s="1165" t="n"/>
+      <c r="I19" s="1180" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="J19" s="1181" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="K19" s="1182" t="n"/>
+      <c r="L19" s="1183" t="n"/>
+      <c r="M19" s="1170" t="n"/>
+      <c r="N19" s="1171" t="n"/>
+      <c r="O19" s="1172" t="n"/>
+      <c r="P19" s="1173" t="n"/>
+      <c r="Q19" s="1174" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="R19" s="1175" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="S19" s="1176" t="inlineStr">
+        <is>
+          <t>Bus</t>
+        </is>
+      </c>
+      <c r="T19" s="1177" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="U19" s="1178" t="n"/>
+      <c r="V19" s="1179" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1159" t="n"/>
+      <c r="C20" s="1160" t="n"/>
+      <c r="D20" s="1161" t="n"/>
+      <c r="E20" s="1162" t="n"/>
+      <c r="F20" s="1163" t="n"/>
+      <c r="G20" s="1184" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H20" s="1185" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I20" s="1166" t="n"/>
+      <c r="J20" s="1167" t="n"/>
+      <c r="K20" s="1168" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="L20" s="1169" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="M20" s="1170" t="n"/>
+      <c r="N20" s="1171" t="n"/>
+      <c r="O20" s="1172" t="n"/>
+      <c r="P20" s="1173" t="n"/>
+      <c r="Q20" s="1188" t="n"/>
+      <c r="R20" s="1189" t="n"/>
+      <c r="S20" s="1190" t="n"/>
+      <c r="T20" s="1191" t="n"/>
+      <c r="U20" s="1178" t="n"/>
+      <c r="V20" s="1179" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1192" t="n"/>
+      <c r="C21" s="1193" t="n"/>
+      <c r="D21" s="1194" t="n"/>
+      <c r="E21" s="1195" t="n"/>
+      <c r="F21" s="1196" t="n"/>
+      <c r="G21" s="1197" t="n"/>
+      <c r="H21" s="1198" t="n"/>
+      <c r="I21" s="1199" t="n"/>
+      <c r="J21" s="1200" t="n"/>
+      <c r="K21" s="1201" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="L21" s="1202" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="M21" s="1203" t="n"/>
+      <c r="N21" s="1204" t="n"/>
+      <c r="O21" s="1205" t="n"/>
+      <c r="P21" s="1206" t="n"/>
+      <c r="Q21" s="1207" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="R21" s="1208" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="S21" s="1209" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="T21" s="1210" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="U21" s="1211" t="n"/>
+      <c r="V21" s="1212" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1213" t="inlineStr">
+        <is>
+          <t>sum</t>
+        </is>
+      </c>
+      <c r="C22" s="1214" t="n">
+        <v>55</v>
+      </c>
+      <c r="D22" s="1215" t="n"/>
+      <c r="E22" s="1216" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="F22" s="1217" t="n"/>
+      <c r="G22" s="1218" t="n">
+        <v>10815.63</v>
+      </c>
+      <c r="H22" s="1219" t="n"/>
+      <c r="I22" s="1220" t="n">
+        <v>36</v>
+      </c>
+      <c r="J22" s="1221" t="n"/>
+      <c r="K22" s="1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1223" t="n"/>
+      <c r="M22" s="1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1225" t="n"/>
+      <c r="O22" s="1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1227" t="n"/>
+      <c r="Q22" s="1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1229" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="S22" s="1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1231" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="U22" s="1232" t="n">
+        <v>11027.43</v>
+      </c>
+      <c r="V22" s="1233" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1234" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C23" s="1235" t="n"/>
+      <c r="D23" s="1236" t="n"/>
+      <c r="E23" s="1237" t="n"/>
+      <c r="F23" s="1238" t="n"/>
+      <c r="G23" s="1239" t="n"/>
+      <c r="H23" s="1240" t="n"/>
+      <c r="I23" s="1241" t="n"/>
+      <c r="J23" s="1242" t="n"/>
+      <c r="K23" s="1243" t="n"/>
+      <c r="L23" s="1244" t="n"/>
+      <c r="M23" s="1245" t="n"/>
+      <c r="N23" s="1246" t="n"/>
+      <c r="O23" s="1247" t="n"/>
+      <c r="P23" s="1248" t="n"/>
+      <c r="Q23" s="1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1250" t="n">
+        <v>293.4</v>
+      </c>
+      <c r="S23" s="1251" t="n">
+        <v>200</v>
+      </c>
+      <c r="T23" s="1252" t="n">
+        <v>293.4</v>
+      </c>
+      <c r="U23" s="1253" t="n"/>
+      <c r="V23" s="1254" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1255" t="inlineStr">
+        <is>
+          <t>current have</t>
+        </is>
+      </c>
+      <c r="C24" s="1256" t="n">
+        <v>55</v>
+      </c>
+      <c r="D24" s="1257" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E24" s="1258" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="F24" s="1259" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G24" s="1260" t="n">
+        <v>10815.63</v>
+      </c>
+      <c r="H24" s="1261" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I24" s="1262" t="n">
+        <v>36</v>
+      </c>
+      <c r="J24" s="1263" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K24" s="1264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1265" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M24" s="1266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1267" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O24" s="1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1269" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="Q24" s="1270" t="n"/>
+      <c r="R24" s="1271" t="n"/>
+      <c r="S24" s="1272" t="n"/>
+      <c r="T24" s="1273" t="n"/>
+      <c r="U24" s="1274" t="n">
+        <v>11027.43</v>
+      </c>
+      <c r="V24" s="1275" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="S2:U2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/2026/money/money.xlsx
+++ b/output/2026/money/money.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="190">
   <si>
     <t>Date</t>
   </si>
@@ -443,6 +443,9 @@
     <t>34.5</t>
   </si>
   <si>
+    <t>piggy</t>
+  </si>
+  <si>
     <t>04/07/2026</t>
   </si>
   <si>
@@ -488,12 +491,106 @@
     <t>60</t>
   </si>
   <si>
-    <t>piggy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>06/07/2026</t>
   </si>
   <si>
-    <t>piggy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>38</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>19.5</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
+    <t>5.8</t>
+  </si>
+  <si>
+    <t>07/07/2026</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>Gum</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>08/07/2026</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>Netflix</t>
+  </si>
+  <si>
+    <t>work headphone</t>
+  </si>
+  <si>
+    <t>41.78</t>
+  </si>
+  <si>
+    <t>148.5</t>
+  </si>
+  <si>
+    <t>shampoo</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>conditioner</t>
+  </si>
+  <si>
+    <t>27.9</t>
+  </si>
+  <si>
+    <t>Facial wash</t>
+  </si>
+  <si>
+    <t>mini Bus</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>09/07/2026</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>11/07/2026</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>12/07/2026</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>Piggy-play</t>
+  </si>
+  <si>
+    <t>70.5</t>
   </si>
 </sst>
 </file>
@@ -544,7 +641,7 @@
       <name val="Book Antiqua"/>
     </font>
   </fonts>
-  <fills count="93">
+  <fills count="143">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1017,8 +1114,258 @@
         <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="221">
+  <borders count="341">
     <border>
       <left/>
       <right/>
@@ -3950,6 +4297,1806 @@
     <border>
       <left/>
       <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -4323,7 +6470,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1427">
+  <cellXfs count="2143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -5600,65 +7747,7 @@
     <xf numFmtId="0" fontId="0" fillId="81" borderId="194" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="81" borderId="193" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="82" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="195" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="22" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="191" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="196" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="191" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="73" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="195" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="74" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="75" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="76" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="77" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="78" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="79" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="80" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="81" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="196" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="82" borderId="191" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="73" borderId="192" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -5967,6 +8056,780 @@
     <xf numFmtId="0" fontId="2" fillId="90" borderId="207" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="91" borderId="206" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="91" borderId="208" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="221" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="222" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="223" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="222" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="223" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="222" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="223" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="222" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="223" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="222" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="223" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="222" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="223" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="222" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="223" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="222" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="223" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="222" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="224" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="221" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="225" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="226" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="227" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="226" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="227" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="226" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="228" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="225" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="226" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="227" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="226" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="227" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="100" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="100" borderId="227" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="226" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="228" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="93" borderId="226" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="93" borderId="227" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="229" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="230" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="230" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="230" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="230" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="231" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="230" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="230" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="230" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="230" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="231" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="230" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="232" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="231" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="229" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="233" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="93" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="94" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="98" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="99" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="235" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="235" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="234" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="236" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="235" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="102" borderId="233" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="237" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="93" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="94" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="95" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="96" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="97" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="98" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="238" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="99" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="238" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="100" borderId="239" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="238" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="240" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="239" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="102" borderId="237" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="241" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="93" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="93" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="94" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="94" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="95" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="96" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="97" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="98" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="98" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="99" borderId="242" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="99" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="100" borderId="242" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="100" borderId="243" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="242" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="101" borderId="244" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="101" borderId="243" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="102" borderId="241" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="245" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="246" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="247" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="246" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="248" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="245" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="249" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="250" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="250" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="250" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="252" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="249" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="250" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="250" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="251" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="250" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="252" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="253" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="254" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="255" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="254" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="255" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="254" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="256" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="253" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="257" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="104" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="108" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="109" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="259" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="259" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="258" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="260" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="259" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="112" borderId="257" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="261" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="103" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="104" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="107" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="108" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="262" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="109" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="262" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="263" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="262" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="264" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="263" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="112" borderId="261" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="246" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="105" borderId="247" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="246" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="247" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="246" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="110" borderId="247" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="250" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="251" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="254" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="255" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="104" borderId="254" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="104" borderId="255" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="106" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="255" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="254" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="256" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="265" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="103" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="104" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="104" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="105" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="106" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="107" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="108" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="108" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="109" borderId="266" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="109" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="266" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="110" borderId="267" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="266" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="111" borderId="268" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="111" borderId="267" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="112" borderId="265" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="269" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="270" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="271" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="270" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="272" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="122" borderId="269" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="273" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="276" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="122" borderId="273" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="275" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="119" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="119" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="274" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="276" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="278" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="278" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="278" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="278" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="279" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="278" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="278" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="278" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="278" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="279" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="278" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="280" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="279" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="122" borderId="277" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="281" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="113" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="114" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="117" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="118" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="119" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="283" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="282" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="284" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="283" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="122" borderId="281" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="285" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="113" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="114" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="116" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="117" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="118" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="286" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="119" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="286" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="287" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="286" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="288" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="287" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="122" borderId="285" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="270" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="115" borderId="271" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="270" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="271" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="270" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="120" borderId="271" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="117" borderId="274" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="117" borderId="275" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="289" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="113" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="113" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="114" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="114" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="115" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="116" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="117" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="117" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="118" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="118" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="119" borderId="290" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="119" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="290" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="120" borderId="291" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="290" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="121" borderId="292" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="121" borderId="291" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="122" borderId="289" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="293" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="294" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="295" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="128" borderId="294" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="128" borderId="295" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="130" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="130" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="296" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="132" borderId="293" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="297" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="298" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="299" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="298" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="299" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="130" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="130" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="300" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="132" borderId="297" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="301" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="302" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="303" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="302" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="303" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="302" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="304" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="132" borderId="301" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="305" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="123" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="124" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="128" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="129" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="307" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="307" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="306" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="308" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="307" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="132" borderId="305" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="309" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="123" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="124" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="126" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="310" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="129" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="310" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="311" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="310" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="312" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="311" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="132" borderId="309" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="294" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="295" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="294" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="128" borderId="295" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="294" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="295" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="294" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="296" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="298" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="125" borderId="299" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="298" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="130" borderId="299" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="298" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="300" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="302" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="303" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="302" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="127" borderId="303" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="313" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="123" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="123" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="124" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="124" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="125" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="126" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="127" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="128" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="128" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="129" borderId="314" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="129" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="130" borderId="314" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="130" borderId="315" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="314" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="131" borderId="316" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="131" borderId="315" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="132" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="317" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="319" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="319" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="318" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="319" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="319" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="318" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="319" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="319" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="319" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="319" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="318" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="320" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="142" borderId="317" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="321" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="322" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="323" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="322" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="323" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="322" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="324" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="142" borderId="321" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="322" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="323" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="322" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="323" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="323" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="322" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="324" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="326" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="326" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="326" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="326" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="326" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="326" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="326" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="326" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="327" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="326" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="328" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="327" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="142" borderId="325" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="329" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="133" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="134" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="138" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="139" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="331" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="331" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="330" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="332" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="331" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="142" borderId="329" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="333" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="133" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="134" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="135" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="136" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="137" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="138" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="334" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="139" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="140" borderId="335" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="334" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="336" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="335" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="142" borderId="333" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="337" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="133" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="133" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="134" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="134" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="135" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="136" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="137" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="138" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="138" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="139" borderId="338" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="139" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="338" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="140" borderId="339" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="338" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="141" borderId="340" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="141" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="142" borderId="337" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="195" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="22" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="196" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="79" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="78" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="80" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="73" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="75" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="74" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="77" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="76" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="81" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -6277,7 +9140,7 @@
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6288,8 +9151,8 @@
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.125" style="2" customWidth="1"/>
-    <col min="3" max="13" width="9" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="3" max="18" width="9" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -6297,43 +9160,43 @@
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1100" t="s">
+      <c r="C2" s="2127" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1097"/>
-      <c r="E2" s="1102" t="s">
+      <c r="D2" s="2124"/>
+      <c r="E2" s="2129" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1097"/>
-      <c r="G2" s="1101" t="s">
+      <c r="F2" s="2124"/>
+      <c r="G2" s="2128" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1097"/>
-      <c r="I2" s="1104" t="s">
+      <c r="H2" s="2124"/>
+      <c r="I2" s="2131" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="1097"/>
-      <c r="K2" s="1103" t="s">
+      <c r="J2" s="2124"/>
+      <c r="K2" s="2130" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="1097"/>
-      <c r="M2" s="1098" t="s">
+      <c r="L2" s="2124"/>
+      <c r="M2" s="2125" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1097"/>
-      <c r="O2" s="1096" t="s">
+      <c r="N2" s="2124"/>
+      <c r="O2" s="2123" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="1097"/>
-      <c r="Q2" s="1099" t="s">
+      <c r="P2" s="2124"/>
+      <c r="Q2" s="2126" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="1097"/>
-      <c r="S2" s="1105" t="s">
+      <c r="R2" s="2124"/>
+      <c r="S2" s="2132" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="1106"/>
-      <c r="U2" s="1097"/>
+      <c r="T2" s="2133"/>
+      <c r="U2" s="2124"/>
       <c r="V2" s="4" t="s">
         <v>10</v>
       </c>
@@ -14570,1732 +17433,5045 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:W46"/>
+  <dimension ref="B2:W136"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1120"/>
-    <col min="2" max="2" width="14.5" style="1120" customWidth="1"/>
-    <col min="3" max="22" width="12" style="1120" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="1120"/>
+    <col min="1" max="1" width="9" style="1098" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="1098" customWidth="1"/>
+    <col min="3" max="22" width="12" style="1098" customWidth="1"/>
+    <col min="23" max="27" width="9" style="1098" customWidth="1"/>
+    <col min="28" max="16384" width="9" style="1098"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B2" s="1107" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1108" t="s">
+    <row r="2" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1096" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2137" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1109"/>
-      <c r="E2" s="1110" t="s">
+      <c r="D2" s="2124"/>
+      <c r="E2" s="2139" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="1109"/>
-      <c r="G2" s="1111" t="s">
+      <c r="F2" s="2124"/>
+      <c r="G2" s="2138" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1109"/>
-      <c r="I2" s="1112" t="s">
+      <c r="H2" s="2124"/>
+      <c r="I2" s="2141" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="1109"/>
-      <c r="K2" s="1113" t="s">
+      <c r="J2" s="2124"/>
+      <c r="K2" s="2140" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="1109"/>
-      <c r="M2" s="1114" t="s">
+      <c r="L2" s="2124"/>
+      <c r="M2" s="2135" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1109"/>
-      <c r="O2" s="1115" t="s">
+      <c r="N2" s="2124"/>
+      <c r="O2" s="2134" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="1109"/>
-      <c r="Q2" s="1116" t="s">
+      <c r="P2" s="2124"/>
+      <c r="Q2" s="2136" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="1109"/>
-      <c r="S2" s="1117" t="s">
+      <c r="R2" s="2124"/>
+      <c r="S2" s="2142" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="1118"/>
-      <c r="U2" s="1109"/>
-      <c r="V2" s="1119" t="s">
+      <c r="T2" s="2133"/>
+      <c r="U2" s="2124"/>
+      <c r="V2" s="1097" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B3" s="1107" t="s">
+      <c r="B3" s="1096" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1121" t="s">
+      <c r="C3" s="1099" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1122" t="s">
+      <c r="D3" s="1100" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1123" t="s">
+      <c r="E3" s="1101" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1124" t="s">
+      <c r="F3" s="1102" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="1125" t="s">
+      <c r="G3" s="1103" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="1126" t="s">
+      <c r="H3" s="1104" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="1127" t="s">
+      <c r="I3" s="1105" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="1128" t="s">
+      <c r="J3" s="1106" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="1129" t="s">
+      <c r="K3" s="1107" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="1130" t="s">
+      <c r="L3" s="1108" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="1131" t="s">
+      <c r="M3" s="1109" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="1132" t="s">
+      <c r="N3" s="1110" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="1133" t="s">
+      <c r="O3" s="1111" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="1134" t="s">
+      <c r="P3" s="1112" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="1135" t="s">
+      <c r="Q3" s="1113" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="1136" t="s">
+      <c r="R3" s="1114" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="1137" t="s">
+      <c r="S3" s="1115" t="s">
         <v>12</v>
       </c>
-      <c r="T3" s="1138" t="s">
+      <c r="T3" s="1116" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="1139" t="s">
+      <c r="U3" s="1117" t="s">
         <v>14</v>
       </c>
-      <c r="V3" s="1140"/>
+      <c r="V3" s="1118"/>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B4" s="1107" t="s">
+      <c r="B4" s="1096" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1121">
+      <c r="C4" s="1099">
         <v>55</v>
       </c>
-      <c r="D4" s="1141"/>
-      <c r="E4" s="1123">
+      <c r="D4" s="1119"/>
+      <c r="E4" s="1101">
         <v>120.8</v>
       </c>
-      <c r="F4" s="1142"/>
-      <c r="G4" s="1125">
+      <c r="F4" s="1120"/>
+      <c r="G4" s="1103">
         <v>10836.63</v>
       </c>
-      <c r="H4" s="1143"/>
-      <c r="I4" s="1127">
+      <c r="H4" s="1121"/>
+      <c r="I4" s="1105">
         <v>108.4</v>
       </c>
-      <c r="J4" s="1144"/>
-      <c r="K4" s="1129">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1145"/>
-      <c r="M4" s="1131">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1146"/>
-      <c r="O4" s="1133">
-        <v>0</v>
-      </c>
-      <c r="P4" s="1147"/>
-      <c r="Q4" s="1148"/>
-      <c r="R4" s="1149"/>
-      <c r="S4" s="1150"/>
-      <c r="T4" s="1151"/>
-      <c r="U4" s="1139">
+      <c r="J4" s="1122"/>
+      <c r="K4" s="1107">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1123"/>
+      <c r="M4" s="1109">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1124"/>
+      <c r="O4" s="1111">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1125"/>
+      <c r="Q4" s="1126"/>
+      <c r="R4" s="1127"/>
+      <c r="S4" s="1128"/>
+      <c r="T4" s="1129"/>
+      <c r="U4" s="1117">
         <v>11120.83</v>
       </c>
-      <c r="V4" s="1140"/>
+      <c r="V4" s="1118"/>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B5" s="1152" t="s">
+      <c r="B5" s="1130" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="1153"/>
-      <c r="D5" s="1154"/>
-      <c r="E5" s="1155"/>
-      <c r="F5" s="1156"/>
-      <c r="G5" s="1157" t="s">
+      <c r="C5" s="1131"/>
+      <c r="D5" s="1132"/>
+      <c r="E5" s="1133"/>
+      <c r="F5" s="1134"/>
+      <c r="G5" s="1135" t="s">
         <v>105</v>
       </c>
-      <c r="H5" s="1158" t="s">
+      <c r="H5" s="1136" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="1159"/>
-      <c r="J5" s="1160"/>
-      <c r="K5" s="1161"/>
-      <c r="L5" s="1162"/>
-      <c r="M5" s="1163"/>
-      <c r="N5" s="1164"/>
-      <c r="O5" s="1165"/>
-      <c r="P5" s="1166"/>
-      <c r="Q5" s="1167"/>
-      <c r="R5" s="1168"/>
-      <c r="S5" s="1169" t="s">
+      <c r="I5" s="1137"/>
+      <c r="J5" s="1138"/>
+      <c r="K5" s="1139"/>
+      <c r="L5" s="1140"/>
+      <c r="M5" s="1141"/>
+      <c r="N5" s="1142"/>
+      <c r="O5" s="1143"/>
+      <c r="P5" s="1144"/>
+      <c r="Q5" s="1145"/>
+      <c r="R5" s="1146"/>
+      <c r="S5" s="1147" t="s">
         <v>105</v>
       </c>
-      <c r="T5" s="1170" t="s">
+      <c r="T5" s="1148" t="s">
         <v>46</v>
       </c>
-      <c r="U5" s="1171"/>
-      <c r="V5" s="1172"/>
+      <c r="U5" s="1149"/>
+      <c r="V5" s="1150"/>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B6" s="1173"/>
-      <c r="C6" s="1174"/>
-      <c r="D6" s="1175"/>
-      <c r="E6" s="1176"/>
-      <c r="F6" s="1177"/>
-      <c r="G6" s="1178" t="s">
+      <c r="B6" s="1151"/>
+      <c r="C6" s="1152"/>
+      <c r="D6" s="1153"/>
+      <c r="E6" s="1154"/>
+      <c r="F6" s="1155"/>
+      <c r="G6" s="1156" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="1179" t="s">
+      <c r="H6" s="1157" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="1180"/>
-      <c r="J6" s="1181"/>
-      <c r="K6" s="1182" t="s">
+      <c r="I6" s="1158"/>
+      <c r="J6" s="1159"/>
+      <c r="K6" s="1160" t="s">
         <v>134</v>
       </c>
-      <c r="L6" s="1183" t="s">
+      <c r="L6" s="1161" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="1184"/>
-      <c r="N6" s="1185"/>
-      <c r="O6" s="1186"/>
-      <c r="P6" s="1187"/>
-      <c r="Q6" s="1188"/>
-      <c r="R6" s="1189"/>
-      <c r="S6" s="1190"/>
-      <c r="T6" s="1191"/>
-      <c r="U6" s="1192"/>
-      <c r="V6" s="1193"/>
+      <c r="M6" s="1162"/>
+      <c r="N6" s="1163"/>
+      <c r="O6" s="1164"/>
+      <c r="P6" s="1165"/>
+      <c r="Q6" s="1166"/>
+      <c r="R6" s="1167"/>
+      <c r="S6" s="1168"/>
+      <c r="T6" s="1169"/>
+      <c r="U6" s="1170"/>
+      <c r="V6" s="1171"/>
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B7" s="1173"/>
-      <c r="C7" s="1174"/>
-      <c r="D7" s="1175"/>
-      <c r="E7" s="1176"/>
-      <c r="F7" s="1177"/>
-      <c r="G7" s="1194"/>
-      <c r="H7" s="1195"/>
-      <c r="I7" s="1180"/>
-      <c r="J7" s="1181"/>
-      <c r="K7" s="1182" t="s">
+      <c r="B7" s="1151"/>
+      <c r="C7" s="1152"/>
+      <c r="D7" s="1153"/>
+      <c r="E7" s="1154"/>
+      <c r="F7" s="1155"/>
+      <c r="G7" s="1172"/>
+      <c r="H7" s="1173"/>
+      <c r="I7" s="1158"/>
+      <c r="J7" s="1159"/>
+      <c r="K7" s="1160" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="1183" t="s">
+      <c r="L7" s="1161" t="s">
         <v>134</v>
       </c>
-      <c r="M7" s="1184"/>
-      <c r="N7" s="1185"/>
-      <c r="O7" s="1186"/>
-      <c r="P7" s="1187"/>
-      <c r="Q7" s="1196" t="s">
+      <c r="M7" s="1162"/>
+      <c r="N7" s="1163"/>
+      <c r="O7" s="1164"/>
+      <c r="P7" s="1165"/>
+      <c r="Q7" s="1174" t="s">
         <v>29</v>
       </c>
-      <c r="R7" s="1197" t="s">
+      <c r="R7" s="1175" t="s">
         <v>134</v>
       </c>
-      <c r="S7" s="1198" t="s">
+      <c r="S7" s="1176" t="s">
         <v>29</v>
       </c>
-      <c r="T7" s="1199" t="s">
+      <c r="T7" s="1177" t="s">
         <v>134</v>
       </c>
-      <c r="U7" s="1192"/>
-      <c r="V7" s="1193"/>
+      <c r="U7" s="1170"/>
+      <c r="V7" s="1171"/>
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B8" s="1173"/>
-      <c r="C8" s="1174"/>
-      <c r="D8" s="1175"/>
-      <c r="E8" s="1176"/>
-      <c r="F8" s="1177"/>
-      <c r="G8" s="1194"/>
-      <c r="H8" s="1195"/>
-      <c r="I8" s="1200" t="s">
+      <c r="B8" s="1151"/>
+      <c r="C8" s="1152"/>
+      <c r="D8" s="1153"/>
+      <c r="E8" s="1154"/>
+      <c r="F8" s="1155"/>
+      <c r="G8" s="1172"/>
+      <c r="H8" s="1173"/>
+      <c r="I8" s="1178" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="1201" t="s">
+      <c r="J8" s="1179" t="s">
         <v>135</v>
       </c>
-      <c r="K8" s="1202"/>
-      <c r="L8" s="1203"/>
-      <c r="M8" s="1184"/>
-      <c r="N8" s="1185"/>
-      <c r="O8" s="1186"/>
-      <c r="P8" s="1187"/>
-      <c r="Q8" s="1196" t="s">
+      <c r="K8" s="1180"/>
+      <c r="L8" s="1181"/>
+      <c r="M8" s="1162"/>
+      <c r="N8" s="1163"/>
+      <c r="O8" s="1164"/>
+      <c r="P8" s="1165"/>
+      <c r="Q8" s="1174" t="s">
         <v>50</v>
       </c>
-      <c r="R8" s="1197" t="s">
+      <c r="R8" s="1175" t="s">
         <v>135</v>
       </c>
-      <c r="S8" s="1198" t="s">
+      <c r="S8" s="1176" t="s">
         <v>50</v>
       </c>
-      <c r="T8" s="1199" t="s">
+      <c r="T8" s="1177" t="s">
         <v>135</v>
       </c>
-      <c r="U8" s="1192"/>
-      <c r="V8" s="1193"/>
+      <c r="U8" s="1170"/>
+      <c r="V8" s="1171"/>
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B9" s="1173"/>
-      <c r="C9" s="1174"/>
-      <c r="D9" s="1175"/>
-      <c r="E9" s="1176"/>
-      <c r="F9" s="1177"/>
-      <c r="G9" s="1194"/>
-      <c r="H9" s="1195"/>
-      <c r="I9" s="1200" t="s">
+      <c r="B9" s="1151"/>
+      <c r="C9" s="1152"/>
+      <c r="D9" s="1153"/>
+      <c r="E9" s="1154"/>
+      <c r="F9" s="1155"/>
+      <c r="G9" s="1172"/>
+      <c r="H9" s="1173"/>
+      <c r="I9" s="1178" t="s">
         <v>50</v>
       </c>
-      <c r="J9" s="1201" t="s">
+      <c r="J9" s="1179" t="s">
         <v>136</v>
       </c>
-      <c r="K9" s="1202"/>
-      <c r="L9" s="1203"/>
-      <c r="M9" s="1184"/>
-      <c r="N9" s="1185"/>
-      <c r="O9" s="1186"/>
-      <c r="P9" s="1187"/>
-      <c r="Q9" s="1196" t="s">
+      <c r="K9" s="1180"/>
+      <c r="L9" s="1181"/>
+      <c r="M9" s="1162"/>
+      <c r="N9" s="1163"/>
+      <c r="O9" s="1164"/>
+      <c r="P9" s="1165"/>
+      <c r="Q9" s="1174" t="s">
         <v>50</v>
       </c>
-      <c r="R9" s="1197" t="s">
+      <c r="R9" s="1175" t="s">
         <v>136</v>
       </c>
-      <c r="S9" s="1198" t="s">
+      <c r="S9" s="1176" t="s">
         <v>50</v>
       </c>
-      <c r="T9" s="1199" t="s">
+      <c r="T9" s="1177" t="s">
         <v>136</v>
       </c>
-      <c r="U9" s="1192"/>
-      <c r="V9" s="1193"/>
+      <c r="U9" s="1170"/>
+      <c r="V9" s="1171"/>
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B10" s="1204"/>
-      <c r="C10" s="1205"/>
-      <c r="D10" s="1206"/>
-      <c r="E10" s="1207"/>
-      <c r="F10" s="1208"/>
-      <c r="G10" s="1209"/>
-      <c r="H10" s="1210"/>
-      <c r="I10" s="1211" t="s">
+      <c r="B10" s="1182"/>
+      <c r="C10" s="1183"/>
+      <c r="D10" s="1184"/>
+      <c r="E10" s="1185"/>
+      <c r="F10" s="1186"/>
+      <c r="G10" s="1187"/>
+      <c r="H10" s="1188"/>
+      <c r="I10" s="1189" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="1212" t="s">
+      <c r="J10" s="1190" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="1213"/>
-      <c r="L10" s="1214"/>
-      <c r="M10" s="1215"/>
-      <c r="N10" s="1216"/>
-      <c r="O10" s="1217"/>
-      <c r="P10" s="1218"/>
-      <c r="Q10" s="1219" t="s">
+      <c r="K10" s="1191"/>
+      <c r="L10" s="1192"/>
+      <c r="M10" s="1193"/>
+      <c r="N10" s="1194"/>
+      <c r="O10" s="1195"/>
+      <c r="P10" s="1196"/>
+      <c r="Q10" s="1197" t="s">
         <v>23</v>
       </c>
-      <c r="R10" s="1220" t="s">
+      <c r="R10" s="1198" t="s">
         <v>48</v>
       </c>
-      <c r="S10" s="1221" t="s">
+      <c r="S10" s="1199" t="s">
         <v>23</v>
       </c>
-      <c r="T10" s="1222" t="s">
+      <c r="T10" s="1200" t="s">
         <v>48</v>
       </c>
-      <c r="U10" s="1223"/>
-      <c r="V10" s="1224"/>
+      <c r="U10" s="1201"/>
+      <c r="V10" s="1202"/>
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B11" s="1225" t="s">
+      <c r="B11" s="1203" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="1226">
+      <c r="C11" s="1204">
         <v>55</v>
       </c>
-      <c r="D11" s="1227"/>
-      <c r="E11" s="1228">
+      <c r="D11" s="1205"/>
+      <c r="E11" s="1206">
         <v>120.8</v>
       </c>
-      <c r="F11" s="1229"/>
-      <c r="G11" s="1230">
+      <c r="F11" s="1207"/>
+      <c r="G11" s="1208">
         <v>10994.13</v>
       </c>
-      <c r="H11" s="1231"/>
-      <c r="I11" s="1232">
+      <c r="H11" s="1209"/>
+      <c r="I11" s="1210">
         <v>70.900000000000006</v>
       </c>
-      <c r="J11" s="1233"/>
-      <c r="K11" s="1234">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1235"/>
-      <c r="M11" s="1236">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1237"/>
-      <c r="O11" s="1238">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1239"/>
-      <c r="Q11" s="1240">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1241">
+      <c r="J11" s="1211"/>
+      <c r="K11" s="1212">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1213"/>
+      <c r="M11" s="1214">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1215"/>
+      <c r="O11" s="1216">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1217"/>
+      <c r="Q11" s="1218">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1219">
         <v>80</v>
       </c>
-      <c r="S11" s="1242">
+      <c r="S11" s="1220">
         <v>200</v>
       </c>
-      <c r="T11" s="1243">
+      <c r="T11" s="1221">
         <v>80</v>
       </c>
-      <c r="U11" s="1244">
+      <c r="U11" s="1222">
         <v>11240.83</v>
       </c>
-      <c r="V11" s="1245" t="s">
+      <c r="V11" s="1223" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B12" s="1246" t="s">
+      <c r="B12" s="1224" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="1247"/>
-      <c r="D12" s="1248"/>
-      <c r="E12" s="1249"/>
-      <c r="F12" s="1250"/>
-      <c r="G12" s="1251"/>
-      <c r="H12" s="1252"/>
-      <c r="I12" s="1253"/>
-      <c r="J12" s="1254"/>
-      <c r="K12" s="1255"/>
-      <c r="L12" s="1256"/>
-      <c r="M12" s="1257"/>
-      <c r="N12" s="1258"/>
-      <c r="O12" s="1259"/>
-      <c r="P12" s="1260"/>
-      <c r="Q12" s="1261">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1262">
+      <c r="C12" s="1225"/>
+      <c r="D12" s="1226"/>
+      <c r="E12" s="1227"/>
+      <c r="F12" s="1228"/>
+      <c r="G12" s="1229"/>
+      <c r="H12" s="1230"/>
+      <c r="I12" s="1231"/>
+      <c r="J12" s="1232"/>
+      <c r="K12" s="1233"/>
+      <c r="L12" s="1234"/>
+      <c r="M12" s="1235"/>
+      <c r="N12" s="1236"/>
+      <c r="O12" s="1237"/>
+      <c r="P12" s="1238"/>
+      <c r="Q12" s="1239">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1240">
         <v>80</v>
       </c>
-      <c r="S12" s="1263">
+      <c r="S12" s="1241">
         <v>200</v>
       </c>
-      <c r="T12" s="1264">
+      <c r="T12" s="1242">
         <v>80</v>
       </c>
-      <c r="U12" s="1265"/>
-      <c r="V12" s="1266"/>
+      <c r="U12" s="1243"/>
+      <c r="V12" s="1244"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B13" s="1107" t="s">
+      <c r="B13" s="1096" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="1121">
+      <c r="C13" s="1099">
         <v>55</v>
       </c>
-      <c r="D13" s="1122" t="s">
+      <c r="D13" s="1100" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="1123">
+      <c r="E13" s="1101">
         <v>120.8</v>
       </c>
-      <c r="F13" s="1124" t="s">
+      <c r="F13" s="1102" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="1125">
+      <c r="G13" s="1103">
         <v>10994.13</v>
       </c>
-      <c r="H13" s="1126" t="s">
+      <c r="H13" s="1104" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="1127">
+      <c r="I13" s="1105">
         <v>70.900000000000006</v>
       </c>
-      <c r="J13" s="1128" t="s">
+      <c r="J13" s="1106" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="1129">
-        <v>0</v>
-      </c>
-      <c r="L13" s="1130" t="s">
+      <c r="K13" s="1107">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1108" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="1131">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1132" t="s">
+      <c r="M13" s="1109">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1110" t="s">
         <v>19</v>
       </c>
-      <c r="O13" s="1133">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1134" t="s">
+      <c r="O13" s="1111">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1112" t="s">
         <v>19</v>
       </c>
-      <c r="Q13" s="1148"/>
-      <c r="R13" s="1149"/>
-      <c r="S13" s="1150"/>
-      <c r="T13" s="1151"/>
-      <c r="U13" s="1139">
+      <c r="Q13" s="1126"/>
+      <c r="R13" s="1127"/>
+      <c r="S13" s="1128"/>
+      <c r="T13" s="1129"/>
+      <c r="U13" s="1117">
         <v>11240.83</v>
       </c>
-      <c r="V13" s="1119" t="s">
+      <c r="V13" s="1097" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B14" s="1267" t="s">
+      <c r="B14" s="1245" t="s">
         <v>137</v>
       </c>
-      <c r="C14" s="1268"/>
-      <c r="D14" s="1269"/>
-      <c r="E14" s="1270"/>
-      <c r="F14" s="1271"/>
-      <c r="G14" s="1272" t="s">
+      <c r="C14" s="1246"/>
+      <c r="D14" s="1247"/>
+      <c r="E14" s="1248"/>
+      <c r="F14" s="1249"/>
+      <c r="G14" s="1250" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="1273" t="s">
+      <c r="H14" s="1251" t="s">
         <v>113</v>
       </c>
-      <c r="I14" s="1274"/>
-      <c r="J14" s="1275"/>
-      <c r="K14" s="1276" t="s">
+      <c r="I14" s="1252"/>
+      <c r="J14" s="1253"/>
+      <c r="K14" s="1254" t="s">
         <v>113</v>
       </c>
-      <c r="L14" s="1277" t="s">
+      <c r="L14" s="1255" t="s">
         <v>28</v>
       </c>
-      <c r="M14" s="1278"/>
-      <c r="N14" s="1279"/>
-      <c r="O14" s="1280"/>
-      <c r="P14" s="1281"/>
-      <c r="Q14" s="1282"/>
-      <c r="R14" s="1283"/>
-      <c r="S14" s="1284"/>
-      <c r="T14" s="1285"/>
-      <c r="U14" s="1286"/>
-      <c r="V14" s="1287"/>
+      <c r="M14" s="1256"/>
+      <c r="N14" s="1257"/>
+      <c r="O14" s="1258"/>
+      <c r="P14" s="1259"/>
+      <c r="Q14" s="1260"/>
+      <c r="R14" s="1261"/>
+      <c r="S14" s="1262"/>
+      <c r="T14" s="1263"/>
+      <c r="U14" s="1264"/>
+      <c r="V14" s="1265"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B15" s="1288"/>
-      <c r="C15" s="1289"/>
-      <c r="D15" s="1290"/>
-      <c r="E15" s="1291"/>
-      <c r="F15" s="1292"/>
-      <c r="G15" s="1293"/>
-      <c r="H15" s="1294"/>
-      <c r="I15" s="1295"/>
-      <c r="J15" s="1296"/>
-      <c r="K15" s="1297" t="s">
+      <c r="B15" s="1266"/>
+      <c r="C15" s="1267"/>
+      <c r="D15" s="1268"/>
+      <c r="E15" s="1269"/>
+      <c r="F15" s="1270"/>
+      <c r="G15" s="1271"/>
+      <c r="H15" s="1272"/>
+      <c r="I15" s="1273"/>
+      <c r="J15" s="1274"/>
+      <c r="K15" s="1275" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="1298" t="s">
+      <c r="L15" s="1276" t="s">
         <v>113</v>
       </c>
-      <c r="M15" s="1299"/>
-      <c r="N15" s="1300"/>
-      <c r="O15" s="1301"/>
-      <c r="P15" s="1302"/>
-      <c r="Q15" s="1303" t="s">
+      <c r="M15" s="1277"/>
+      <c r="N15" s="1278"/>
+      <c r="O15" s="1279"/>
+      <c r="P15" s="1280"/>
+      <c r="Q15" s="1281" t="s">
         <v>29</v>
       </c>
-      <c r="R15" s="1304" t="s">
+      <c r="R15" s="1282" t="s">
         <v>113</v>
       </c>
-      <c r="S15" s="1305" t="s">
+      <c r="S15" s="1283" t="s">
         <v>29</v>
       </c>
-      <c r="T15" s="1306" t="s">
+      <c r="T15" s="1284" t="s">
         <v>113</v>
       </c>
-      <c r="U15" s="1307"/>
-      <c r="V15" s="1308"/>
+      <c r="U15" s="1285"/>
+      <c r="V15" s="1286"/>
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B16" s="1288"/>
-      <c r="C16" s="1289"/>
-      <c r="D16" s="1290"/>
-      <c r="E16" s="1291"/>
-      <c r="F16" s="1292"/>
-      <c r="G16" s="1293"/>
-      <c r="H16" s="1294"/>
-      <c r="I16" s="1309" t="s">
+      <c r="B16" s="1266"/>
+      <c r="C16" s="1267"/>
+      <c r="D16" s="1268"/>
+      <c r="E16" s="1269"/>
+      <c r="F16" s="1270"/>
+      <c r="G16" s="1271"/>
+      <c r="H16" s="1272"/>
+      <c r="I16" s="1287" t="s">
         <v>50</v>
       </c>
-      <c r="J16" s="1310" t="s">
+      <c r="J16" s="1288" t="s">
         <v>135</v>
       </c>
-      <c r="K16" s="1311"/>
-      <c r="L16" s="1312"/>
-      <c r="M16" s="1299"/>
-      <c r="N16" s="1300"/>
-      <c r="O16" s="1301"/>
-      <c r="P16" s="1302"/>
-      <c r="Q16" s="1303" t="s">
+      <c r="K16" s="1289"/>
+      <c r="L16" s="1290"/>
+      <c r="M16" s="1277"/>
+      <c r="N16" s="1278"/>
+      <c r="O16" s="1279"/>
+      <c r="P16" s="1280"/>
+      <c r="Q16" s="1281" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="1304" t="s">
+      <c r="R16" s="1282" t="s">
         <v>135</v>
       </c>
-      <c r="S16" s="1305" t="s">
+      <c r="S16" s="1283" t="s">
         <v>50</v>
       </c>
-      <c r="T16" s="1306" t="s">
+      <c r="T16" s="1284" t="s">
         <v>135</v>
       </c>
-      <c r="U16" s="1307"/>
-      <c r="V16" s="1308"/>
+      <c r="U16" s="1285"/>
+      <c r="V16" s="1286"/>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B17" s="1288"/>
-      <c r="C17" s="1289"/>
-      <c r="D17" s="1290"/>
-      <c r="E17" s="1291"/>
-      <c r="F17" s="1292"/>
-      <c r="G17" s="1313" t="s">
+      <c r="B17" s="1266"/>
+      <c r="C17" s="1267"/>
+      <c r="D17" s="1268"/>
+      <c r="E17" s="1269"/>
+      <c r="F17" s="1270"/>
+      <c r="G17" s="1291" t="s">
         <v>138</v>
       </c>
-      <c r="H17" s="1314" t="s">
+      <c r="H17" s="1292" t="s">
         <v>139</v>
       </c>
-      <c r="I17" s="1295"/>
-      <c r="J17" s="1296"/>
-      <c r="K17" s="1311"/>
-      <c r="L17" s="1312"/>
-      <c r="M17" s="1299"/>
-      <c r="N17" s="1300"/>
-      <c r="O17" s="1315" t="s">
+      <c r="I17" s="1273"/>
+      <c r="J17" s="1274"/>
+      <c r="K17" s="1289"/>
+      <c r="L17" s="1290"/>
+      <c r="M17" s="1277"/>
+      <c r="N17" s="1278"/>
+      <c r="O17" s="1293" t="s">
         <v>139</v>
       </c>
-      <c r="P17" s="1316" t="s">
+      <c r="P17" s="1294" t="s">
         <v>28</v>
       </c>
-      <c r="Q17" s="1317"/>
-      <c r="R17" s="1318"/>
-      <c r="S17" s="1319"/>
-      <c r="T17" s="1320"/>
-      <c r="U17" s="1307"/>
-      <c r="V17" s="1308"/>
+      <c r="Q17" s="1295"/>
+      <c r="R17" s="1296"/>
+      <c r="S17" s="1297"/>
+      <c r="T17" s="1298"/>
+      <c r="U17" s="1285"/>
+      <c r="V17" s="1286"/>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B18" s="1288"/>
-      <c r="C18" s="1289"/>
-      <c r="D18" s="1290"/>
-      <c r="E18" s="1291"/>
-      <c r="F18" s="1292"/>
-      <c r="G18" s="1293"/>
-      <c r="H18" s="1294"/>
-      <c r="I18" s="1295"/>
-      <c r="J18" s="1296"/>
-      <c r="K18" s="1311"/>
-      <c r="L18" s="1312"/>
-      <c r="M18" s="1299"/>
-      <c r="N18" s="1300"/>
-      <c r="O18" s="1315" t="s">
+      <c r="B18" s="1266"/>
+      <c r="C18" s="1267"/>
+      <c r="D18" s="1268"/>
+      <c r="E18" s="1269"/>
+      <c r="F18" s="1270"/>
+      <c r="G18" s="1271"/>
+      <c r="H18" s="1272"/>
+      <c r="I18" s="1273"/>
+      <c r="J18" s="1274"/>
+      <c r="K18" s="1289"/>
+      <c r="L18" s="1290"/>
+      <c r="M18" s="1277"/>
+      <c r="N18" s="1278"/>
+      <c r="O18" s="1293" t="s">
         <v>46</v>
       </c>
-      <c r="P18" s="1316" t="s">
+      <c r="P18" s="1294" t="s">
         <v>139</v>
       </c>
-      <c r="Q18" s="1303" t="s">
+      <c r="Q18" s="1281" t="s">
         <v>46</v>
       </c>
-      <c r="R18" s="1304" t="s">
+      <c r="R18" s="1282" t="s">
         <v>139</v>
       </c>
-      <c r="S18" s="1305" t="s">
+      <c r="S18" s="1283" t="s">
         <v>46</v>
       </c>
-      <c r="T18" s="1306" t="s">
+      <c r="T18" s="1284" t="s">
         <v>139</v>
       </c>
-      <c r="U18" s="1307"/>
-      <c r="V18" s="1308"/>
+      <c r="U18" s="1285"/>
+      <c r="V18" s="1286"/>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B19" s="1288"/>
-      <c r="C19" s="1289"/>
-      <c r="D19" s="1290"/>
-      <c r="E19" s="1291"/>
-      <c r="F19" s="1292"/>
-      <c r="G19" s="1293"/>
-      <c r="H19" s="1294"/>
-      <c r="I19" s="1309" t="s">
+      <c r="B19" s="1266"/>
+      <c r="C19" s="1267"/>
+      <c r="D19" s="1268"/>
+      <c r="E19" s="1269"/>
+      <c r="F19" s="1270"/>
+      <c r="G19" s="1271"/>
+      <c r="H19" s="1272"/>
+      <c r="I19" s="1287" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="1310" t="s">
+      <c r="J19" s="1288" t="s">
         <v>136</v>
       </c>
-      <c r="K19" s="1311"/>
-      <c r="L19" s="1312"/>
-      <c r="M19" s="1299"/>
-      <c r="N19" s="1300"/>
-      <c r="O19" s="1301"/>
-      <c r="P19" s="1302"/>
-      <c r="Q19" s="1303" t="s">
+      <c r="K19" s="1289"/>
+      <c r="L19" s="1290"/>
+      <c r="M19" s="1277"/>
+      <c r="N19" s="1278"/>
+      <c r="O19" s="1279"/>
+      <c r="P19" s="1280"/>
+      <c r="Q19" s="1281" t="s">
         <v>50</v>
       </c>
-      <c r="R19" s="1304" t="s">
+      <c r="R19" s="1282" t="s">
         <v>136</v>
       </c>
-      <c r="S19" s="1305" t="s">
+      <c r="S19" s="1283" t="s">
         <v>50</v>
       </c>
-      <c r="T19" s="1306" t="s">
+      <c r="T19" s="1284" t="s">
         <v>136</v>
       </c>
-      <c r="U19" s="1307"/>
-      <c r="V19" s="1308"/>
+      <c r="U19" s="1285"/>
+      <c r="V19" s="1286"/>
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B20" s="1288"/>
-      <c r="C20" s="1289"/>
-      <c r="D20" s="1290"/>
-      <c r="E20" s="1291"/>
-      <c r="F20" s="1292"/>
-      <c r="G20" s="1313" t="s">
+      <c r="B20" s="1266"/>
+      <c r="C20" s="1267"/>
+      <c r="D20" s="1268"/>
+      <c r="E20" s="1269"/>
+      <c r="F20" s="1270"/>
+      <c r="G20" s="1291" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="1314" t="s">
+      <c r="H20" s="1292" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="1295"/>
-      <c r="J20" s="1296"/>
-      <c r="K20" s="1297" t="s">
+      <c r="I20" s="1273"/>
+      <c r="J20" s="1274"/>
+      <c r="K20" s="1275" t="s">
         <v>119</v>
       </c>
-      <c r="L20" s="1298" t="s">
+      <c r="L20" s="1276" t="s">
         <v>28</v>
       </c>
-      <c r="M20" s="1299"/>
-      <c r="N20" s="1300"/>
-      <c r="O20" s="1301"/>
-      <c r="P20" s="1302"/>
-      <c r="Q20" s="1317"/>
-      <c r="R20" s="1318"/>
-      <c r="S20" s="1319"/>
-      <c r="T20" s="1320"/>
-      <c r="U20" s="1307"/>
-      <c r="V20" s="1308"/>
+      <c r="M20" s="1277"/>
+      <c r="N20" s="1278"/>
+      <c r="O20" s="1279"/>
+      <c r="P20" s="1280"/>
+      <c r="Q20" s="1295"/>
+      <c r="R20" s="1296"/>
+      <c r="S20" s="1297"/>
+      <c r="T20" s="1298"/>
+      <c r="U20" s="1285"/>
+      <c r="V20" s="1286"/>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B21" s="1321"/>
-      <c r="C21" s="1322"/>
-      <c r="D21" s="1323"/>
-      <c r="E21" s="1324"/>
-      <c r="F21" s="1325"/>
-      <c r="G21" s="1326"/>
-      <c r="H21" s="1327"/>
-      <c r="I21" s="1328"/>
-      <c r="J21" s="1329"/>
-      <c r="K21" s="1330" t="s">
+      <c r="B21" s="1299"/>
+      <c r="C21" s="1300"/>
+      <c r="D21" s="1301"/>
+      <c r="E21" s="1302"/>
+      <c r="F21" s="1303"/>
+      <c r="G21" s="1304"/>
+      <c r="H21" s="1305"/>
+      <c r="I21" s="1306"/>
+      <c r="J21" s="1307"/>
+      <c r="K21" s="1308" t="s">
         <v>33</v>
       </c>
-      <c r="L21" s="1331" t="s">
+      <c r="L21" s="1309" t="s">
         <v>119</v>
       </c>
-      <c r="M21" s="1332"/>
-      <c r="N21" s="1333"/>
-      <c r="O21" s="1334"/>
-      <c r="P21" s="1335"/>
-      <c r="Q21" s="1336" t="s">
+      <c r="M21" s="1310"/>
+      <c r="N21" s="1311"/>
+      <c r="O21" s="1312"/>
+      <c r="P21" s="1313"/>
+      <c r="Q21" s="1314" t="s">
         <v>33</v>
       </c>
-      <c r="R21" s="1337" t="s">
+      <c r="R21" s="1315" t="s">
         <v>119</v>
       </c>
-      <c r="S21" s="1338" t="s">
+      <c r="S21" s="1316" t="s">
         <v>33</v>
       </c>
-      <c r="T21" s="1339" t="s">
+      <c r="T21" s="1317" t="s">
         <v>119</v>
       </c>
-      <c r="U21" s="1340"/>
-      <c r="V21" s="1341"/>
-      <c r="W21" s="1120" t="s">
+      <c r="U21" s="1318"/>
+      <c r="V21" s="1319"/>
+      <c r="W21" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B22" s="1320" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1321">
+        <v>55</v>
+      </c>
+      <c r="D22" s="1322"/>
+      <c r="E22" s="1323">
+        <v>120.8</v>
+      </c>
+      <c r="F22" s="1324"/>
+      <c r="G22" s="1325">
+        <v>10815.63</v>
+      </c>
+      <c r="H22" s="1326"/>
+      <c r="I22" s="1327">
+        <v>36</v>
+      </c>
+      <c r="J22" s="1328"/>
+      <c r="K22" s="1329">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1330"/>
+      <c r="M22" s="1331">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1332"/>
+      <c r="O22" s="1333">
+        <v>0</v>
+      </c>
+      <c r="P22" s="1334"/>
+      <c r="Q22" s="1335">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1336">
+        <v>213.4</v>
+      </c>
+      <c r="S22" s="1337">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1338">
+        <v>213.4</v>
+      </c>
+      <c r="U22" s="1339">
+        <v>11027.43</v>
+      </c>
+      <c r="V22" s="1340" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B23" s="1341" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1342"/>
+      <c r="D23" s="1343"/>
+      <c r="E23" s="1344"/>
+      <c r="F23" s="1345"/>
+      <c r="G23" s="1346"/>
+      <c r="H23" s="1347"/>
+      <c r="I23" s="1348"/>
+      <c r="J23" s="1349"/>
+      <c r="K23" s="1350"/>
+      <c r="L23" s="1351"/>
+      <c r="M23" s="1352"/>
+      <c r="N23" s="1353"/>
+      <c r="O23" s="1354"/>
+      <c r="P23" s="1355"/>
+      <c r="Q23" s="1356">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1357">
+        <v>293.39999999999998</v>
+      </c>
+      <c r="S23" s="1358">
+        <v>200</v>
+      </c>
+      <c r="T23" s="1359">
+        <v>293.39999999999998</v>
+      </c>
+      <c r="U23" s="1360"/>
+      <c r="V23" s="1361"/>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B24" s="1362" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1363">
+        <v>55</v>
+      </c>
+      <c r="D24" s="1364" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1365">
+        <v>120.8</v>
+      </c>
+      <c r="F24" s="1366" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="1367">
+        <v>10815.63</v>
+      </c>
+      <c r="H24" s="1368" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="1369">
+        <v>36</v>
+      </c>
+      <c r="J24" s="1370" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="1371">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1372" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="1373">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1374" t="s">
+        <v>19</v>
+      </c>
+      <c r="O24" s="1375">
+        <v>0</v>
+      </c>
+      <c r="P24" s="1376" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q24" s="1377"/>
+      <c r="R24" s="1378"/>
+      <c r="S24" s="1379"/>
+      <c r="T24" s="1380"/>
+      <c r="U24" s="1381">
+        <v>11027.43</v>
+      </c>
+      <c r="V24" s="1382" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B25" s="1245" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="1246"/>
+      <c r="D25" s="1247"/>
+      <c r="E25" s="1248"/>
+      <c r="F25" s="1249"/>
+      <c r="G25" s="1250" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="1251" t="s">
+        <v>142</v>
+      </c>
+      <c r="I25" s="1252"/>
+      <c r="J25" s="1253"/>
+      <c r="K25" s="1383"/>
+      <c r="L25" s="1384"/>
+      <c r="M25" s="1256"/>
+      <c r="N25" s="1257"/>
+      <c r="O25" s="1258"/>
+      <c r="P25" s="1259"/>
+      <c r="Q25" s="1385" t="s">
+        <v>33</v>
+      </c>
+      <c r="R25" s="1386" t="s">
+        <v>142</v>
+      </c>
+      <c r="S25" s="1387" t="s">
+        <v>33</v>
+      </c>
+      <c r="T25" s="1388" t="s">
+        <v>142</v>
+      </c>
+      <c r="U25" s="1264"/>
+      <c r="V25" s="1265"/>
+      <c r="W25" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B26" s="1266"/>
+      <c r="C26" s="1267"/>
+      <c r="D26" s="1268"/>
+      <c r="E26" s="1269"/>
+      <c r="F26" s="1270"/>
+      <c r="G26" s="1291" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1292" t="s">
+        <v>27</v>
+      </c>
+      <c r="I26" s="1273"/>
+      <c r="J26" s="1274"/>
+      <c r="K26" s="1275" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="1276" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="1277"/>
+      <c r="N26" s="1278"/>
+      <c r="O26" s="1279"/>
+      <c r="P26" s="1280"/>
+      <c r="Q26" s="1295"/>
+      <c r="R26" s="1296"/>
+      <c r="S26" s="1297"/>
+      <c r="T26" s="1298"/>
+      <c r="U26" s="1285"/>
+      <c r="V26" s="1286"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B27" s="1299"/>
+      <c r="C27" s="1300"/>
+      <c r="D27" s="1301"/>
+      <c r="E27" s="1302"/>
+      <c r="F27" s="1303"/>
+      <c r="G27" s="1304"/>
+      <c r="H27" s="1305"/>
+      <c r="I27" s="1306"/>
+      <c r="J27" s="1307"/>
+      <c r="K27" s="1308" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27" s="1309" t="s">
+        <v>27</v>
+      </c>
+      <c r="M27" s="1310"/>
+      <c r="N27" s="1311"/>
+      <c r="O27" s="1312"/>
+      <c r="P27" s="1313"/>
+      <c r="Q27" s="1314" t="s">
+        <v>44</v>
+      </c>
+      <c r="R27" s="1315" t="s">
+        <v>27</v>
+      </c>
+      <c r="S27" s="1316" t="s">
+        <v>44</v>
+      </c>
+      <c r="T27" s="1317" t="s">
+        <v>27</v>
+      </c>
+      <c r="U27" s="1318"/>
+      <c r="V27" s="1319"/>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B28" s="1320" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="1321">
+        <v>55</v>
+      </c>
+      <c r="D28" s="1322"/>
+      <c r="E28" s="1323">
+        <v>120.8</v>
+      </c>
+      <c r="F28" s="1324"/>
+      <c r="G28" s="1325">
+        <v>10707.63</v>
+      </c>
+      <c r="H28" s="1326"/>
+      <c r="I28" s="1327">
+        <v>36</v>
+      </c>
+      <c r="J28" s="1328"/>
+      <c r="K28" s="1329">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1330"/>
+      <c r="M28" s="1331">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1332"/>
+      <c r="O28" s="1333">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1334"/>
+      <c r="Q28" s="1335">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1336">
+        <v>108</v>
+      </c>
+      <c r="S28" s="1337">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1338">
+        <v>108</v>
+      </c>
+      <c r="U28" s="1339">
+        <v>10919.43</v>
+      </c>
+      <c r="V28" s="1340" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B29" s="1341" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1342"/>
+      <c r="D29" s="1343"/>
+      <c r="E29" s="1344"/>
+      <c r="F29" s="1345"/>
+      <c r="G29" s="1346"/>
+      <c r="H29" s="1347"/>
+      <c r="I29" s="1348"/>
+      <c r="J29" s="1349"/>
+      <c r="K29" s="1350"/>
+      <c r="L29" s="1351"/>
+      <c r="M29" s="1352"/>
+      <c r="N29" s="1353"/>
+      <c r="O29" s="1354"/>
+      <c r="P29" s="1355"/>
+      <c r="Q29" s="1356">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1357">
+        <v>401.4</v>
+      </c>
+      <c r="S29" s="1358">
+        <v>200</v>
+      </c>
+      <c r="T29" s="1359">
+        <v>401.4</v>
+      </c>
+      <c r="U29" s="1360"/>
+      <c r="V29" s="1361"/>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B30" s="1245" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="1246"/>
+      <c r="D30" s="1247"/>
+      <c r="E30" s="1248"/>
+      <c r="F30" s="1249"/>
+      <c r="G30" s="1389"/>
+      <c r="H30" s="1390"/>
+      <c r="I30" s="1391" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="1392" t="s">
+        <v>48</v>
+      </c>
+      <c r="K30" s="1383"/>
+      <c r="L30" s="1384"/>
+      <c r="M30" s="1256"/>
+      <c r="N30" s="1257"/>
+      <c r="O30" s="1258"/>
+      <c r="P30" s="1259"/>
+      <c r="Q30" s="1385" t="s">
+        <v>23</v>
+      </c>
+      <c r="R30" s="1386" t="s">
+        <v>48</v>
+      </c>
+      <c r="S30" s="1387" t="s">
+        <v>23</v>
+      </c>
+      <c r="T30" s="1388" t="s">
+        <v>48</v>
+      </c>
+      <c r="U30" s="1264"/>
+      <c r="V30" s="1265"/>
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B31" s="1266"/>
+      <c r="C31" s="1267"/>
+      <c r="D31" s="1268"/>
+      <c r="E31" s="1269"/>
+      <c r="F31" s="1270"/>
+      <c r="G31" s="1291" t="s">
+        <v>5</v>
+      </c>
+      <c r="H31" s="1292" t="s">
+        <v>144</v>
+      </c>
+      <c r="I31" s="1273"/>
+      <c r="J31" s="1274"/>
+      <c r="K31" s="1275" t="s">
+        <v>144</v>
+      </c>
+      <c r="L31" s="1276" t="s">
+        <v>28</v>
+      </c>
+      <c r="M31" s="1277"/>
+      <c r="N31" s="1278"/>
+      <c r="O31" s="1279"/>
+      <c r="P31" s="1280"/>
+      <c r="Q31" s="1295"/>
+      <c r="R31" s="1296"/>
+      <c r="S31" s="1297"/>
+      <c r="T31" s="1298"/>
+      <c r="U31" s="1285"/>
+      <c r="V31" s="1286"/>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B32" s="1266"/>
+      <c r="C32" s="1267"/>
+      <c r="D32" s="1268"/>
+      <c r="E32" s="1269"/>
+      <c r="F32" s="1270"/>
+      <c r="G32" s="1271"/>
+      <c r="H32" s="1272"/>
+      <c r="I32" s="1273"/>
+      <c r="J32" s="1274"/>
+      <c r="K32" s="1275" t="s">
+        <v>29</v>
+      </c>
+      <c r="L32" s="1276" t="s">
+        <v>144</v>
+      </c>
+      <c r="M32" s="1277"/>
+      <c r="N32" s="1278"/>
+      <c r="O32" s="1279"/>
+      <c r="P32" s="1280"/>
+      <c r="Q32" s="1281" t="s">
+        <v>29</v>
+      </c>
+      <c r="R32" s="1282" t="s">
+        <v>144</v>
+      </c>
+      <c r="S32" s="1283" t="s">
+        <v>29</v>
+      </c>
+      <c r="T32" s="1284" t="s">
+        <v>144</v>
+      </c>
+      <c r="U32" s="1285"/>
+      <c r="V32" s="1286"/>
+      <c r="W32" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B33" s="1266"/>
+      <c r="C33" s="1393" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="1394" t="s">
+        <v>145</v>
+      </c>
+      <c r="E33" s="1269"/>
+      <c r="F33" s="1270"/>
+      <c r="G33" s="1271"/>
+      <c r="H33" s="1272"/>
+      <c r="I33" s="1273"/>
+      <c r="J33" s="1274"/>
+      <c r="K33" s="1289"/>
+      <c r="L33" s="1290"/>
+      <c r="M33" s="1277"/>
+      <c r="N33" s="1278"/>
+      <c r="O33" s="1279"/>
+      <c r="P33" s="1280"/>
+      <c r="Q33" s="1281" t="s">
+        <v>44</v>
+      </c>
+      <c r="R33" s="1282" t="s">
+        <v>145</v>
+      </c>
+      <c r="S33" s="1283" t="s">
+        <v>44</v>
+      </c>
+      <c r="T33" s="1284" t="s">
+        <v>145</v>
+      </c>
+      <c r="U33" s="1285"/>
+      <c r="V33" s="1286"/>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B34" s="1266"/>
+      <c r="C34" s="1267"/>
+      <c r="D34" s="1268"/>
+      <c r="E34" s="1269"/>
+      <c r="F34" s="1270"/>
+      <c r="G34" s="1291" t="s">
+        <v>5</v>
+      </c>
+      <c r="H34" s="1292" t="s">
+        <v>146</v>
+      </c>
+      <c r="I34" s="1273"/>
+      <c r="J34" s="1274"/>
+      <c r="K34" s="1275" t="s">
+        <v>146</v>
+      </c>
+      <c r="L34" s="1276" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34" s="1277"/>
+      <c r="N34" s="1278"/>
+      <c r="O34" s="1279"/>
+      <c r="P34" s="1280"/>
+      <c r="Q34" s="1295"/>
+      <c r="R34" s="1296"/>
+      <c r="S34" s="1297"/>
+      <c r="T34" s="1298"/>
+      <c r="U34" s="1285"/>
+      <c r="V34" s="1286"/>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B35" s="1266"/>
+      <c r="C35" s="1267"/>
+      <c r="D35" s="1268"/>
+      <c r="E35" s="1269"/>
+      <c r="F35" s="1270"/>
+      <c r="G35" s="1271"/>
+      <c r="H35" s="1272"/>
+      <c r="I35" s="1273"/>
+      <c r="J35" s="1274"/>
+      <c r="K35" s="1275" t="s">
+        <v>147</v>
+      </c>
+      <c r="L35" s="1276" t="s">
+        <v>146</v>
+      </c>
+      <c r="M35" s="1277"/>
+      <c r="N35" s="1278"/>
+      <c r="O35" s="1279"/>
+      <c r="P35" s="1280"/>
+      <c r="Q35" s="1281" t="s">
+        <v>147</v>
+      </c>
+      <c r="R35" s="1282" t="s">
+        <v>146</v>
+      </c>
+      <c r="S35" s="1283" t="s">
+        <v>147</v>
+      </c>
+      <c r="T35" s="1284" t="s">
+        <v>146</v>
+      </c>
+      <c r="U35" s="1285"/>
+      <c r="V35" s="1286"/>
+    </row>
+    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B36" s="1266"/>
+      <c r="C36" s="1393" t="s">
+        <v>148</v>
+      </c>
+      <c r="D36" s="1394" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" s="1269"/>
+      <c r="F36" s="1270"/>
+      <c r="G36" s="1271"/>
+      <c r="H36" s="1272"/>
+      <c r="I36" s="1273"/>
+      <c r="J36" s="1274"/>
+      <c r="K36" s="1289"/>
+      <c r="L36" s="1290"/>
+      <c r="M36" s="1277"/>
+      <c r="N36" s="1278"/>
+      <c r="O36" s="1279"/>
+      <c r="P36" s="1280"/>
+      <c r="Q36" s="1281" t="s">
+        <v>148</v>
+      </c>
+      <c r="R36" s="1282" t="s">
+        <v>149</v>
+      </c>
+      <c r="S36" s="1283" t="s">
+        <v>148</v>
+      </c>
+      <c r="T36" s="1284" t="s">
+        <v>149</v>
+      </c>
+      <c r="U36" s="1285"/>
+      <c r="V36" s="1286"/>
+      <c r="W36" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B37" s="1266"/>
+      <c r="C37" s="1267"/>
+      <c r="D37" s="1268"/>
+      <c r="E37" s="1269"/>
+      <c r="F37" s="1270"/>
+      <c r="G37" s="1271"/>
+      <c r="H37" s="1272"/>
+      <c r="I37" s="1287" t="s">
+        <v>120</v>
+      </c>
+      <c r="J37" s="1288" t="s">
+        <v>150</v>
+      </c>
+      <c r="K37" s="1289"/>
+      <c r="L37" s="1290"/>
+      <c r="M37" s="1277"/>
+      <c r="N37" s="1278"/>
+      <c r="O37" s="1279"/>
+      <c r="P37" s="1280"/>
+      <c r="Q37" s="1281" t="s">
+        <v>120</v>
+      </c>
+      <c r="R37" s="1282" t="s">
+        <v>150</v>
+      </c>
+      <c r="S37" s="1283" t="s">
+        <v>120</v>
+      </c>
+      <c r="T37" s="1284" t="s">
+        <v>150</v>
+      </c>
+      <c r="U37" s="1285"/>
+      <c r="V37" s="1286"/>
+    </row>
+    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B38" s="1266"/>
+      <c r="C38" s="1267"/>
+      <c r="D38" s="1268"/>
+      <c r="E38" s="1269"/>
+      <c r="F38" s="1270"/>
+      <c r="G38" s="1291" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="1292" t="s">
+        <v>151</v>
+      </c>
+      <c r="I38" s="1287" t="s">
+        <v>151</v>
+      </c>
+      <c r="J38" s="1288" t="s">
+        <v>28</v>
+      </c>
+      <c r="K38" s="1289"/>
+      <c r="L38" s="1290"/>
+      <c r="M38" s="1277"/>
+      <c r="N38" s="1278"/>
+      <c r="O38" s="1279"/>
+      <c r="P38" s="1280"/>
+      <c r="Q38" s="1295"/>
+      <c r="R38" s="1296"/>
+      <c r="S38" s="1297"/>
+      <c r="T38" s="1298"/>
+      <c r="U38" s="1285"/>
+      <c r="V38" s="1286"/>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B39" s="1266"/>
+      <c r="C39" s="1267"/>
+      <c r="D39" s="1268"/>
+      <c r="E39" s="1269"/>
+      <c r="F39" s="1270"/>
+      <c r="G39" s="1271"/>
+      <c r="H39" s="1272"/>
+      <c r="I39" s="1287" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="1288" t="s">
+        <v>152</v>
+      </c>
+      <c r="K39" s="1289"/>
+      <c r="L39" s="1290"/>
+      <c r="M39" s="1277"/>
+      <c r="N39" s="1278"/>
+      <c r="O39" s="1279"/>
+      <c r="P39" s="1280"/>
+      <c r="Q39" s="1281" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" s="1282" t="s">
+        <v>152</v>
+      </c>
+      <c r="S39" s="1283" t="s">
+        <v>25</v>
+      </c>
+      <c r="T39" s="1284" t="s">
+        <v>152</v>
+      </c>
+      <c r="U39" s="1285"/>
+      <c r="V39" s="1286"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B40" s="1266"/>
+      <c r="C40" s="1267"/>
+      <c r="D40" s="1268"/>
+      <c r="E40" s="1269"/>
+      <c r="F40" s="1270"/>
+      <c r="G40" s="1291" t="s">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1292" t="s">
+        <v>153</v>
+      </c>
+      <c r="I40" s="1273"/>
+      <c r="J40" s="1274"/>
+      <c r="K40" s="1275" t="s">
+        <v>153</v>
+      </c>
+      <c r="L40" s="1276" t="s">
+        <v>28</v>
+      </c>
+      <c r="M40" s="1277"/>
+      <c r="N40" s="1278"/>
+      <c r="O40" s="1279"/>
+      <c r="P40" s="1280"/>
+      <c r="Q40" s="1295"/>
+      <c r="R40" s="1296"/>
+      <c r="S40" s="1297"/>
+      <c r="T40" s="1298"/>
+      <c r="U40" s="1285"/>
+      <c r="V40" s="1286"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B41" s="1266"/>
+      <c r="C41" s="1267"/>
+      <c r="D41" s="1268"/>
+      <c r="E41" s="1269"/>
+      <c r="F41" s="1270"/>
+      <c r="G41" s="1271"/>
+      <c r="H41" s="1272"/>
+      <c r="I41" s="1273"/>
+      <c r="J41" s="1274"/>
+      <c r="K41" s="1275" t="s">
+        <v>46</v>
+      </c>
+      <c r="L41" s="1276" t="s">
+        <v>153</v>
+      </c>
+      <c r="M41" s="1277"/>
+      <c r="N41" s="1278"/>
+      <c r="O41" s="1279"/>
+      <c r="P41" s="1280"/>
+      <c r="Q41" s="1281" t="s">
+        <v>46</v>
+      </c>
+      <c r="R41" s="1282" t="s">
+        <v>153</v>
+      </c>
+      <c r="S41" s="1283" t="s">
+        <v>46</v>
+      </c>
+      <c r="T41" s="1284" t="s">
+        <v>153</v>
+      </c>
+      <c r="U41" s="1285"/>
+      <c r="V41" s="1286"/>
+      <c r="W41" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B42" s="1266"/>
+      <c r="C42" s="1267"/>
+      <c r="D42" s="1268"/>
+      <c r="E42" s="1269"/>
+      <c r="F42" s="1270"/>
+      <c r="G42" s="1271"/>
+      <c r="H42" s="1272"/>
+      <c r="I42" s="1287" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="1288" t="s">
+        <v>154</v>
+      </c>
+      <c r="K42" s="1289"/>
+      <c r="L42" s="1290"/>
+      <c r="M42" s="1277"/>
+      <c r="N42" s="1278"/>
+      <c r="O42" s="1279"/>
+      <c r="P42" s="1280"/>
+      <c r="Q42" s="1281" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" s="1282" t="s">
+        <v>154</v>
+      </c>
+      <c r="S42" s="1283" t="s">
+        <v>23</v>
+      </c>
+      <c r="T42" s="1284" t="s">
+        <v>154</v>
+      </c>
+      <c r="U42" s="1285"/>
+      <c r="V42" s="1286"/>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B43" s="1299"/>
+      <c r="C43" s="1395" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B22" s="1342" t="s">
+      <c r="D43" s="1396" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="1397" t="s">
+        <v>103</v>
+      </c>
+      <c r="F43" s="1398" t="s">
+        <v>155</v>
+      </c>
+      <c r="G43" s="1304"/>
+      <c r="H43" s="1305"/>
+      <c r="I43" s="1306"/>
+      <c r="J43" s="1307"/>
+      <c r="K43" s="1399"/>
+      <c r="L43" s="1400"/>
+      <c r="M43" s="1310"/>
+      <c r="N43" s="1311"/>
+      <c r="O43" s="1312"/>
+      <c r="P43" s="1313"/>
+      <c r="Q43" s="1401"/>
+      <c r="R43" s="1402"/>
+      <c r="S43" s="1403"/>
+      <c r="T43" s="1404"/>
+      <c r="U43" s="1318"/>
+      <c r="V43" s="1319"/>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B44" s="1320" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="1343">
-        <v>55</v>
-      </c>
-      <c r="D22" s="1344"/>
-      <c r="E22" s="1345">
-        <v>120.8</v>
-      </c>
-      <c r="F22" s="1346"/>
-      <c r="G22" s="1347">
-        <v>10815.63</v>
-      </c>
-      <c r="H22" s="1348"/>
-      <c r="I22" s="1349">
+      <c r="C44" s="1321">
+        <v>75</v>
+      </c>
+      <c r="D44" s="1322"/>
+      <c r="E44" s="1323">
+        <v>60.8</v>
+      </c>
+      <c r="F44" s="1324"/>
+      <c r="G44" s="1325">
+        <v>9939.33</v>
+      </c>
+      <c r="H44" s="1326"/>
+      <c r="I44" s="1327">
+        <v>506.9</v>
+      </c>
+      <c r="J44" s="1328"/>
+      <c r="K44" s="1329">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1330"/>
+      <c r="M44" s="1331">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1332"/>
+      <c r="O44" s="1333">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1334"/>
+      <c r="Q44" s="1335">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1336">
+        <v>337.4</v>
+      </c>
+      <c r="S44" s="1337">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1338">
+        <v>337.4</v>
+      </c>
+      <c r="U44" s="1339">
+        <v>10582.03</v>
+      </c>
+      <c r="V44" s="1340" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B45" s="1341" t="s">
+        <v>20</v>
+      </c>
+      <c r="C45" s="1342"/>
+      <c r="D45" s="1343"/>
+      <c r="E45" s="1344"/>
+      <c r="F45" s="1345"/>
+      <c r="G45" s="1346"/>
+      <c r="H45" s="1347"/>
+      <c r="I45" s="1348"/>
+      <c r="J45" s="1349"/>
+      <c r="K45" s="1350"/>
+      <c r="L45" s="1351"/>
+      <c r="M45" s="1352"/>
+      <c r="N45" s="1353"/>
+      <c r="O45" s="1354"/>
+      <c r="P45" s="1355"/>
+      <c r="Q45" s="1356">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1357">
+        <v>738.8</v>
+      </c>
+      <c r="S45" s="1358">
+        <v>200</v>
+      </c>
+      <c r="T45" s="1359">
+        <v>738.8</v>
+      </c>
+      <c r="U45" s="1360"/>
+      <c r="V45" s="1361"/>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B46" s="1362" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="1363">
+        <v>75</v>
+      </c>
+      <c r="D46" s="1364" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="1365">
+        <v>60.8</v>
+      </c>
+      <c r="F46" s="1366" t="s">
+        <v>19</v>
+      </c>
+      <c r="G46" s="1367">
+        <v>9939.33</v>
+      </c>
+      <c r="H46" s="1368" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="1369">
+        <v>506.9</v>
+      </c>
+      <c r="J46" s="1370" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="1371">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1372" t="s">
+        <v>19</v>
+      </c>
+      <c r="M46" s="1373">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1374" t="s">
+        <v>19</v>
+      </c>
+      <c r="O46" s="1375">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1376" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q46" s="1377"/>
+      <c r="R46" s="1378"/>
+      <c r="S46" s="1379"/>
+      <c r="T46" s="1380"/>
+      <c r="U46" s="1381">
+        <v>10582.03</v>
+      </c>
+      <c r="V46" s="1382" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="1405" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="1406"/>
+      <c r="D47" s="1407"/>
+      <c r="E47" s="1408"/>
+      <c r="F47" s="1409"/>
+      <c r="G47" s="1410"/>
+      <c r="H47" s="1411"/>
+      <c r="I47" s="1412" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="1413" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="1414"/>
+      <c r="L47" s="1415"/>
+      <c r="M47" s="1416"/>
+      <c r="N47" s="1417"/>
+      <c r="O47" s="1418"/>
+      <c r="P47" s="1419"/>
+      <c r="Q47" s="1420" t="s">
+        <v>23</v>
+      </c>
+      <c r="R47" s="1421" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" s="1422" t="s">
+        <v>23</v>
+      </c>
+      <c r="T47" s="1423" t="s">
+        <v>24</v>
+      </c>
+      <c r="U47" s="1424"/>
+      <c r="V47" s="1425"/>
+    </row>
+    <row r="48" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="1426"/>
+      <c r="C48" s="1427"/>
+      <c r="D48" s="1428"/>
+      <c r="E48" s="1429"/>
+      <c r="F48" s="1430"/>
+      <c r="G48" s="1431"/>
+      <c r="H48" s="1432"/>
+      <c r="I48" s="1433" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="1434" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48" s="1435"/>
+      <c r="L48" s="1436"/>
+      <c r="M48" s="1437"/>
+      <c r="N48" s="1438"/>
+      <c r="O48" s="1439"/>
+      <c r="P48" s="1440"/>
+      <c r="Q48" s="1441" t="s">
+        <v>25</v>
+      </c>
+      <c r="R48" s="1442" t="s">
+        <v>26</v>
+      </c>
+      <c r="S48" s="1443" t="s">
+        <v>25</v>
+      </c>
+      <c r="T48" s="1444" t="s">
+        <v>26</v>
+      </c>
+      <c r="U48" s="1445"/>
+      <c r="V48" s="1446"/>
+    </row>
+    <row r="49" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="1426"/>
+      <c r="C49" s="1427"/>
+      <c r="D49" s="1428"/>
+      <c r="E49" s="1429"/>
+      <c r="F49" s="1430"/>
+      <c r="G49" s="1447" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="1448" t="s">
+        <v>157</v>
+      </c>
+      <c r="I49" s="1449"/>
+      <c r="J49" s="1450"/>
+      <c r="K49" s="1451" t="s">
+        <v>157</v>
+      </c>
+      <c r="L49" s="1452" t="s">
+        <v>28</v>
+      </c>
+      <c r="M49" s="1437"/>
+      <c r="N49" s="1438"/>
+      <c r="O49" s="1439"/>
+      <c r="P49" s="1440"/>
+      <c r="Q49" s="1453"/>
+      <c r="R49" s="1454"/>
+      <c r="S49" s="1455"/>
+      <c r="T49" s="1456"/>
+      <c r="U49" s="1445"/>
+      <c r="V49" s="1446"/>
+    </row>
+    <row r="50" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="1426"/>
+      <c r="C50" s="1427"/>
+      <c r="D50" s="1428"/>
+      <c r="E50" s="1429"/>
+      <c r="F50" s="1430"/>
+      <c r="G50" s="1431"/>
+      <c r="H50" s="1432"/>
+      <c r="I50" s="1449"/>
+      <c r="J50" s="1450"/>
+      <c r="K50" s="1451" t="s">
+        <v>46</v>
+      </c>
+      <c r="L50" s="1452" t="s">
+        <v>157</v>
+      </c>
+      <c r="M50" s="1437"/>
+      <c r="N50" s="1438"/>
+      <c r="O50" s="1439"/>
+      <c r="P50" s="1440"/>
+      <c r="Q50" s="1441" t="s">
+        <v>46</v>
+      </c>
+      <c r="R50" s="1442" t="s">
+        <v>157</v>
+      </c>
+      <c r="S50" s="1443" t="s">
+        <v>46</v>
+      </c>
+      <c r="T50" s="1444" t="s">
+        <v>157</v>
+      </c>
+      <c r="U50" s="1445"/>
+      <c r="V50" s="1446"/>
+    </row>
+    <row r="51" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="1426"/>
+      <c r="C51" s="1427"/>
+      <c r="D51" s="1428"/>
+      <c r="E51" s="1429"/>
+      <c r="F51" s="1430"/>
+      <c r="G51" s="1431"/>
+      <c r="H51" s="1432"/>
+      <c r="I51" s="1433" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="1434" t="s">
         <v>36</v>
       </c>
-      <c r="J22" s="1350"/>
-      <c r="K22" s="1351">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1352"/>
-      <c r="M22" s="1353">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1354"/>
-      <c r="O22" s="1355">
-        <v>0</v>
-      </c>
-      <c r="P22" s="1356"/>
-      <c r="Q22" s="1357">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1358">
-        <v>213.4</v>
-      </c>
-      <c r="S22" s="1359">
-        <v>0</v>
-      </c>
-      <c r="T22" s="1360">
-        <v>213.4</v>
-      </c>
-      <c r="U22" s="1361">
-        <v>11027.43</v>
-      </c>
-      <c r="V22" s="1362" t="s">
+      <c r="K51" s="1435"/>
+      <c r="L51" s="1436"/>
+      <c r="M51" s="1437"/>
+      <c r="N51" s="1438"/>
+      <c r="O51" s="1439"/>
+      <c r="P51" s="1440"/>
+      <c r="Q51" s="1441" t="s">
+        <v>25</v>
+      </c>
+      <c r="R51" s="1442" t="s">
+        <v>36</v>
+      </c>
+      <c r="S51" s="1443" t="s">
+        <v>25</v>
+      </c>
+      <c r="T51" s="1444" t="s">
+        <v>36</v>
+      </c>
+      <c r="U51" s="1445"/>
+      <c r="V51" s="1446"/>
+    </row>
+    <row r="52" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="1426"/>
+      <c r="C52" s="1457" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" s="1458" t="s">
+        <v>158</v>
+      </c>
+      <c r="E52" s="1429"/>
+      <c r="F52" s="1430"/>
+      <c r="G52" s="1431"/>
+      <c r="H52" s="1432"/>
+      <c r="I52" s="1449"/>
+      <c r="J52" s="1450"/>
+      <c r="K52" s="1435"/>
+      <c r="L52" s="1436"/>
+      <c r="M52" s="1437"/>
+      <c r="N52" s="1438"/>
+      <c r="O52" s="1439"/>
+      <c r="P52" s="1440"/>
+      <c r="Q52" s="1441" t="s">
+        <v>44</v>
+      </c>
+      <c r="R52" s="1442" t="s">
+        <v>158</v>
+      </c>
+      <c r="S52" s="1443" t="s">
+        <v>44</v>
+      </c>
+      <c r="T52" s="1444" t="s">
+        <v>158</v>
+      </c>
+      <c r="U52" s="1445"/>
+      <c r="V52" s="1446"/>
+    </row>
+    <row r="53" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="1426"/>
+      <c r="C53" s="1427"/>
+      <c r="D53" s="1428"/>
+      <c r="E53" s="1429"/>
+      <c r="F53" s="1430"/>
+      <c r="G53" s="1447" t="s">
+        <v>5</v>
+      </c>
+      <c r="H53" s="1448" t="s">
+        <v>70</v>
+      </c>
+      <c r="I53" s="1449"/>
+      <c r="J53" s="1450"/>
+      <c r="K53" s="1451" t="s">
+        <v>70</v>
+      </c>
+      <c r="L53" s="1452" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="1437"/>
+      <c r="N53" s="1438"/>
+      <c r="O53" s="1439"/>
+      <c r="P53" s="1440"/>
+      <c r="Q53" s="1453"/>
+      <c r="R53" s="1454"/>
+      <c r="S53" s="1455"/>
+      <c r="T53" s="1456"/>
+      <c r="U53" s="1445"/>
+      <c r="V53" s="1446"/>
+    </row>
+    <row r="54" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="1426"/>
+      <c r="C54" s="1427"/>
+      <c r="D54" s="1428"/>
+      <c r="E54" s="1429"/>
+      <c r="F54" s="1430"/>
+      <c r="G54" s="1431"/>
+      <c r="H54" s="1432"/>
+      <c r="I54" s="1449"/>
+      <c r="J54" s="1450"/>
+      <c r="K54" s="1451" t="s">
+        <v>71</v>
+      </c>
+      <c r="L54" s="1452" t="s">
+        <v>70</v>
+      </c>
+      <c r="M54" s="1437"/>
+      <c r="N54" s="1438"/>
+      <c r="O54" s="1439"/>
+      <c r="P54" s="1440"/>
+      <c r="Q54" s="1441" t="s">
+        <v>71</v>
+      </c>
+      <c r="R54" s="1442" t="s">
+        <v>70</v>
+      </c>
+      <c r="S54" s="1443" t="s">
+        <v>71</v>
+      </c>
+      <c r="T54" s="1444" t="s">
+        <v>70</v>
+      </c>
+      <c r="U54" s="1445"/>
+      <c r="V54" s="1446"/>
+    </row>
+    <row r="55" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="1426"/>
+      <c r="C55" s="1427"/>
+      <c r="D55" s="1428"/>
+      <c r="E55" s="1429"/>
+      <c r="F55" s="1430"/>
+      <c r="G55" s="1431"/>
+      <c r="H55" s="1432"/>
+      <c r="I55" s="1433" t="s">
+        <v>23</v>
+      </c>
+      <c r="J55" s="1434" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="1435"/>
+      <c r="L55" s="1436"/>
+      <c r="M55" s="1437"/>
+      <c r="N55" s="1438"/>
+      <c r="O55" s="1439"/>
+      <c r="P55" s="1440"/>
+      <c r="Q55" s="1441" t="s">
+        <v>23</v>
+      </c>
+      <c r="R55" s="1442" t="s">
+        <v>24</v>
+      </c>
+      <c r="S55" s="1443" t="s">
+        <v>23</v>
+      </c>
+      <c r="T55" s="1444" t="s">
+        <v>24</v>
+      </c>
+      <c r="U55" s="1445"/>
+      <c r="V55" s="1446"/>
+    </row>
+    <row r="56" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="1426"/>
+      <c r="C56" s="1427"/>
+      <c r="D56" s="1428"/>
+      <c r="E56" s="1429"/>
+      <c r="F56" s="1430"/>
+      <c r="G56" s="1431"/>
+      <c r="H56" s="1432"/>
+      <c r="I56" s="1433" t="s">
+        <v>94</v>
+      </c>
+      <c r="J56" s="1434" t="s">
+        <v>159</v>
+      </c>
+      <c r="K56" s="1435"/>
+      <c r="L56" s="1436"/>
+      <c r="M56" s="1437"/>
+      <c r="N56" s="1438"/>
+      <c r="O56" s="1439"/>
+      <c r="P56" s="1440"/>
+      <c r="Q56" s="1441" t="s">
+        <v>94</v>
+      </c>
+      <c r="R56" s="1442" t="s">
+        <v>159</v>
+      </c>
+      <c r="S56" s="1443" t="s">
+        <v>94</v>
+      </c>
+      <c r="T56" s="1444" t="s">
+        <v>159</v>
+      </c>
+      <c r="U56" s="1445"/>
+      <c r="V56" s="1446"/>
+    </row>
+    <row r="57" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="1426"/>
+      <c r="C57" s="1427"/>
+      <c r="D57" s="1428"/>
+      <c r="E57" s="1429"/>
+      <c r="F57" s="1430"/>
+      <c r="G57" s="1431"/>
+      <c r="H57" s="1432"/>
+      <c r="I57" s="1433" t="s">
+        <v>94</v>
+      </c>
+      <c r="J57" s="1434" t="s">
+        <v>160</v>
+      </c>
+      <c r="K57" s="1435"/>
+      <c r="L57" s="1436"/>
+      <c r="M57" s="1437"/>
+      <c r="N57" s="1438"/>
+      <c r="O57" s="1439"/>
+      <c r="P57" s="1440"/>
+      <c r="Q57" s="1441" t="s">
+        <v>94</v>
+      </c>
+      <c r="R57" s="1442" t="s">
+        <v>160</v>
+      </c>
+      <c r="S57" s="1443" t="s">
+        <v>94</v>
+      </c>
+      <c r="T57" s="1444" t="s">
+        <v>160</v>
+      </c>
+      <c r="U57" s="1445"/>
+      <c r="V57" s="1446"/>
+    </row>
+    <row r="58" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="1459"/>
+      <c r="C58" s="1460"/>
+      <c r="D58" s="1461"/>
+      <c r="E58" s="1462"/>
+      <c r="F58" s="1463"/>
+      <c r="G58" s="1464"/>
+      <c r="H58" s="1465"/>
+      <c r="I58" s="1466" t="s">
+        <v>50</v>
+      </c>
+      <c r="J58" s="1467" t="s">
+        <v>161</v>
+      </c>
+      <c r="K58" s="1468"/>
+      <c r="L58" s="1469"/>
+      <c r="M58" s="1470"/>
+      <c r="N58" s="1471"/>
+      <c r="O58" s="1472"/>
+      <c r="P58" s="1473"/>
+      <c r="Q58" s="1474" t="s">
+        <v>50</v>
+      </c>
+      <c r="R58" s="1475" t="s">
+        <v>161</v>
+      </c>
+      <c r="S58" s="1476" t="s">
+        <v>50</v>
+      </c>
+      <c r="T58" s="1477" t="s">
+        <v>161</v>
+      </c>
+      <c r="U58" s="1478"/>
+      <c r="V58" s="1479"/>
+    </row>
+    <row r="59" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="1480" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="1481">
+        <v>61</v>
+      </c>
+      <c r="D59" s="1482"/>
+      <c r="E59" s="1483">
+        <v>60.8</v>
+      </c>
+      <c r="F59" s="1484"/>
+      <c r="G59" s="1485">
+        <v>9651.33</v>
+      </c>
+      <c r="H59" s="1486"/>
+      <c r="I59" s="1487">
+        <v>432.4</v>
+      </c>
+      <c r="J59" s="1488"/>
+      <c r="K59" s="1489">
+        <v>0</v>
+      </c>
+      <c r="L59" s="1490"/>
+      <c r="M59" s="1491">
+        <v>0</v>
+      </c>
+      <c r="N59" s="1492"/>
+      <c r="O59" s="1493">
+        <v>0</v>
+      </c>
+      <c r="P59" s="1494"/>
+      <c r="Q59" s="1495">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1496">
+        <v>376.5</v>
+      </c>
+      <c r="S59" s="1497">
+        <v>0</v>
+      </c>
+      <c r="T59" s="1498">
+        <v>376.5</v>
+      </c>
+      <c r="U59" s="1499">
+        <v>10205.530000000001</v>
+      </c>
+      <c r="V59" s="1500" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B23" s="1363" t="s">
+    <row r="60" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="1501" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="1364"/>
-      <c r="D23" s="1365"/>
-      <c r="E23" s="1366"/>
-      <c r="F23" s="1367"/>
-      <c r="G23" s="1368"/>
-      <c r="H23" s="1369"/>
-      <c r="I23" s="1370"/>
-      <c r="J23" s="1371"/>
-      <c r="K23" s="1372"/>
-      <c r="L23" s="1373"/>
-      <c r="M23" s="1374"/>
-      <c r="N23" s="1375"/>
-      <c r="O23" s="1376"/>
-      <c r="P23" s="1377"/>
-      <c r="Q23" s="1378">
-        <v>0</v>
-      </c>
-      <c r="R23" s="1379">
-        <v>293.39999999999998</v>
-      </c>
-      <c r="S23" s="1380">
+      <c r="C60" s="1502"/>
+      <c r="D60" s="1503"/>
+      <c r="E60" s="1504"/>
+      <c r="F60" s="1505"/>
+      <c r="G60" s="1506"/>
+      <c r="H60" s="1507"/>
+      <c r="I60" s="1508"/>
+      <c r="J60" s="1509"/>
+      <c r="K60" s="1510"/>
+      <c r="L60" s="1511"/>
+      <c r="M60" s="1512"/>
+      <c r="N60" s="1513"/>
+      <c r="O60" s="1514"/>
+      <c r="P60" s="1515"/>
+      <c r="Q60" s="1516">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1517">
+        <v>1115.3</v>
+      </c>
+      <c r="S60" s="1518">
         <v>200</v>
       </c>
-      <c r="T23" s="1381">
-        <v>293.39999999999998</v>
-      </c>
-      <c r="U23" s="1382"/>
-      <c r="V23" s="1383"/>
-    </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B24" s="1384" t="s">
+      <c r="T60" s="1519">
+        <v>1115.3</v>
+      </c>
+      <c r="U60" s="1520"/>
+      <c r="V60" s="1521"/>
+    </row>
+    <row r="61" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="1522" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="1385">
-        <v>55</v>
-      </c>
-      <c r="D24" s="1386" t="s">
+      <c r="C61" s="1523">
+        <v>61</v>
+      </c>
+      <c r="D61" s="1524" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="1387">
-        <v>120.8</v>
-      </c>
-      <c r="F24" s="1388" t="s">
+      <c r="E61" s="1525">
+        <v>60.8</v>
+      </c>
+      <c r="F61" s="1526" t="s">
         <v>19</v>
       </c>
-      <c r="G24" s="1389">
-        <v>10815.63</v>
-      </c>
-      <c r="H24" s="1390" t="s">
+      <c r="G61" s="1527">
+        <v>9651.33</v>
+      </c>
+      <c r="H61" s="1528" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="1391">
-        <v>36</v>
-      </c>
-      <c r="J24" s="1392" t="s">
+      <c r="I61" s="1529">
+        <v>432.4</v>
+      </c>
+      <c r="J61" s="1530" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="1393">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1394" t="s">
+      <c r="K61" s="1531">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1532" t="s">
         <v>19</v>
       </c>
-      <c r="M24" s="1395">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1396" t="s">
+      <c r="M61" s="1533">
+        <v>0</v>
+      </c>
+      <c r="N61" s="1534" t="s">
         <v>19</v>
       </c>
-      <c r="O24" s="1397">
-        <v>0</v>
-      </c>
-      <c r="P24" s="1398" t="s">
+      <c r="O61" s="1535">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1536" t="s">
         <v>19</v>
       </c>
-      <c r="Q24" s="1399"/>
-      <c r="R24" s="1400"/>
-      <c r="S24" s="1401"/>
-      <c r="T24" s="1402"/>
-      <c r="U24" s="1403">
-        <v>11027.43</v>
-      </c>
-      <c r="V24" s="1404" t="s">
+      <c r="Q61" s="1537"/>
+      <c r="R61" s="1538"/>
+      <c r="S61" s="1539"/>
+      <c r="T61" s="1540"/>
+      <c r="U61" s="1541">
+        <v>10205.530000000001</v>
+      </c>
+      <c r="V61" s="1542" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B25" s="1267" t="s">
+    <row r="62" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="1543" t="s">
+        <v>162</v>
+      </c>
+      <c r="C62" s="1544"/>
+      <c r="D62" s="1545"/>
+      <c r="E62" s="1546"/>
+      <c r="F62" s="1547"/>
+      <c r="G62" s="1548" t="s">
+        <v>163</v>
+      </c>
+      <c r="H62" s="1549" t="s">
+        <v>86</v>
+      </c>
+      <c r="I62" s="1550"/>
+      <c r="J62" s="1551"/>
+      <c r="K62" s="1552"/>
+      <c r="L62" s="1553"/>
+      <c r="M62" s="1554"/>
+      <c r="N62" s="1555"/>
+      <c r="O62" s="1556"/>
+      <c r="P62" s="1557"/>
+      <c r="Q62" s="1558"/>
+      <c r="R62" s="1559"/>
+      <c r="S62" s="1560" t="s">
+        <v>163</v>
+      </c>
+      <c r="T62" s="1561" t="s">
+        <v>86</v>
+      </c>
+      <c r="U62" s="1562"/>
+      <c r="V62" s="1563"/>
+    </row>
+    <row r="63" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="1564"/>
+      <c r="C63" s="1565"/>
+      <c r="D63" s="1566"/>
+      <c r="E63" s="1567"/>
+      <c r="F63" s="1568"/>
+      <c r="G63" s="1569"/>
+      <c r="H63" s="1570"/>
+      <c r="I63" s="1571" t="s">
+        <v>50</v>
+      </c>
+      <c r="J63" s="1572" t="s">
+        <v>136</v>
+      </c>
+      <c r="K63" s="1573"/>
+      <c r="L63" s="1574"/>
+      <c r="M63" s="1575"/>
+      <c r="N63" s="1576"/>
+      <c r="O63" s="1577"/>
+      <c r="P63" s="1578"/>
+      <c r="Q63" s="1579" t="s">
+        <v>50</v>
+      </c>
+      <c r="R63" s="1580" t="s">
+        <v>136</v>
+      </c>
+      <c r="S63" s="1581" t="s">
+        <v>50</v>
+      </c>
+      <c r="T63" s="1582" t="s">
+        <v>136</v>
+      </c>
+      <c r="U63" s="1583"/>
+      <c r="V63" s="1584"/>
+    </row>
+    <row r="64" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="1564"/>
+      <c r="C64" s="1565"/>
+      <c r="D64" s="1566"/>
+      <c r="E64" s="1567"/>
+      <c r="F64" s="1568"/>
+      <c r="G64" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H64" s="1586" t="s">
+        <v>128</v>
+      </c>
+      <c r="I64" s="1587"/>
+      <c r="J64" s="1588"/>
+      <c r="K64" s="1589" t="s">
+        <v>128</v>
+      </c>
+      <c r="L64" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M64" s="1575"/>
+      <c r="N64" s="1576"/>
+      <c r="O64" s="1577"/>
+      <c r="P64" s="1578"/>
+      <c r="Q64" s="1591"/>
+      <c r="R64" s="1592"/>
+      <c r="S64" s="1593"/>
+      <c r="T64" s="1594"/>
+      <c r="U64" s="1583"/>
+      <c r="V64" s="1584"/>
+    </row>
+    <row r="65" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="1564"/>
+      <c r="C65" s="1565"/>
+      <c r="D65" s="1566"/>
+      <c r="E65" s="1567"/>
+      <c r="F65" s="1568"/>
+      <c r="G65" s="1569"/>
+      <c r="H65" s="1570"/>
+      <c r="I65" s="1587"/>
+      <c r="J65" s="1588"/>
+      <c r="K65" s="1589" t="s">
+        <v>46</v>
+      </c>
+      <c r="L65" s="1590" t="s">
+        <v>128</v>
+      </c>
+      <c r="M65" s="1575"/>
+      <c r="N65" s="1576"/>
+      <c r="O65" s="1577"/>
+      <c r="P65" s="1578"/>
+      <c r="Q65" s="1579" t="s">
+        <v>46</v>
+      </c>
+      <c r="R65" s="1580" t="s">
+        <v>128</v>
+      </c>
+      <c r="S65" s="1581" t="s">
+        <v>46</v>
+      </c>
+      <c r="T65" s="1582" t="s">
+        <v>128</v>
+      </c>
+      <c r="U65" s="1583"/>
+      <c r="V65" s="1584"/>
+    </row>
+    <row r="66" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="1564"/>
+      <c r="C66" s="1565"/>
+      <c r="D66" s="1566"/>
+      <c r="E66" s="1567"/>
+      <c r="F66" s="1568"/>
+      <c r="G66" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="1586" t="s">
+        <v>101</v>
+      </c>
+      <c r="I66" s="1587"/>
+      <c r="J66" s="1588"/>
+      <c r="K66" s="1589" t="s">
+        <v>101</v>
+      </c>
+      <c r="L66" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M66" s="1575"/>
+      <c r="N66" s="1576"/>
+      <c r="O66" s="1577"/>
+      <c r="P66" s="1578"/>
+      <c r="Q66" s="1591"/>
+      <c r="R66" s="1592"/>
+      <c r="S66" s="1593"/>
+      <c r="T66" s="1594"/>
+      <c r="U66" s="1583"/>
+      <c r="V66" s="1584"/>
+    </row>
+    <row r="67" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B67" s="1564"/>
+      <c r="C67" s="1565"/>
+      <c r="D67" s="1566"/>
+      <c r="E67" s="1567"/>
+      <c r="F67" s="1568"/>
+      <c r="G67" s="1569"/>
+      <c r="H67" s="1570"/>
+      <c r="I67" s="1587"/>
+      <c r="J67" s="1588"/>
+      <c r="K67" s="1589" t="s">
+        <v>164</v>
+      </c>
+      <c r="L67" s="1590" t="s">
+        <v>101</v>
+      </c>
+      <c r="M67" s="1575"/>
+      <c r="N67" s="1576"/>
+      <c r="O67" s="1577"/>
+      <c r="P67" s="1578"/>
+      <c r="Q67" s="1579" t="s">
+        <v>164</v>
+      </c>
+      <c r="R67" s="1580" t="s">
+        <v>101</v>
+      </c>
+      <c r="S67" s="1581" t="s">
+        <v>164</v>
+      </c>
+      <c r="T67" s="1582" t="s">
+        <v>101</v>
+      </c>
+      <c r="U67" s="1583"/>
+      <c r="V67" s="1584"/>
+    </row>
+    <row r="68" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="1595"/>
+      <c r="C68" s="1596"/>
+      <c r="D68" s="1597"/>
+      <c r="E68" s="1598"/>
+      <c r="F68" s="1599"/>
+      <c r="G68" s="1600"/>
+      <c r="H68" s="1601"/>
+      <c r="I68" s="1602" t="s">
+        <v>50</v>
+      </c>
+      <c r="J68" s="1603" t="s">
+        <v>165</v>
+      </c>
+      <c r="K68" s="1604"/>
+      <c r="L68" s="1605"/>
+      <c r="M68" s="1606"/>
+      <c r="N68" s="1607"/>
+      <c r="O68" s="1608"/>
+      <c r="P68" s="1609"/>
+      <c r="Q68" s="1610" t="s">
+        <v>50</v>
+      </c>
+      <c r="R68" s="1611" t="s">
+        <v>165</v>
+      </c>
+      <c r="S68" s="1612" t="s">
+        <v>50</v>
+      </c>
+      <c r="T68" s="1613" t="s">
+        <v>165</v>
+      </c>
+      <c r="U68" s="1614"/>
+      <c r="V68" s="1615"/>
+    </row>
+    <row r="69" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="1616" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="1617">
+        <v>61</v>
+      </c>
+      <c r="D69" s="1618"/>
+      <c r="E69" s="1619">
+        <v>60.8</v>
+      </c>
+      <c r="F69" s="1620"/>
+      <c r="G69" s="1621">
+        <v>12614.33</v>
+      </c>
+      <c r="H69" s="1622"/>
+      <c r="I69" s="1623">
+        <v>406.6</v>
+      </c>
+      <c r="J69" s="1624"/>
+      <c r="K69" s="1625">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1626"/>
+      <c r="M69" s="1627">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1628"/>
+      <c r="O69" s="1629">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1630"/>
+      <c r="Q69" s="1631">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1632">
+        <v>62.8</v>
+      </c>
+      <c r="S69" s="1633">
+        <v>3000</v>
+      </c>
+      <c r="T69" s="1634">
+        <v>62.8</v>
+      </c>
+      <c r="U69" s="1635">
+        <v>13142.73</v>
+      </c>
+      <c r="V69" s="1636" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="1637" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="1638"/>
+      <c r="D70" s="1639"/>
+      <c r="E70" s="1640"/>
+      <c r="F70" s="1641"/>
+      <c r="G70" s="1642"/>
+      <c r="H70" s="1643"/>
+      <c r="I70" s="1644"/>
+      <c r="J70" s="1645"/>
+      <c r="K70" s="1646"/>
+      <c r="L70" s="1647"/>
+      <c r="M70" s="1648"/>
+      <c r="N70" s="1649"/>
+      <c r="O70" s="1650"/>
+      <c r="P70" s="1651"/>
+      <c r="Q70" s="1652">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1653">
+        <v>1178.0999999999999</v>
+      </c>
+      <c r="S70" s="1654">
+        <v>3200</v>
+      </c>
+      <c r="T70" s="1655">
+        <v>1178.0999999999999</v>
+      </c>
+      <c r="U70" s="1656"/>
+      <c r="V70" s="1657"/>
+    </row>
+    <row r="71" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="1543" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" s="1544"/>
+      <c r="D71" s="1545"/>
+      <c r="E71" s="1546"/>
+      <c r="F71" s="1547"/>
+      <c r="G71" s="1658"/>
+      <c r="H71" s="1659"/>
+      <c r="I71" s="1660" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="1661" t="s">
+        <v>24</v>
+      </c>
+      <c r="K71" s="1552"/>
+      <c r="L71" s="1553"/>
+      <c r="M71" s="1554"/>
+      <c r="N71" s="1555"/>
+      <c r="O71" s="1556"/>
+      <c r="P71" s="1557"/>
+      <c r="Q71" s="1662" t="s">
+        <v>23</v>
+      </c>
+      <c r="R71" s="1663" t="s">
+        <v>24</v>
+      </c>
+      <c r="S71" s="1560" t="s">
+        <v>23</v>
+      </c>
+      <c r="T71" s="1561" t="s">
+        <v>24</v>
+      </c>
+      <c r="U71" s="1562"/>
+      <c r="V71" s="1563"/>
+    </row>
+    <row r="72" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="1564"/>
+      <c r="C72" s="1565"/>
+      <c r="D72" s="1566"/>
+      <c r="E72" s="1567"/>
+      <c r="F72" s="1568"/>
+      <c r="G72" s="1569"/>
+      <c r="H72" s="1570"/>
+      <c r="I72" s="1571" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" s="1572" t="s">
+        <v>26</v>
+      </c>
+      <c r="K72" s="1573"/>
+      <c r="L72" s="1574"/>
+      <c r="M72" s="1575"/>
+      <c r="N72" s="1576"/>
+      <c r="O72" s="1577"/>
+      <c r="P72" s="1578"/>
+      <c r="Q72" s="1579" t="s">
+        <v>25</v>
+      </c>
+      <c r="R72" s="1580" t="s">
+        <v>26</v>
+      </c>
+      <c r="S72" s="1581" t="s">
+        <v>25</v>
+      </c>
+      <c r="T72" s="1582" t="s">
+        <v>26</v>
+      </c>
+      <c r="U72" s="1583"/>
+      <c r="V72" s="1584"/>
+    </row>
+    <row r="73" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="1564"/>
+      <c r="C73" s="1565"/>
+      <c r="D73" s="1566"/>
+      <c r="E73" s="1567"/>
+      <c r="F73" s="1568"/>
+      <c r="G73" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H73" s="1586" t="s">
+        <v>167</v>
+      </c>
+      <c r="I73" s="1587"/>
+      <c r="J73" s="1588"/>
+      <c r="K73" s="1589" t="s">
+        <v>167</v>
+      </c>
+      <c r="L73" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M73" s="1575"/>
+      <c r="N73" s="1576"/>
+      <c r="O73" s="1577"/>
+      <c r="P73" s="1578"/>
+      <c r="Q73" s="1591"/>
+      <c r="R73" s="1592"/>
+      <c r="S73" s="1593"/>
+      <c r="T73" s="1594"/>
+      <c r="U73" s="1583"/>
+      <c r="V73" s="1584"/>
+    </row>
+    <row r="74" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B74" s="1564"/>
+      <c r="C74" s="1565"/>
+      <c r="D74" s="1566"/>
+      <c r="E74" s="1567"/>
+      <c r="F74" s="1568"/>
+      <c r="G74" s="1569"/>
+      <c r="H74" s="1570"/>
+      <c r="I74" s="1587"/>
+      <c r="J74" s="1588"/>
+      <c r="K74" s="1589" t="s">
+        <v>46</v>
+      </c>
+      <c r="L74" s="1590" t="s">
+        <v>167</v>
+      </c>
+      <c r="M74" s="1575"/>
+      <c r="N74" s="1576"/>
+      <c r="O74" s="1577"/>
+      <c r="P74" s="1578"/>
+      <c r="Q74" s="1579" t="s">
+        <v>46</v>
+      </c>
+      <c r="R74" s="1580" t="s">
+        <v>167</v>
+      </c>
+      <c r="S74" s="1581" t="s">
+        <v>46</v>
+      </c>
+      <c r="T74" s="1582" t="s">
+        <v>167</v>
+      </c>
+      <c r="U74" s="1583"/>
+      <c r="V74" s="1584"/>
+    </row>
+    <row r="75" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B75" s="1564"/>
+      <c r="C75" s="1565"/>
+      <c r="D75" s="1566"/>
+      <c r="E75" s="1567"/>
+      <c r="F75" s="1568"/>
+      <c r="G75" s="1585" t="s">
+        <v>168</v>
+      </c>
+      <c r="H75" s="1586" t="s">
+        <v>128</v>
+      </c>
+      <c r="I75" s="1587"/>
+      <c r="J75" s="1588"/>
+      <c r="K75" s="1573"/>
+      <c r="L75" s="1574"/>
+      <c r="M75" s="1575"/>
+      <c r="N75" s="1576"/>
+      <c r="O75" s="1577"/>
+      <c r="P75" s="1578"/>
+      <c r="Q75" s="1579" t="s">
+        <v>168</v>
+      </c>
+      <c r="R75" s="1580" t="s">
+        <v>128</v>
+      </c>
+      <c r="S75" s="1581" t="s">
+        <v>168</v>
+      </c>
+      <c r="T75" s="1582" t="s">
+        <v>128</v>
+      </c>
+      <c r="U75" s="1583"/>
+      <c r="V75" s="1584"/>
+    </row>
+    <row r="76" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B76" s="1564"/>
+      <c r="C76" s="1565"/>
+      <c r="D76" s="1566"/>
+      <c r="E76" s="1567"/>
+      <c r="F76" s="1568"/>
+      <c r="G76" s="1569"/>
+      <c r="H76" s="1570"/>
+      <c r="I76" s="1571" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="1572" t="s">
+        <v>79</v>
+      </c>
+      <c r="K76" s="1573"/>
+      <c r="L76" s="1574"/>
+      <c r="M76" s="1575"/>
+      <c r="N76" s="1576"/>
+      <c r="O76" s="1577"/>
+      <c r="P76" s="1578"/>
+      <c r="Q76" s="1579" t="s">
+        <v>25</v>
+      </c>
+      <c r="R76" s="1580" t="s">
+        <v>79</v>
+      </c>
+      <c r="S76" s="1581" t="s">
+        <v>25</v>
+      </c>
+      <c r="T76" s="1582" t="s">
+        <v>79</v>
+      </c>
+      <c r="U76" s="1583"/>
+      <c r="V76" s="1584"/>
+    </row>
+    <row r="77" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="1564"/>
+      <c r="C77" s="1664" t="s">
+        <v>169</v>
+      </c>
+      <c r="D77" s="1665" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" s="1567"/>
+      <c r="F77" s="1568"/>
+      <c r="G77" s="1569"/>
+      <c r="H77" s="1570"/>
+      <c r="I77" s="1587"/>
+      <c r="J77" s="1588"/>
+      <c r="K77" s="1573"/>
+      <c r="L77" s="1574"/>
+      <c r="M77" s="1575"/>
+      <c r="N77" s="1576"/>
+      <c r="O77" s="1577"/>
+      <c r="P77" s="1578"/>
+      <c r="Q77" s="1579" t="s">
+        <v>169</v>
+      </c>
+      <c r="R77" s="1580" t="s">
+        <v>113</v>
+      </c>
+      <c r="S77" s="1581" t="s">
+        <v>169</v>
+      </c>
+      <c r="T77" s="1582" t="s">
+        <v>113</v>
+      </c>
+      <c r="U77" s="1583"/>
+      <c r="V77" s="1584"/>
+    </row>
+    <row r="78" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="1564"/>
+      <c r="C78" s="1565"/>
+      <c r="D78" s="1566"/>
+      <c r="E78" s="1567"/>
+      <c r="F78" s="1568"/>
+      <c r="G78" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78" s="1586" t="s">
+        <v>170</v>
+      </c>
+      <c r="I78" s="1587"/>
+      <c r="J78" s="1588"/>
+      <c r="K78" s="1589" t="s">
+        <v>170</v>
+      </c>
+      <c r="L78" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="1575"/>
+      <c r="N78" s="1576"/>
+      <c r="O78" s="1577"/>
+      <c r="P78" s="1578"/>
+      <c r="Q78" s="1591"/>
+      <c r="R78" s="1592"/>
+      <c r="S78" s="1593"/>
+      <c r="T78" s="1594"/>
+      <c r="U78" s="1583"/>
+      <c r="V78" s="1584"/>
+    </row>
+    <row r="79" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="1564"/>
+      <c r="C79" s="1565"/>
+      <c r="D79" s="1566"/>
+      <c r="E79" s="1567"/>
+      <c r="F79" s="1568"/>
+      <c r="G79" s="1569"/>
+      <c r="H79" s="1570"/>
+      <c r="I79" s="1587"/>
+      <c r="J79" s="1588"/>
+      <c r="K79" s="1589" t="s">
+        <v>74</v>
+      </c>
+      <c r="L79" s="1590" t="s">
+        <v>170</v>
+      </c>
+      <c r="M79" s="1575"/>
+      <c r="N79" s="1576"/>
+      <c r="O79" s="1577"/>
+      <c r="P79" s="1578"/>
+      <c r="Q79" s="1579" t="s">
+        <v>74</v>
+      </c>
+      <c r="R79" s="1580" t="s">
+        <v>170</v>
+      </c>
+      <c r="S79" s="1581" t="s">
+        <v>74</v>
+      </c>
+      <c r="T79" s="1582" t="s">
+        <v>170</v>
+      </c>
+      <c r="U79" s="1583"/>
+      <c r="V79" s="1584"/>
+    </row>
+    <row r="80" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="1564"/>
+      <c r="C80" s="1565"/>
+      <c r="D80" s="1566"/>
+      <c r="E80" s="1567"/>
+      <c r="F80" s="1568"/>
+      <c r="G80" s="1569"/>
+      <c r="H80" s="1570"/>
+      <c r="I80" s="1571" t="s">
+        <v>50</v>
+      </c>
+      <c r="J80" s="1572" t="s">
+        <v>109</v>
+      </c>
+      <c r="K80" s="1573"/>
+      <c r="L80" s="1574"/>
+      <c r="M80" s="1575"/>
+      <c r="N80" s="1576"/>
+      <c r="O80" s="1577"/>
+      <c r="P80" s="1578"/>
+      <c r="Q80" s="1579" t="s">
+        <v>50</v>
+      </c>
+      <c r="R80" s="1580" t="s">
+        <v>109</v>
+      </c>
+      <c r="S80" s="1581" t="s">
+        <v>50</v>
+      </c>
+      <c r="T80" s="1582" t="s">
+        <v>109</v>
+      </c>
+      <c r="U80" s="1583"/>
+      <c r="V80" s="1584"/>
+    </row>
+    <row r="81" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="1564"/>
+      <c r="C81" s="1565"/>
+      <c r="D81" s="1566"/>
+      <c r="E81" s="1567"/>
+      <c r="F81" s="1568"/>
+      <c r="G81" s="1569"/>
+      <c r="H81" s="1570"/>
+      <c r="I81" s="1571" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="1572" t="s">
+        <v>48</v>
+      </c>
+      <c r="K81" s="1573"/>
+      <c r="L81" s="1574"/>
+      <c r="M81" s="1575"/>
+      <c r="N81" s="1576"/>
+      <c r="O81" s="1577"/>
+      <c r="P81" s="1578"/>
+      <c r="Q81" s="1579" t="s">
+        <v>23</v>
+      </c>
+      <c r="R81" s="1580" t="s">
+        <v>48</v>
+      </c>
+      <c r="S81" s="1581" t="s">
+        <v>23</v>
+      </c>
+      <c r="T81" s="1582" t="s">
+        <v>48</v>
+      </c>
+      <c r="U81" s="1583"/>
+      <c r="V81" s="1584"/>
+    </row>
+    <row r="82" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="1564"/>
+      <c r="C82" s="1565"/>
+      <c r="D82" s="1566"/>
+      <c r="E82" s="1567"/>
+      <c r="F82" s="1568"/>
+      <c r="G82" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H82" s="1586" t="s">
+        <v>171</v>
+      </c>
+      <c r="I82" s="1587"/>
+      <c r="J82" s="1588"/>
+      <c r="K82" s="1589" t="s">
+        <v>171</v>
+      </c>
+      <c r="L82" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M82" s="1575"/>
+      <c r="N82" s="1576"/>
+      <c r="O82" s="1577"/>
+      <c r="P82" s="1578"/>
+      <c r="Q82" s="1591"/>
+      <c r="R82" s="1592"/>
+      <c r="S82" s="1593"/>
+      <c r="T82" s="1594"/>
+      <c r="U82" s="1583"/>
+      <c r="V82" s="1584"/>
+    </row>
+    <row r="83" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="1564"/>
+      <c r="C83" s="1565"/>
+      <c r="D83" s="1566"/>
+      <c r="E83" s="1567"/>
+      <c r="F83" s="1568"/>
+      <c r="G83" s="1569"/>
+      <c r="H83" s="1570"/>
+      <c r="I83" s="1587"/>
+      <c r="J83" s="1588"/>
+      <c r="K83" s="1589" t="s">
+        <v>172</v>
+      </c>
+      <c r="L83" s="1590" t="s">
+        <v>171</v>
+      </c>
+      <c r="M83" s="1575"/>
+      <c r="N83" s="1576"/>
+      <c r="O83" s="1577"/>
+      <c r="P83" s="1578"/>
+      <c r="Q83" s="1579" t="s">
+        <v>172</v>
+      </c>
+      <c r="R83" s="1580" t="s">
+        <v>171</v>
+      </c>
+      <c r="S83" s="1581" t="s">
+        <v>172</v>
+      </c>
+      <c r="T83" s="1582" t="s">
+        <v>171</v>
+      </c>
+      <c r="U83" s="1583"/>
+      <c r="V83" s="1584"/>
+    </row>
+    <row r="84" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B84" s="1564"/>
+      <c r="C84" s="1565"/>
+      <c r="D84" s="1566"/>
+      <c r="E84" s="1567"/>
+      <c r="F84" s="1568"/>
+      <c r="G84" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H84" s="1586" t="s">
+        <v>173</v>
+      </c>
+      <c r="I84" s="1587"/>
+      <c r="J84" s="1588"/>
+      <c r="K84" s="1589" t="s">
+        <v>173</v>
+      </c>
+      <c r="L84" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M84" s="1575"/>
+      <c r="N84" s="1576"/>
+      <c r="O84" s="1577"/>
+      <c r="P84" s="1578"/>
+      <c r="Q84" s="1591"/>
+      <c r="R84" s="1592"/>
+      <c r="S84" s="1593"/>
+      <c r="T84" s="1594"/>
+      <c r="U84" s="1583"/>
+      <c r="V84" s="1584"/>
+    </row>
+    <row r="85" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B85" s="1564"/>
+      <c r="C85" s="1565"/>
+      <c r="D85" s="1566"/>
+      <c r="E85" s="1567"/>
+      <c r="F85" s="1568"/>
+      <c r="G85" s="1569"/>
+      <c r="H85" s="1570"/>
+      <c r="I85" s="1587"/>
+      <c r="J85" s="1588"/>
+      <c r="K85" s="1589" t="s">
+        <v>174</v>
+      </c>
+      <c r="L85" s="1590" t="s">
+        <v>173</v>
+      </c>
+      <c r="M85" s="1575"/>
+      <c r="N85" s="1576"/>
+      <c r="O85" s="1577"/>
+      <c r="P85" s="1578"/>
+      <c r="Q85" s="1579" t="s">
+        <v>174</v>
+      </c>
+      <c r="R85" s="1580" t="s">
+        <v>173</v>
+      </c>
+      <c r="S85" s="1581" t="s">
+        <v>174</v>
+      </c>
+      <c r="T85" s="1582" t="s">
+        <v>173</v>
+      </c>
+      <c r="U85" s="1583"/>
+      <c r="V85" s="1584"/>
+    </row>
+    <row r="86" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B86" s="1564"/>
+      <c r="C86" s="1565"/>
+      <c r="D86" s="1566"/>
+      <c r="E86" s="1567"/>
+      <c r="F86" s="1568"/>
+      <c r="G86" s="1585" t="s">
+        <v>5</v>
+      </c>
+      <c r="H86" s="1586" t="s">
+        <v>175</v>
+      </c>
+      <c r="I86" s="1587"/>
+      <c r="J86" s="1588"/>
+      <c r="K86" s="1589" t="s">
+        <v>175</v>
+      </c>
+      <c r="L86" s="1590" t="s">
+        <v>28</v>
+      </c>
+      <c r="M86" s="1575"/>
+      <c r="N86" s="1576"/>
+      <c r="O86" s="1577"/>
+      <c r="P86" s="1578"/>
+      <c r="Q86" s="1591"/>
+      <c r="R86" s="1592"/>
+      <c r="S86" s="1593"/>
+      <c r="T86" s="1594"/>
+      <c r="U86" s="1583"/>
+      <c r="V86" s="1584"/>
+    </row>
+    <row r="87" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="1564"/>
+      <c r="C87" s="1565"/>
+      <c r="D87" s="1566"/>
+      <c r="E87" s="1567"/>
+      <c r="F87" s="1568"/>
+      <c r="G87" s="1569"/>
+      <c r="H87" s="1570"/>
+      <c r="I87" s="1587"/>
+      <c r="J87" s="1588"/>
+      <c r="K87" s="1589" t="s">
+        <v>176</v>
+      </c>
+      <c r="L87" s="1590" t="s">
+        <v>175</v>
+      </c>
+      <c r="M87" s="1575"/>
+      <c r="N87" s="1576"/>
+      <c r="O87" s="1577"/>
+      <c r="P87" s="1578"/>
+      <c r="Q87" s="1579" t="s">
+        <v>176</v>
+      </c>
+      <c r="R87" s="1580" t="s">
+        <v>175</v>
+      </c>
+      <c r="S87" s="1581" t="s">
+        <v>176</v>
+      </c>
+      <c r="T87" s="1582" t="s">
+        <v>175</v>
+      </c>
+      <c r="U87" s="1583"/>
+      <c r="V87" s="1584"/>
+    </row>
+    <row r="88" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B88" s="1564"/>
+      <c r="C88" s="1565"/>
+      <c r="D88" s="1566"/>
+      <c r="E88" s="1567"/>
+      <c r="F88" s="1568"/>
+      <c r="G88" s="1569"/>
+      <c r="H88" s="1570"/>
+      <c r="I88" s="1571" t="s">
+        <v>177</v>
+      </c>
+      <c r="J88" s="1572" t="s">
+        <v>178</v>
+      </c>
+      <c r="K88" s="1573"/>
+      <c r="L88" s="1574"/>
+      <c r="M88" s="1575"/>
+      <c r="N88" s="1576"/>
+      <c r="O88" s="1577"/>
+      <c r="P88" s="1578"/>
+      <c r="Q88" s="1579" t="s">
+        <v>177</v>
+      </c>
+      <c r="R88" s="1580" t="s">
+        <v>178</v>
+      </c>
+      <c r="S88" s="1581" t="s">
+        <v>177</v>
+      </c>
+      <c r="T88" s="1582" t="s">
+        <v>178</v>
+      </c>
+      <c r="U88" s="1583"/>
+      <c r="V88" s="1584"/>
+    </row>
+    <row r="89" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B89" s="1564"/>
+      <c r="C89" s="1565"/>
+      <c r="D89" s="1566"/>
+      <c r="E89" s="1567"/>
+      <c r="F89" s="1568"/>
+      <c r="G89" s="1585" t="s">
+        <v>33</v>
+      </c>
+      <c r="H89" s="1586" t="s">
+        <v>155</v>
+      </c>
+      <c r="I89" s="1587"/>
+      <c r="J89" s="1588"/>
+      <c r="K89" s="1573"/>
+      <c r="L89" s="1574"/>
+      <c r="M89" s="1575"/>
+      <c r="N89" s="1576"/>
+      <c r="O89" s="1577"/>
+      <c r="P89" s="1578"/>
+      <c r="Q89" s="1579" t="s">
+        <v>33</v>
+      </c>
+      <c r="R89" s="1580" t="s">
+        <v>155</v>
+      </c>
+      <c r="S89" s="1581" t="s">
+        <v>33</v>
+      </c>
+      <c r="T89" s="1582" t="s">
+        <v>155</v>
+      </c>
+      <c r="U89" s="1583"/>
+      <c r="V89" s="1584"/>
+      <c r="W89" s="1098" t="s">
         <v>140</v>
       </c>
-      <c r="C25" s="1268"/>
-      <c r="D25" s="1269"/>
-      <c r="E25" s="1270"/>
-      <c r="F25" s="1271"/>
-      <c r="G25" s="1272" t="s">
+    </row>
+    <row r="90" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B90" s="1564"/>
+      <c r="C90" s="1565"/>
+      <c r="D90" s="1566"/>
+      <c r="E90" s="1567"/>
+      <c r="F90" s="1568"/>
+      <c r="G90" s="1569"/>
+      <c r="H90" s="1570"/>
+      <c r="I90" s="1571" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="1572" t="s">
+        <v>48</v>
+      </c>
+      <c r="K90" s="1573"/>
+      <c r="L90" s="1574"/>
+      <c r="M90" s="1575"/>
+      <c r="N90" s="1576"/>
+      <c r="O90" s="1577"/>
+      <c r="P90" s="1578"/>
+      <c r="Q90" s="1579" t="s">
+        <v>23</v>
+      </c>
+      <c r="R90" s="1580" t="s">
+        <v>48</v>
+      </c>
+      <c r="S90" s="1581" t="s">
+        <v>23</v>
+      </c>
+      <c r="T90" s="1582" t="s">
+        <v>48</v>
+      </c>
+      <c r="U90" s="1583"/>
+      <c r="V90" s="1584"/>
+    </row>
+    <row r="91" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="1595"/>
+      <c r="C91" s="1666" t="s">
+        <v>62</v>
+      </c>
+      <c r="D91" s="1667" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" s="1668" t="s">
+        <v>103</v>
+      </c>
+      <c r="F91" s="1669" t="s">
+        <v>62</v>
+      </c>
+      <c r="G91" s="1600"/>
+      <c r="H91" s="1601"/>
+      <c r="I91" s="1670"/>
+      <c r="J91" s="1671"/>
+      <c r="K91" s="1604"/>
+      <c r="L91" s="1605"/>
+      <c r="M91" s="1606"/>
+      <c r="N91" s="1607"/>
+      <c r="O91" s="1608"/>
+      <c r="P91" s="1609"/>
+      <c r="Q91" s="1672"/>
+      <c r="R91" s="1673"/>
+      <c r="S91" s="1674"/>
+      <c r="T91" s="1675"/>
+      <c r="U91" s="1614"/>
+      <c r="V91" s="1615"/>
+    </row>
+    <row r="92" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B92" s="1616" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" s="1617">
+        <v>60</v>
+      </c>
+      <c r="D92" s="1618"/>
+      <c r="E92" s="1619">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F92" s="1620"/>
+      <c r="G92" s="1621">
+        <v>12197.15</v>
+      </c>
+      <c r="H92" s="1622"/>
+      <c r="I92" s="1623">
+        <v>368.7</v>
+      </c>
+      <c r="J92" s="1624"/>
+      <c r="K92" s="1625">
+        <v>0</v>
+      </c>
+      <c r="L92" s="1626"/>
+      <c r="M92" s="1627">
+        <v>0</v>
+      </c>
+      <c r="N92" s="1628"/>
+      <c r="O92" s="1629">
+        <v>0</v>
+      </c>
+      <c r="P92" s="1630"/>
+      <c r="Q92" s="1631">
+        <v>0</v>
+      </c>
+      <c r="R92" s="1632">
+        <v>484.08</v>
+      </c>
+      <c r="S92" s="1633">
+        <v>0</v>
+      </c>
+      <c r="T92" s="1634">
+        <v>484.08</v>
+      </c>
+      <c r="U92" s="1635">
+        <v>12658.65</v>
+      </c>
+      <c r="V92" s="1636" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="1637" t="s">
+        <v>20</v>
+      </c>
+      <c r="C93" s="1638"/>
+      <c r="D93" s="1639"/>
+      <c r="E93" s="1640"/>
+      <c r="F93" s="1641"/>
+      <c r="G93" s="1642"/>
+      <c r="H93" s="1643"/>
+      <c r="I93" s="1644"/>
+      <c r="J93" s="1645"/>
+      <c r="K93" s="1646"/>
+      <c r="L93" s="1647"/>
+      <c r="M93" s="1648"/>
+      <c r="N93" s="1649"/>
+      <c r="O93" s="1650"/>
+      <c r="P93" s="1651"/>
+      <c r="Q93" s="1652">
+        <v>0</v>
+      </c>
+      <c r="R93" s="1653">
+        <v>1662.18</v>
+      </c>
+      <c r="S93" s="1654">
+        <v>3200</v>
+      </c>
+      <c r="T93" s="1655">
+        <v>1662.18</v>
+      </c>
+      <c r="U93" s="1656"/>
+      <c r="V93" s="1657"/>
+    </row>
+    <row r="94" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B94" s="1676" t="s">
+        <v>21</v>
+      </c>
+      <c r="C94" s="1677">
+        <v>60</v>
+      </c>
+      <c r="D94" s="1678" t="s">
+        <v>19</v>
+      </c>
+      <c r="E94" s="1679">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F94" s="1680" t="s">
+        <v>19</v>
+      </c>
+      <c r="G94" s="1681">
+        <v>12197.15</v>
+      </c>
+      <c r="H94" s="1682" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" s="1683">
+        <v>368.7</v>
+      </c>
+      <c r="J94" s="1684" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="1685">
+        <v>0</v>
+      </c>
+      <c r="L94" s="1686" t="s">
+        <v>19</v>
+      </c>
+      <c r="M94" s="1687">
+        <v>0</v>
+      </c>
+      <c r="N94" s="1688" t="s">
+        <v>19</v>
+      </c>
+      <c r="O94" s="1689">
+        <v>0</v>
+      </c>
+      <c r="P94" s="1690" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q94" s="1691"/>
+      <c r="R94" s="1692"/>
+      <c r="S94" s="1693"/>
+      <c r="T94" s="1694"/>
+      <c r="U94" s="1695">
+        <v>12658.65</v>
+      </c>
+      <c r="V94" s="1696" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B95" s="1697" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="1698"/>
+      <c r="D95" s="1699"/>
+      <c r="E95" s="1700"/>
+      <c r="F95" s="1701"/>
+      <c r="G95" s="1702" t="s">
+        <v>180</v>
+      </c>
+      <c r="H95" s="1703" t="s">
+        <v>151</v>
+      </c>
+      <c r="I95" s="1704"/>
+      <c r="J95" s="1705"/>
+      <c r="K95" s="1706"/>
+      <c r="L95" s="1707"/>
+      <c r="M95" s="1708"/>
+      <c r="N95" s="1709"/>
+      <c r="O95" s="1710"/>
+      <c r="P95" s="1711"/>
+      <c r="Q95" s="1712"/>
+      <c r="R95" s="1713"/>
+      <c r="S95" s="1714" t="s">
+        <v>180</v>
+      </c>
+      <c r="T95" s="1715" t="s">
+        <v>151</v>
+      </c>
+      <c r="U95" s="1716"/>
+      <c r="V95" s="1717"/>
+    </row>
+    <row r="96" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="1718"/>
+      <c r="C96" s="1719"/>
+      <c r="D96" s="1720"/>
+      <c r="E96" s="1721"/>
+      <c r="F96" s="1722"/>
+      <c r="G96" s="1723"/>
+      <c r="H96" s="1724"/>
+      <c r="I96" s="1725" t="s">
+        <v>50</v>
+      </c>
+      <c r="J96" s="1726" t="s">
+        <v>136</v>
+      </c>
+      <c r="K96" s="1727"/>
+      <c r="L96" s="1728"/>
+      <c r="M96" s="1729"/>
+      <c r="N96" s="1730"/>
+      <c r="O96" s="1731"/>
+      <c r="P96" s="1732"/>
+      <c r="Q96" s="1733" t="s">
+        <v>50</v>
+      </c>
+      <c r="R96" s="1734" t="s">
+        <v>136</v>
+      </c>
+      <c r="S96" s="1735" t="s">
+        <v>50</v>
+      </c>
+      <c r="T96" s="1736" t="s">
+        <v>136</v>
+      </c>
+      <c r="U96" s="1737"/>
+      <c r="V96" s="1738"/>
+    </row>
+    <row r="97" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="1718"/>
+      <c r="C97" s="1719"/>
+      <c r="D97" s="1720"/>
+      <c r="E97" s="1721"/>
+      <c r="F97" s="1722"/>
+      <c r="G97" s="1739" t="s">
+        <v>151</v>
+      </c>
+      <c r="H97" s="1740" t="s">
+        <v>180</v>
+      </c>
+      <c r="I97" s="1741"/>
+      <c r="J97" s="1742"/>
+      <c r="K97" s="1727"/>
+      <c r="L97" s="1728"/>
+      <c r="M97" s="1729"/>
+      <c r="N97" s="1730"/>
+      <c r="O97" s="1731"/>
+      <c r="P97" s="1732"/>
+      <c r="Q97" s="1743"/>
+      <c r="R97" s="1744"/>
+      <c r="S97" s="1735" t="s">
+        <v>151</v>
+      </c>
+      <c r="T97" s="1736" t="s">
+        <v>180</v>
+      </c>
+      <c r="U97" s="1737"/>
+      <c r="V97" s="1738"/>
+    </row>
+    <row r="98" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="1718"/>
+      <c r="C98" s="1719"/>
+      <c r="D98" s="1720"/>
+      <c r="E98" s="1721"/>
+      <c r="F98" s="1722"/>
+      <c r="G98" s="1739" t="s">
+        <v>138</v>
+      </c>
+      <c r="H98" s="1740" t="s">
+        <v>113</v>
+      </c>
+      <c r="I98" s="1741"/>
+      <c r="J98" s="1742"/>
+      <c r="K98" s="1727"/>
+      <c r="L98" s="1728"/>
+      <c r="M98" s="1729"/>
+      <c r="N98" s="1730"/>
+      <c r="O98" s="1745" t="s">
+        <v>113</v>
+      </c>
+      <c r="P98" s="1746" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q98" s="1743"/>
+      <c r="R98" s="1744"/>
+      <c r="S98" s="1747"/>
+      <c r="T98" s="1748"/>
+      <c r="U98" s="1737"/>
+      <c r="V98" s="1738"/>
+    </row>
+    <row r="99" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="1718"/>
+      <c r="C99" s="1719"/>
+      <c r="D99" s="1720"/>
+      <c r="E99" s="1721"/>
+      <c r="F99" s="1722"/>
+      <c r="G99" s="1723"/>
+      <c r="H99" s="1724"/>
+      <c r="I99" s="1741"/>
+      <c r="J99" s="1742"/>
+      <c r="K99" s="1727"/>
+      <c r="L99" s="1728"/>
+      <c r="M99" s="1729"/>
+      <c r="N99" s="1730"/>
+      <c r="O99" s="1745" t="s">
+        <v>44</v>
+      </c>
+      <c r="P99" s="1746" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q99" s="1733" t="s">
+        <v>44</v>
+      </c>
+      <c r="R99" s="1734" t="s">
+        <v>113</v>
+      </c>
+      <c r="S99" s="1735" t="s">
+        <v>44</v>
+      </c>
+      <c r="T99" s="1736" t="s">
+        <v>113</v>
+      </c>
+      <c r="U99" s="1737"/>
+      <c r="V99" s="1738"/>
+    </row>
+    <row r="100" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="1749"/>
+      <c r="C100" s="1750"/>
+      <c r="D100" s="1751"/>
+      <c r="E100" s="1752"/>
+      <c r="F100" s="1753"/>
+      <c r="G100" s="1754"/>
+      <c r="H100" s="1755"/>
+      <c r="I100" s="1756" t="s">
+        <v>50</v>
+      </c>
+      <c r="J100" s="1757" t="s">
+        <v>165</v>
+      </c>
+      <c r="K100" s="1758"/>
+      <c r="L100" s="1759"/>
+      <c r="M100" s="1760"/>
+      <c r="N100" s="1761"/>
+      <c r="O100" s="1762"/>
+      <c r="P100" s="1763"/>
+      <c r="Q100" s="1764" t="s">
+        <v>50</v>
+      </c>
+      <c r="R100" s="1765" t="s">
+        <v>165</v>
+      </c>
+      <c r="S100" s="1766" t="s">
+        <v>50</v>
+      </c>
+      <c r="T100" s="1767" t="s">
+        <v>165</v>
+      </c>
+      <c r="U100" s="1768"/>
+      <c r="V100" s="1769"/>
+    </row>
+    <row r="101" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="1770" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="1771">
+        <v>60</v>
+      </c>
+      <c r="D101" s="1772"/>
+      <c r="E101" s="1773">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F101" s="1774"/>
+      <c r="G101" s="1775">
+        <v>12168.15</v>
+      </c>
+      <c r="H101" s="1776"/>
+      <c r="I101" s="1777">
+        <v>342.9</v>
+      </c>
+      <c r="J101" s="1778"/>
+      <c r="K101" s="1779">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1780"/>
+      <c r="M101" s="1781">
+        <v>0</v>
+      </c>
+      <c r="N101" s="1782"/>
+      <c r="O101" s="1783">
+        <v>0</v>
+      </c>
+      <c r="P101" s="1784"/>
+      <c r="Q101" s="1785">
+        <v>0</v>
+      </c>
+      <c r="R101" s="1786">
+        <v>54.8</v>
+      </c>
+      <c r="S101" s="1787">
+        <v>500</v>
+      </c>
+      <c r="T101" s="1788">
+        <v>554.79999999999995</v>
+      </c>
+      <c r="U101" s="1789">
+        <v>12603.85</v>
+      </c>
+      <c r="V101" s="1790" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="1791" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" s="1792"/>
+      <c r="D102" s="1793"/>
+      <c r="E102" s="1794"/>
+      <c r="F102" s="1795"/>
+      <c r="G102" s="1796"/>
+      <c r="H102" s="1797"/>
+      <c r="I102" s="1798"/>
+      <c r="J102" s="1799"/>
+      <c r="K102" s="1800"/>
+      <c r="L102" s="1801"/>
+      <c r="M102" s="1802"/>
+      <c r="N102" s="1803"/>
+      <c r="O102" s="1804"/>
+      <c r="P102" s="1805"/>
+      <c r="Q102" s="1806">
+        <v>0</v>
+      </c>
+      <c r="R102" s="1807">
+        <v>1716.98</v>
+      </c>
+      <c r="S102" s="1808">
+        <v>3700</v>
+      </c>
+      <c r="T102" s="1809">
+        <v>2216.98</v>
+      </c>
+      <c r="U102" s="1810"/>
+      <c r="V102" s="1811"/>
+    </row>
+    <row r="103" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B103" s="1697" t="s">
+        <v>181</v>
+      </c>
+      <c r="C103" s="1698"/>
+      <c r="D103" s="1699"/>
+      <c r="E103" s="1700"/>
+      <c r="F103" s="1701"/>
+      <c r="G103" s="1812"/>
+      <c r="H103" s="1813"/>
+      <c r="I103" s="1814" t="s">
+        <v>50</v>
+      </c>
+      <c r="J103" s="1815" t="s">
+        <v>136</v>
+      </c>
+      <c r="K103" s="1706"/>
+      <c r="L103" s="1707"/>
+      <c r="M103" s="1708"/>
+      <c r="N103" s="1709"/>
+      <c r="O103" s="1710"/>
+      <c r="P103" s="1711"/>
+      <c r="Q103" s="1816" t="s">
+        <v>50</v>
+      </c>
+      <c r="R103" s="1817" t="s">
+        <v>136</v>
+      </c>
+      <c r="S103" s="1714" t="s">
+        <v>50</v>
+      </c>
+      <c r="T103" s="1715" t="s">
+        <v>136</v>
+      </c>
+      <c r="U103" s="1716"/>
+      <c r="V103" s="1717"/>
+    </row>
+    <row r="104" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="1718"/>
+      <c r="C104" s="1719"/>
+      <c r="D104" s="1720"/>
+      <c r="E104" s="1721"/>
+      <c r="F104" s="1722"/>
+      <c r="G104" s="1739" t="s">
+        <v>5</v>
+      </c>
+      <c r="H104" s="1740" t="s">
+        <v>78</v>
+      </c>
+      <c r="I104" s="1741"/>
+      <c r="J104" s="1742"/>
+      <c r="K104" s="1818" t="s">
+        <v>78</v>
+      </c>
+      <c r="L104" s="1819" t="s">
+        <v>28</v>
+      </c>
+      <c r="M104" s="1729"/>
+      <c r="N104" s="1730"/>
+      <c r="O104" s="1731"/>
+      <c r="P104" s="1732"/>
+      <c r="Q104" s="1743"/>
+      <c r="R104" s="1744"/>
+      <c r="S104" s="1747"/>
+      <c r="T104" s="1748"/>
+      <c r="U104" s="1737"/>
+      <c r="V104" s="1738"/>
+    </row>
+    <row r="105" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="1718"/>
+      <c r="C105" s="1719"/>
+      <c r="D105" s="1720"/>
+      <c r="E105" s="1721"/>
+      <c r="F105" s="1722"/>
+      <c r="G105" s="1723"/>
+      <c r="H105" s="1724"/>
+      <c r="I105" s="1741"/>
+      <c r="J105" s="1742"/>
+      <c r="K105" s="1818" t="s">
+        <v>164</v>
+      </c>
+      <c r="L105" s="1819" t="s">
+        <v>78</v>
+      </c>
+      <c r="M105" s="1729"/>
+      <c r="N105" s="1730"/>
+      <c r="O105" s="1731"/>
+      <c r="P105" s="1732"/>
+      <c r="Q105" s="1733" t="s">
+        <v>164</v>
+      </c>
+      <c r="R105" s="1734" t="s">
+        <v>78</v>
+      </c>
+      <c r="S105" s="1735" t="s">
+        <v>164</v>
+      </c>
+      <c r="T105" s="1736" t="s">
+        <v>78</v>
+      </c>
+      <c r="U105" s="1737"/>
+      <c r="V105" s="1738"/>
+    </row>
+    <row r="106" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="1718"/>
+      <c r="C106" s="1719"/>
+      <c r="D106" s="1720"/>
+      <c r="E106" s="1721"/>
+      <c r="F106" s="1722"/>
+      <c r="G106" s="1723"/>
+      <c r="H106" s="1724"/>
+      <c r="I106" s="1725" t="s">
+        <v>50</v>
+      </c>
+      <c r="J106" s="1726" t="s">
+        <v>165</v>
+      </c>
+      <c r="K106" s="1727"/>
+      <c r="L106" s="1728"/>
+      <c r="M106" s="1729"/>
+      <c r="N106" s="1730"/>
+      <c r="O106" s="1731"/>
+      <c r="P106" s="1732"/>
+      <c r="Q106" s="1733" t="s">
+        <v>50</v>
+      </c>
+      <c r="R106" s="1734" t="s">
+        <v>165</v>
+      </c>
+      <c r="S106" s="1735" t="s">
+        <v>50</v>
+      </c>
+      <c r="T106" s="1736" t="s">
+        <v>165</v>
+      </c>
+      <c r="U106" s="1737"/>
+      <c r="V106" s="1738"/>
+    </row>
+    <row r="107" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="1718"/>
+      <c r="C107" s="1719"/>
+      <c r="D107" s="1720"/>
+      <c r="E107" s="1721"/>
+      <c r="F107" s="1722"/>
+      <c r="G107" s="1739" t="s">
+        <v>5</v>
+      </c>
+      <c r="H107" s="1740" t="s">
+        <v>182</v>
+      </c>
+      <c r="I107" s="1741"/>
+      <c r="J107" s="1742"/>
+      <c r="K107" s="1818" t="s">
+        <v>182</v>
+      </c>
+      <c r="L107" s="1819" t="s">
+        <v>28</v>
+      </c>
+      <c r="M107" s="1729"/>
+      <c r="N107" s="1730"/>
+      <c r="O107" s="1731"/>
+      <c r="P107" s="1732"/>
+      <c r="Q107" s="1743"/>
+      <c r="R107" s="1744"/>
+      <c r="S107" s="1747"/>
+      <c r="T107" s="1748"/>
+      <c r="U107" s="1737"/>
+      <c r="V107" s="1738"/>
+    </row>
+    <row r="108" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="1718"/>
+      <c r="C108" s="1719"/>
+      <c r="D108" s="1720"/>
+      <c r="E108" s="1721"/>
+      <c r="F108" s="1722"/>
+      <c r="G108" s="1723"/>
+      <c r="H108" s="1724"/>
+      <c r="I108" s="1741"/>
+      <c r="J108" s="1742"/>
+      <c r="K108" s="1818" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="1273" t="s">
-        <v>141</v>
-      </c>
-      <c r="I25" s="1274"/>
-      <c r="J25" s="1275"/>
-      <c r="K25" s="1405"/>
-      <c r="L25" s="1406"/>
-      <c r="M25" s="1278"/>
-      <c r="N25" s="1279"/>
-      <c r="O25" s="1280"/>
-      <c r="P25" s="1281"/>
-      <c r="Q25" s="1407" t="s">
+      <c r="L108" s="1819" t="s">
+        <v>182</v>
+      </c>
+      <c r="M108" s="1729"/>
+      <c r="N108" s="1730"/>
+      <c r="O108" s="1731"/>
+      <c r="P108" s="1732"/>
+      <c r="Q108" s="1733" t="s">
         <v>33</v>
       </c>
-      <c r="R25" s="1408" t="s">
-        <v>141</v>
-      </c>
-      <c r="S25" s="1409" t="s">
+      <c r="R108" s="1734" t="s">
+        <v>182</v>
+      </c>
+      <c r="S108" s="1735" t="s">
         <v>33</v>
       </c>
-      <c r="T25" s="1410" t="s">
-        <v>141</v>
-      </c>
-      <c r="U25" s="1286"/>
-      <c r="V25" s="1287"/>
-      <c r="W25" s="1120" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B26" s="1288"/>
-      <c r="C26" s="1289"/>
-      <c r="D26" s="1290"/>
-      <c r="E26" s="1291"/>
-      <c r="F26" s="1292"/>
-      <c r="G26" s="1313" t="s">
+      <c r="T108" s="1736" t="s">
+        <v>182</v>
+      </c>
+      <c r="U108" s="1737"/>
+      <c r="V108" s="1738"/>
+      <c r="W108" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="1749"/>
+      <c r="C109" s="1750"/>
+      <c r="D109" s="1751"/>
+      <c r="E109" s="1752"/>
+      <c r="F109" s="1753"/>
+      <c r="G109" s="1754"/>
+      <c r="H109" s="1755"/>
+      <c r="I109" s="1756" t="s">
+        <v>23</v>
+      </c>
+      <c r="J109" s="1757" t="s">
+        <v>48</v>
+      </c>
+      <c r="K109" s="1758"/>
+      <c r="L109" s="1759"/>
+      <c r="M109" s="1760"/>
+      <c r="N109" s="1761"/>
+      <c r="O109" s="1762"/>
+      <c r="P109" s="1763"/>
+      <c r="Q109" s="1764" t="s">
+        <v>23</v>
+      </c>
+      <c r="R109" s="1765" t="s">
+        <v>48</v>
+      </c>
+      <c r="S109" s="1766" t="s">
+        <v>23</v>
+      </c>
+      <c r="T109" s="1767" t="s">
+        <v>48</v>
+      </c>
+      <c r="U109" s="1768"/>
+      <c r="V109" s="1769"/>
+    </row>
+    <row r="110" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="1770" t="s">
+        <v>18</v>
+      </c>
+      <c r="C110" s="1771">
+        <v>60</v>
+      </c>
+      <c r="D110" s="1772"/>
+      <c r="E110" s="1773">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F110" s="1774"/>
+      <c r="G110" s="1775">
+        <v>12045.15</v>
+      </c>
+      <c r="H110" s="1776"/>
+      <c r="I110" s="1777">
+        <v>314.5</v>
+      </c>
+      <c r="J110" s="1778"/>
+      <c r="K110" s="1779">
+        <v>0</v>
+      </c>
+      <c r="L110" s="1780"/>
+      <c r="M110" s="1781">
+        <v>0</v>
+      </c>
+      <c r="N110" s="1782"/>
+      <c r="O110" s="1783">
+        <v>0</v>
+      </c>
+      <c r="P110" s="1784"/>
+      <c r="Q110" s="1785">
+        <v>0</v>
+      </c>
+      <c r="R110" s="1786">
+        <v>151.4</v>
+      </c>
+      <c r="S110" s="1787">
+        <v>0</v>
+      </c>
+      <c r="T110" s="1788">
+        <v>151.4</v>
+      </c>
+      <c r="U110" s="1789">
+        <v>12452.45</v>
+      </c>
+      <c r="V110" s="1790" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="1791" t="s">
+        <v>20</v>
+      </c>
+      <c r="C111" s="1792"/>
+      <c r="D111" s="1793"/>
+      <c r="E111" s="1794"/>
+      <c r="F111" s="1795"/>
+      <c r="G111" s="1796"/>
+      <c r="H111" s="1797"/>
+      <c r="I111" s="1798"/>
+      <c r="J111" s="1799"/>
+      <c r="K111" s="1800"/>
+      <c r="L111" s="1801"/>
+      <c r="M111" s="1802"/>
+      <c r="N111" s="1803"/>
+      <c r="O111" s="1804"/>
+      <c r="P111" s="1805"/>
+      <c r="Q111" s="1806">
+        <v>0</v>
+      </c>
+      <c r="R111" s="1807">
+        <v>1868.38</v>
+      </c>
+      <c r="S111" s="1808">
+        <v>3700</v>
+      </c>
+      <c r="T111" s="1809">
+        <v>2368.38</v>
+      </c>
+      <c r="U111" s="1810"/>
+      <c r="V111" s="1811"/>
+    </row>
+    <row r="112" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B112" s="1820" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="1821">
+        <v>60</v>
+      </c>
+      <c r="D112" s="1822" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" s="1823">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F112" s="1824" t="s">
+        <v>19</v>
+      </c>
+      <c r="G112" s="1825">
+        <v>12045.15</v>
+      </c>
+      <c r="H112" s="1826" t="s">
+        <v>19</v>
+      </c>
+      <c r="I112" s="1827">
+        <v>314.5</v>
+      </c>
+      <c r="J112" s="1828" t="s">
+        <v>19</v>
+      </c>
+      <c r="K112" s="1829">
+        <v>0</v>
+      </c>
+      <c r="L112" s="1830" t="s">
+        <v>19</v>
+      </c>
+      <c r="M112" s="1831">
+        <v>0</v>
+      </c>
+      <c r="N112" s="1832" t="s">
+        <v>19</v>
+      </c>
+      <c r="O112" s="1833">
+        <v>0</v>
+      </c>
+      <c r="P112" s="1834" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q112" s="1835"/>
+      <c r="R112" s="1836"/>
+      <c r="S112" s="1837"/>
+      <c r="T112" s="1838"/>
+      <c r="U112" s="1839">
+        <v>12452.45</v>
+      </c>
+      <c r="V112" s="1840" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B113" s="1841" t="s">
+        <v>183</v>
+      </c>
+      <c r="C113" s="1842"/>
+      <c r="D113" s="1843"/>
+      <c r="E113" s="1844"/>
+      <c r="F113" s="1845"/>
+      <c r="G113" s="1846" t="s">
+        <v>60</v>
+      </c>
+      <c r="H113" s="1847" t="s">
+        <v>61</v>
+      </c>
+      <c r="I113" s="1848"/>
+      <c r="J113" s="1849"/>
+      <c r="K113" s="1850"/>
+      <c r="L113" s="1851"/>
+      <c r="M113" s="1852" t="s">
+        <v>61</v>
+      </c>
+      <c r="N113" s="1853" t="s">
+        <v>28</v>
+      </c>
+      <c r="O113" s="1854"/>
+      <c r="P113" s="1855"/>
+      <c r="Q113" s="1856"/>
+      <c r="R113" s="1857"/>
+      <c r="S113" s="1858"/>
+      <c r="T113" s="1859"/>
+      <c r="U113" s="1860"/>
+      <c r="V113" s="1861"/>
+    </row>
+    <row r="114" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B114" s="1862"/>
+      <c r="C114" s="1863"/>
+      <c r="D114" s="1864"/>
+      <c r="E114" s="1865"/>
+      <c r="F114" s="1866"/>
+      <c r="G114" s="1867" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="1314" t="s">
-        <v>27</v>
-      </c>
-      <c r="I26" s="1295"/>
-      <c r="J26" s="1296"/>
-      <c r="K26" s="1297" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="1298" t="s">
+      <c r="H114" s="1868" t="s">
+        <v>184</v>
+      </c>
+      <c r="I114" s="1869"/>
+      <c r="J114" s="1870"/>
+      <c r="K114" s="1871" t="s">
+        <v>184</v>
+      </c>
+      <c r="L114" s="1872" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="1299"/>
-      <c r="N26" s="1300"/>
-      <c r="O26" s="1301"/>
-      <c r="P26" s="1302"/>
-      <c r="Q26" s="1317"/>
-      <c r="R26" s="1318"/>
-      <c r="S26" s="1319"/>
-      <c r="T26" s="1320"/>
-      <c r="U26" s="1307"/>
-      <c r="V26" s="1308"/>
-    </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B27" s="1321"/>
-      <c r="C27" s="1322"/>
-      <c r="D27" s="1323"/>
-      <c r="E27" s="1324"/>
-      <c r="F27" s="1325"/>
-      <c r="G27" s="1326"/>
-      <c r="H27" s="1327"/>
-      <c r="I27" s="1328"/>
-      <c r="J27" s="1329"/>
-      <c r="K27" s="1330" t="s">
+      <c r="M114" s="1873"/>
+      <c r="N114" s="1874"/>
+      <c r="O114" s="1875"/>
+      <c r="P114" s="1876"/>
+      <c r="Q114" s="1877"/>
+      <c r="R114" s="1878"/>
+      <c r="S114" s="1879"/>
+      <c r="T114" s="1880"/>
+      <c r="U114" s="1881"/>
+      <c r="V114" s="1882"/>
+    </row>
+    <row r="115" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B115" s="1883"/>
+      <c r="C115" s="1884"/>
+      <c r="D115" s="1885"/>
+      <c r="E115" s="1886"/>
+      <c r="F115" s="1887"/>
+      <c r="G115" s="1888"/>
+      <c r="H115" s="1889"/>
+      <c r="I115" s="1890"/>
+      <c r="J115" s="1891"/>
+      <c r="K115" s="1892" t="s">
+        <v>35</v>
+      </c>
+      <c r="L115" s="1893" t="s">
+        <v>184</v>
+      </c>
+      <c r="M115" s="1894"/>
+      <c r="N115" s="1895"/>
+      <c r="O115" s="1896"/>
+      <c r="P115" s="1897"/>
+      <c r="Q115" s="1898" t="s">
+        <v>35</v>
+      </c>
+      <c r="R115" s="1899" t="s">
+        <v>184</v>
+      </c>
+      <c r="S115" s="1900" t="s">
+        <v>35</v>
+      </c>
+      <c r="T115" s="1901" t="s">
+        <v>184</v>
+      </c>
+      <c r="U115" s="1902"/>
+      <c r="V115" s="1903"/>
+    </row>
+    <row r="116" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B116" s="1904" t="s">
+        <v>18</v>
+      </c>
+      <c r="C116" s="1905">
+        <v>60</v>
+      </c>
+      <c r="D116" s="1906"/>
+      <c r="E116" s="1907">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F116" s="1908"/>
+      <c r="G116" s="1909">
+        <v>11922.67</v>
+      </c>
+      <c r="H116" s="1910"/>
+      <c r="I116" s="1911">
+        <v>314.5</v>
+      </c>
+      <c r="J116" s="1912"/>
+      <c r="K116" s="1913">
+        <v>0</v>
+      </c>
+      <c r="L116" s="1914"/>
+      <c r="M116" s="1915">
+        <v>48.48</v>
+      </c>
+      <c r="N116" s="1916"/>
+      <c r="O116" s="1917">
+        <v>0</v>
+      </c>
+      <c r="P116" s="1918"/>
+      <c r="Q116" s="1919">
+        <v>0</v>
+      </c>
+      <c r="R116" s="1920">
+        <v>74</v>
+      </c>
+      <c r="S116" s="1921">
+        <v>0</v>
+      </c>
+      <c r="T116" s="1922">
+        <v>74</v>
+      </c>
+      <c r="U116" s="1923">
+        <v>12378.45</v>
+      </c>
+      <c r="V116" s="1924" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B117" s="1925" t="s">
+        <v>20</v>
+      </c>
+      <c r="C117" s="1926"/>
+      <c r="D117" s="1927"/>
+      <c r="E117" s="1928"/>
+      <c r="F117" s="1929"/>
+      <c r="G117" s="1930"/>
+      <c r="H117" s="1931"/>
+      <c r="I117" s="1932"/>
+      <c r="J117" s="1933"/>
+      <c r="K117" s="1934"/>
+      <c r="L117" s="1935"/>
+      <c r="M117" s="1936"/>
+      <c r="N117" s="1937"/>
+      <c r="O117" s="1938"/>
+      <c r="P117" s="1939"/>
+      <c r="Q117" s="1940">
+        <v>0</v>
+      </c>
+      <c r="R117" s="1941">
+        <v>1942.38</v>
+      </c>
+      <c r="S117" s="1942">
+        <v>3700</v>
+      </c>
+      <c r="T117" s="1943">
+        <v>2442.38</v>
+      </c>
+      <c r="U117" s="1944"/>
+      <c r="V117" s="1945"/>
+    </row>
+    <row r="118" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B118" s="1841" t="s">
+        <v>185</v>
+      </c>
+      <c r="C118" s="1842"/>
+      <c r="D118" s="1843"/>
+      <c r="E118" s="1844"/>
+      <c r="F118" s="1845"/>
+      <c r="G118" s="1946"/>
+      <c r="H118" s="1947"/>
+      <c r="I118" s="1948" t="s">
+        <v>23</v>
+      </c>
+      <c r="J118" s="1949" t="s">
+        <v>48</v>
+      </c>
+      <c r="K118" s="1850"/>
+      <c r="L118" s="1851"/>
+      <c r="M118" s="1950"/>
+      <c r="N118" s="1951"/>
+      <c r="O118" s="1854"/>
+      <c r="P118" s="1855"/>
+      <c r="Q118" s="1952" t="s">
+        <v>23</v>
+      </c>
+      <c r="R118" s="1953" t="s">
+        <v>48</v>
+      </c>
+      <c r="S118" s="1954" t="s">
+        <v>23</v>
+      </c>
+      <c r="T118" s="1955" t="s">
+        <v>48</v>
+      </c>
+      <c r="U118" s="1860"/>
+      <c r="V118" s="1861"/>
+    </row>
+    <row r="119" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B119" s="1862"/>
+      <c r="C119" s="1863"/>
+      <c r="D119" s="1864"/>
+      <c r="E119" s="1865"/>
+      <c r="F119" s="1866"/>
+      <c r="G119" s="1867" t="s">
+        <v>5</v>
+      </c>
+      <c r="H119" s="1868" t="s">
+        <v>145</v>
+      </c>
+      <c r="I119" s="1869"/>
+      <c r="J119" s="1870"/>
+      <c r="K119" s="1871" t="s">
+        <v>145</v>
+      </c>
+      <c r="L119" s="1872" t="s">
+        <v>28</v>
+      </c>
+      <c r="M119" s="1873"/>
+      <c r="N119" s="1874"/>
+      <c r="O119" s="1875"/>
+      <c r="P119" s="1876"/>
+      <c r="Q119" s="1877"/>
+      <c r="R119" s="1878"/>
+      <c r="S119" s="1879"/>
+      <c r="T119" s="1880"/>
+      <c r="U119" s="1881"/>
+      <c r="V119" s="1882"/>
+    </row>
+    <row r="120" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B120" s="1862"/>
+      <c r="C120" s="1863"/>
+      <c r="D120" s="1864"/>
+      <c r="E120" s="1865"/>
+      <c r="F120" s="1866"/>
+      <c r="G120" s="1956"/>
+      <c r="H120" s="1957"/>
+      <c r="I120" s="1869"/>
+      <c r="J120" s="1870"/>
+      <c r="K120" s="1871" t="s">
+        <v>148</v>
+      </c>
+      <c r="L120" s="1872" t="s">
+        <v>145</v>
+      </c>
+      <c r="M120" s="1873"/>
+      <c r="N120" s="1874"/>
+      <c r="O120" s="1875"/>
+      <c r="P120" s="1876"/>
+      <c r="Q120" s="1958" t="s">
+        <v>148</v>
+      </c>
+      <c r="R120" s="1959" t="s">
+        <v>145</v>
+      </c>
+      <c r="S120" s="1960" t="s">
+        <v>148</v>
+      </c>
+      <c r="T120" s="1961" t="s">
+        <v>145</v>
+      </c>
+      <c r="U120" s="1881"/>
+      <c r="V120" s="1882"/>
+    </row>
+    <row r="121" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B121" s="1862"/>
+      <c r="C121" s="1863"/>
+      <c r="D121" s="1864"/>
+      <c r="E121" s="1865"/>
+      <c r="F121" s="1866"/>
+      <c r="G121" s="1867" t="s">
+        <v>5</v>
+      </c>
+      <c r="H121" s="1868" t="s">
+        <v>186</v>
+      </c>
+      <c r="I121" s="1869"/>
+      <c r="J121" s="1870"/>
+      <c r="K121" s="1871" t="s">
+        <v>186</v>
+      </c>
+      <c r="L121" s="1872" t="s">
+        <v>28</v>
+      </c>
+      <c r="M121" s="1873"/>
+      <c r="N121" s="1874"/>
+      <c r="O121" s="1875"/>
+      <c r="P121" s="1876"/>
+      <c r="Q121" s="1877"/>
+      <c r="R121" s="1878"/>
+      <c r="S121" s="1879"/>
+      <c r="T121" s="1880"/>
+      <c r="U121" s="1881"/>
+      <c r="V121" s="1882"/>
+    </row>
+    <row r="122" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B122" s="1862"/>
+      <c r="C122" s="1863"/>
+      <c r="D122" s="1864"/>
+      <c r="E122" s="1865"/>
+      <c r="F122" s="1866"/>
+      <c r="G122" s="1956"/>
+      <c r="H122" s="1957"/>
+      <c r="I122" s="1869"/>
+      <c r="J122" s="1870"/>
+      <c r="K122" s="1871" t="s">
+        <v>33</v>
+      </c>
+      <c r="L122" s="1872" t="s">
+        <v>186</v>
+      </c>
+      <c r="M122" s="1873"/>
+      <c r="N122" s="1874"/>
+      <c r="O122" s="1875"/>
+      <c r="P122" s="1876"/>
+      <c r="Q122" s="1958" t="s">
+        <v>33</v>
+      </c>
+      <c r="R122" s="1959" t="s">
+        <v>186</v>
+      </c>
+      <c r="S122" s="1960" t="s">
+        <v>33</v>
+      </c>
+      <c r="T122" s="1961" t="s">
+        <v>186</v>
+      </c>
+      <c r="U122" s="1881"/>
+      <c r="V122" s="1882"/>
+      <c r="W122" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="123" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B123" s="1883"/>
+      <c r="C123" s="1884"/>
+      <c r="D123" s="1885"/>
+      <c r="E123" s="1886"/>
+      <c r="F123" s="1887"/>
+      <c r="G123" s="1888"/>
+      <c r="H123" s="1889"/>
+      <c r="I123" s="1962" t="s">
+        <v>50</v>
+      </c>
+      <c r="J123" s="1963" t="s">
+        <v>161</v>
+      </c>
+      <c r="K123" s="1964"/>
+      <c r="L123" s="1965"/>
+      <c r="M123" s="1894"/>
+      <c r="N123" s="1895"/>
+      <c r="O123" s="1896"/>
+      <c r="P123" s="1897"/>
+      <c r="Q123" s="1898" t="s">
+        <v>50</v>
+      </c>
+      <c r="R123" s="1899" t="s">
+        <v>161</v>
+      </c>
+      <c r="S123" s="1900" t="s">
+        <v>50</v>
+      </c>
+      <c r="T123" s="1901" t="s">
+        <v>161</v>
+      </c>
+      <c r="U123" s="1902"/>
+      <c r="V123" s="1903"/>
+    </row>
+    <row r="124" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B124" s="1904" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" s="1905">
+        <v>60</v>
+      </c>
+      <c r="D124" s="1906"/>
+      <c r="E124" s="1907">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F124" s="1908"/>
+      <c r="G124" s="1909">
+        <v>11793.67</v>
+      </c>
+      <c r="H124" s="1910"/>
+      <c r="I124" s="1911">
+        <v>306.10000000000002</v>
+      </c>
+      <c r="J124" s="1912"/>
+      <c r="K124" s="1913">
+        <v>0</v>
+      </c>
+      <c r="L124" s="1914"/>
+      <c r="M124" s="1915">
+        <v>48.48</v>
+      </c>
+      <c r="N124" s="1916"/>
+      <c r="O124" s="1917">
+        <v>0</v>
+      </c>
+      <c r="P124" s="1918"/>
+      <c r="Q124" s="1919">
+        <v>0</v>
+      </c>
+      <c r="R124" s="1920">
+        <v>137.4</v>
+      </c>
+      <c r="S124" s="1921">
+        <v>0</v>
+      </c>
+      <c r="T124" s="1922">
+        <v>137.4</v>
+      </c>
+      <c r="U124" s="1923">
+        <v>12241.05</v>
+      </c>
+      <c r="V124" s="1924" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B125" s="1925" t="s">
+        <v>20</v>
+      </c>
+      <c r="C125" s="1926"/>
+      <c r="D125" s="1927"/>
+      <c r="E125" s="1928"/>
+      <c r="F125" s="1929"/>
+      <c r="G125" s="1930"/>
+      <c r="H125" s="1931"/>
+      <c r="I125" s="1932"/>
+      <c r="J125" s="1933"/>
+      <c r="K125" s="1934"/>
+      <c r="L125" s="1935"/>
+      <c r="M125" s="1936"/>
+      <c r="N125" s="1937"/>
+      <c r="O125" s="1938"/>
+      <c r="P125" s="1939"/>
+      <c r="Q125" s="1940">
+        <v>0</v>
+      </c>
+      <c r="R125" s="1941">
+        <v>2079.7800000000002</v>
+      </c>
+      <c r="S125" s="1942">
+        <v>3700</v>
+      </c>
+      <c r="T125" s="1943">
+        <v>2579.7800000000002</v>
+      </c>
+      <c r="U125" s="1944"/>
+      <c r="V125" s="1945"/>
+    </row>
+    <row r="126" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B126" s="1966" t="s">
+        <v>21</v>
+      </c>
+      <c r="C126" s="1967">
+        <v>60</v>
+      </c>
+      <c r="D126" s="1968" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" s="1969">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F126" s="1970" t="s">
+        <v>19</v>
+      </c>
+      <c r="G126" s="1971">
+        <v>11793.67</v>
+      </c>
+      <c r="H126" s="1972" t="s">
+        <v>19</v>
+      </c>
+      <c r="I126" s="1973">
+        <v>306.10000000000002</v>
+      </c>
+      <c r="J126" s="1974" t="s">
+        <v>19</v>
+      </c>
+      <c r="K126" s="1975">
+        <v>0</v>
+      </c>
+      <c r="L126" s="1976" t="s">
+        <v>19</v>
+      </c>
+      <c r="M126" s="1977">
+        <v>48.48</v>
+      </c>
+      <c r="N126" s="1978" t="s">
+        <v>19</v>
+      </c>
+      <c r="O126" s="1979">
+        <v>0</v>
+      </c>
+      <c r="P126" s="1980" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q126" s="1981"/>
+      <c r="R126" s="1982"/>
+      <c r="S126" s="1983"/>
+      <c r="T126" s="1984"/>
+      <c r="U126" s="1985">
+        <v>12241.05</v>
+      </c>
+      <c r="V126" s="1986" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B127" s="1987" t="s">
+        <v>187</v>
+      </c>
+      <c r="C127" s="1988"/>
+      <c r="D127" s="1989"/>
+      <c r="E127" s="1990"/>
+      <c r="F127" s="1991"/>
+      <c r="G127" s="1992" t="s">
+        <v>5</v>
+      </c>
+      <c r="H127" s="1993" t="s">
+        <v>101</v>
+      </c>
+      <c r="I127" s="1994"/>
+      <c r="J127" s="1995"/>
+      <c r="K127" s="1996" t="s">
+        <v>101</v>
+      </c>
+      <c r="L127" s="1997" t="s">
+        <v>28</v>
+      </c>
+      <c r="M127" s="1998"/>
+      <c r="N127" s="1999"/>
+      <c r="O127" s="2000"/>
+      <c r="P127" s="2001"/>
+      <c r="Q127" s="2002"/>
+      <c r="R127" s="2003"/>
+      <c r="S127" s="2004"/>
+      <c r="T127" s="2005"/>
+      <c r="U127" s="2006"/>
+      <c r="V127" s="2007"/>
+    </row>
+    <row r="128" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B128" s="2008"/>
+      <c r="C128" s="2009"/>
+      <c r="D128" s="2010"/>
+      <c r="E128" s="2011"/>
+      <c r="F128" s="2012"/>
+      <c r="G128" s="2013"/>
+      <c r="H128" s="2014"/>
+      <c r="I128" s="2015"/>
+      <c r="J128" s="2016"/>
+      <c r="K128" s="2017" t="s">
         <v>44</v>
       </c>
-      <c r="L27" s="1331" t="s">
-        <v>27</v>
-      </c>
-      <c r="M27" s="1332"/>
-      <c r="N27" s="1333"/>
-      <c r="O27" s="1334"/>
-      <c r="P27" s="1335"/>
-      <c r="Q27" s="1336" t="s">
+      <c r="L128" s="2018" t="s">
+        <v>101</v>
+      </c>
+      <c r="M128" s="2019"/>
+      <c r="N128" s="2020"/>
+      <c r="O128" s="2021"/>
+      <c r="P128" s="2022"/>
+      <c r="Q128" s="2023" t="s">
         <v>44</v>
       </c>
-      <c r="R27" s="1337" t="s">
-        <v>27</v>
-      </c>
-      <c r="S27" s="1338" t="s">
+      <c r="R128" s="2024" t="s">
+        <v>101</v>
+      </c>
+      <c r="S128" s="2025" t="s">
         <v>44</v>
       </c>
-      <c r="T27" s="1339" t="s">
-        <v>27</v>
-      </c>
-      <c r="U27" s="1340"/>
-      <c r="V27" s="1341"/>
-    </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B28" s="1342" t="s">
+      <c r="T128" s="2026" t="s">
+        <v>101</v>
+      </c>
+      <c r="U128" s="2027"/>
+      <c r="V128" s="2028"/>
+    </row>
+    <row r="129" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B129" s="2008"/>
+      <c r="C129" s="2009"/>
+      <c r="D129" s="2010"/>
+      <c r="E129" s="2011"/>
+      <c r="F129" s="2012"/>
+      <c r="G129" s="2013"/>
+      <c r="H129" s="2014"/>
+      <c r="I129" s="2029" t="s">
+        <v>188</v>
+      </c>
+      <c r="J129" s="2030" t="s">
+        <v>150</v>
+      </c>
+      <c r="K129" s="2031"/>
+      <c r="L129" s="2032"/>
+      <c r="M129" s="2019"/>
+      <c r="N129" s="2020"/>
+      <c r="O129" s="2021"/>
+      <c r="P129" s="2022"/>
+      <c r="Q129" s="2023" t="s">
+        <v>188</v>
+      </c>
+      <c r="R129" s="2024" t="s">
+        <v>150</v>
+      </c>
+      <c r="S129" s="2025" t="s">
+        <v>188</v>
+      </c>
+      <c r="T129" s="2026" t="s">
+        <v>150</v>
+      </c>
+      <c r="U129" s="2027"/>
+      <c r="V129" s="2028"/>
+    </row>
+    <row r="130" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B130" s="2008"/>
+      <c r="C130" s="2009"/>
+      <c r="D130" s="2010"/>
+      <c r="E130" s="2011"/>
+      <c r="F130" s="2012"/>
+      <c r="G130" s="2013"/>
+      <c r="H130" s="2014"/>
+      <c r="I130" s="2029" t="s">
+        <v>23</v>
+      </c>
+      <c r="J130" s="2030" t="s">
+        <v>48</v>
+      </c>
+      <c r="K130" s="2031"/>
+      <c r="L130" s="2032"/>
+      <c r="M130" s="2019"/>
+      <c r="N130" s="2020"/>
+      <c r="O130" s="2021"/>
+      <c r="P130" s="2022"/>
+      <c r="Q130" s="2023" t="s">
+        <v>23</v>
+      </c>
+      <c r="R130" s="2024" t="s">
+        <v>48</v>
+      </c>
+      <c r="S130" s="2025" t="s">
+        <v>23</v>
+      </c>
+      <c r="T130" s="2026" t="s">
+        <v>48</v>
+      </c>
+      <c r="U130" s="2027"/>
+      <c r="V130" s="2028"/>
+    </row>
+    <row r="131" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B131" s="2008"/>
+      <c r="C131" s="2009"/>
+      <c r="D131" s="2010"/>
+      <c r="E131" s="2011"/>
+      <c r="F131" s="2012"/>
+      <c r="G131" s="2033" t="s">
+        <v>5</v>
+      </c>
+      <c r="H131" s="2034" t="s">
+        <v>189</v>
+      </c>
+      <c r="I131" s="2015"/>
+      <c r="J131" s="2016"/>
+      <c r="K131" s="2017" t="s">
+        <v>189</v>
+      </c>
+      <c r="L131" s="2018" t="s">
+        <v>28</v>
+      </c>
+      <c r="M131" s="2019"/>
+      <c r="N131" s="2020"/>
+      <c r="O131" s="2021"/>
+      <c r="P131" s="2022"/>
+      <c r="Q131" s="2035"/>
+      <c r="R131" s="2036"/>
+      <c r="S131" s="2037"/>
+      <c r="T131" s="2038"/>
+      <c r="U131" s="2027"/>
+      <c r="V131" s="2028"/>
+    </row>
+    <row r="132" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B132" s="2008"/>
+      <c r="C132" s="2009"/>
+      <c r="D132" s="2010"/>
+      <c r="E132" s="2011"/>
+      <c r="F132" s="2012"/>
+      <c r="G132" s="2013"/>
+      <c r="H132" s="2014"/>
+      <c r="I132" s="2015"/>
+      <c r="J132" s="2016"/>
+      <c r="K132" s="2017" t="s">
+        <v>46</v>
+      </c>
+      <c r="L132" s="2018" t="s">
+        <v>189</v>
+      </c>
+      <c r="M132" s="2019"/>
+      <c r="N132" s="2020"/>
+      <c r="O132" s="2021"/>
+      <c r="P132" s="2022"/>
+      <c r="Q132" s="2023" t="s">
+        <v>46</v>
+      </c>
+      <c r="R132" s="2024" t="s">
+        <v>189</v>
+      </c>
+      <c r="S132" s="2025" t="s">
+        <v>46</v>
+      </c>
+      <c r="T132" s="2026" t="s">
+        <v>189</v>
+      </c>
+      <c r="U132" s="2027"/>
+      <c r="V132" s="2028"/>
+      <c r="W132" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="133" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B133" s="2039"/>
+      <c r="C133" s="2040"/>
+      <c r="D133" s="2041"/>
+      <c r="E133" s="2042"/>
+      <c r="F133" s="2043"/>
+      <c r="G133" s="2044"/>
+      <c r="H133" s="2045"/>
+      <c r="I133" s="2046" t="s">
+        <v>23</v>
+      </c>
+      <c r="J133" s="2047" t="s">
+        <v>48</v>
+      </c>
+      <c r="K133" s="2048"/>
+      <c r="L133" s="2049"/>
+      <c r="M133" s="2050"/>
+      <c r="N133" s="2051"/>
+      <c r="O133" s="2052"/>
+      <c r="P133" s="2053"/>
+      <c r="Q133" s="2054" t="s">
+        <v>23</v>
+      </c>
+      <c r="R133" s="2055" t="s">
+        <v>48</v>
+      </c>
+      <c r="S133" s="2056" t="s">
+        <v>23</v>
+      </c>
+      <c r="T133" s="2057" t="s">
+        <v>48</v>
+      </c>
+      <c r="U133" s="2058"/>
+      <c r="V133" s="2059"/>
+    </row>
+    <row r="134" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B134" s="2060" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="1343">
-        <v>55</v>
-      </c>
-      <c r="D28" s="1344"/>
-      <c r="E28" s="1345">
-        <v>120.8</v>
-      </c>
-      <c r="F28" s="1346"/>
-      <c r="G28" s="1347">
-        <v>10707.63</v>
-      </c>
-      <c r="H28" s="1348"/>
-      <c r="I28" s="1349">
-        <v>36</v>
-      </c>
-      <c r="J28" s="1350"/>
-      <c r="K28" s="1351">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1352"/>
-      <c r="M28" s="1353">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1354"/>
-      <c r="O28" s="1355">
-        <v>0</v>
-      </c>
-      <c r="P28" s="1356"/>
-      <c r="Q28" s="1357">
-        <v>0</v>
-      </c>
-      <c r="R28" s="1358">
-        <v>108</v>
-      </c>
-      <c r="S28" s="1359">
-        <v>0</v>
-      </c>
-      <c r="T28" s="1360">
-        <v>108</v>
-      </c>
-      <c r="U28" s="1361">
-        <v>10919.43</v>
-      </c>
-      <c r="V28" s="1362" t="s">
+      <c r="C134" s="2061">
+        <v>60</v>
+      </c>
+      <c r="D134" s="2062"/>
+      <c r="E134" s="2063">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F134" s="2064"/>
+      <c r="G134" s="2065">
+        <v>11713.17</v>
+      </c>
+      <c r="H134" s="2066"/>
+      <c r="I134" s="2067">
+        <v>280.89999999999998</v>
+      </c>
+      <c r="J134" s="2068"/>
+      <c r="K134" s="2069">
+        <v>0</v>
+      </c>
+      <c r="L134" s="2070"/>
+      <c r="M134" s="2071">
+        <v>48.48</v>
+      </c>
+      <c r="N134" s="2072"/>
+      <c r="O134" s="2073">
+        <v>0</v>
+      </c>
+      <c r="P134" s="2074"/>
+      <c r="Q134" s="2075">
+        <v>0</v>
+      </c>
+      <c r="R134" s="2076">
+        <v>105.7</v>
+      </c>
+      <c r="S134" s="2077">
+        <v>0</v>
+      </c>
+      <c r="T134" s="2078">
+        <v>105.7</v>
+      </c>
+      <c r="U134" s="2079">
+        <v>12135.35</v>
+      </c>
+      <c r="V134" s="2080" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B29" s="1363" t="s">
+    <row r="135" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B135" s="2081" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="1364"/>
-      <c r="D29" s="1365"/>
-      <c r="E29" s="1366"/>
-      <c r="F29" s="1367"/>
-      <c r="G29" s="1368"/>
-      <c r="H29" s="1369"/>
-      <c r="I29" s="1370"/>
-      <c r="J29" s="1371"/>
-      <c r="K29" s="1372"/>
-      <c r="L29" s="1373"/>
-      <c r="M29" s="1374"/>
-      <c r="N29" s="1375"/>
-      <c r="O29" s="1376"/>
-      <c r="P29" s="1377"/>
-      <c r="Q29" s="1378">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1379">
-        <v>401.4</v>
-      </c>
-      <c r="S29" s="1380">
-        <v>200</v>
-      </c>
-      <c r="T29" s="1381">
-        <v>401.4</v>
-      </c>
-      <c r="U29" s="1382"/>
-      <c r="V29" s="1383"/>
-    </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B30" s="1267" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="1268"/>
-      <c r="D30" s="1269"/>
-      <c r="E30" s="1270"/>
-      <c r="F30" s="1271"/>
-      <c r="G30" s="1411"/>
-      <c r="H30" s="1412"/>
-      <c r="I30" s="1413" t="s">
-        <v>23</v>
-      </c>
-      <c r="J30" s="1414" t="s">
-        <v>48</v>
-      </c>
-      <c r="K30" s="1405"/>
-      <c r="L30" s="1406"/>
-      <c r="M30" s="1278"/>
-      <c r="N30" s="1279"/>
-      <c r="O30" s="1280"/>
-      <c r="P30" s="1281"/>
-      <c r="Q30" s="1407" t="s">
-        <v>23</v>
-      </c>
-      <c r="R30" s="1408" t="s">
-        <v>48</v>
-      </c>
-      <c r="S30" s="1409" t="s">
-        <v>23</v>
-      </c>
-      <c r="T30" s="1410" t="s">
-        <v>48</v>
-      </c>
-      <c r="U30" s="1286"/>
-      <c r="V30" s="1287"/>
-    </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B31" s="1288"/>
-      <c r="C31" s="1289"/>
-      <c r="D31" s="1290"/>
-      <c r="E31" s="1291"/>
-      <c r="F31" s="1292"/>
-      <c r="G31" s="1313" t="s">
-        <v>5</v>
-      </c>
-      <c r="H31" s="1314" t="s">
-        <v>143</v>
-      </c>
-      <c r="I31" s="1295"/>
-      <c r="J31" s="1296"/>
-      <c r="K31" s="1297" t="s">
-        <v>143</v>
-      </c>
-      <c r="L31" s="1298" t="s">
-        <v>28</v>
-      </c>
-      <c r="M31" s="1299"/>
-      <c r="N31" s="1300"/>
-      <c r="O31" s="1301"/>
-      <c r="P31" s="1302"/>
-      <c r="Q31" s="1317"/>
-      <c r="R31" s="1318"/>
-      <c r="S31" s="1319"/>
-      <c r="T31" s="1320"/>
-      <c r="U31" s="1307"/>
-      <c r="V31" s="1308"/>
-    </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B32" s="1288"/>
-      <c r="C32" s="1289"/>
-      <c r="D32" s="1290"/>
-      <c r="E32" s="1291"/>
-      <c r="F32" s="1292"/>
-      <c r="G32" s="1293"/>
-      <c r="H32" s="1294"/>
-      <c r="I32" s="1295"/>
-      <c r="J32" s="1296"/>
-      <c r="K32" s="1297" t="s">
-        <v>29</v>
-      </c>
-      <c r="L32" s="1298" t="s">
-        <v>143</v>
-      </c>
-      <c r="M32" s="1299"/>
-      <c r="N32" s="1300"/>
-      <c r="O32" s="1301"/>
-      <c r="P32" s="1302"/>
-      <c r="Q32" s="1303" t="s">
-        <v>29</v>
-      </c>
-      <c r="R32" s="1304" t="s">
-        <v>143</v>
-      </c>
-      <c r="S32" s="1305" t="s">
-        <v>29</v>
-      </c>
-      <c r="T32" s="1306" t="s">
-        <v>143</v>
-      </c>
-      <c r="U32" s="1307"/>
-      <c r="V32" s="1308"/>
-      <c r="W32" s="1120" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B33" s="1288"/>
-      <c r="C33" s="1415" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="1416" t="s">
-        <v>144</v>
-      </c>
-      <c r="E33" s="1291"/>
-      <c r="F33" s="1292"/>
-      <c r="G33" s="1293"/>
-      <c r="H33" s="1294"/>
-      <c r="I33" s="1295"/>
-      <c r="J33" s="1296"/>
-      <c r="K33" s="1311"/>
-      <c r="L33" s="1312"/>
-      <c r="M33" s="1299"/>
-      <c r="N33" s="1300"/>
-      <c r="O33" s="1301"/>
-      <c r="P33" s="1302"/>
-      <c r="Q33" s="1303" t="s">
-        <v>44</v>
-      </c>
-      <c r="R33" s="1304" t="s">
-        <v>144</v>
-      </c>
-      <c r="S33" s="1305" t="s">
-        <v>44</v>
-      </c>
-      <c r="T33" s="1306" t="s">
-        <v>144</v>
-      </c>
-      <c r="U33" s="1307"/>
-      <c r="V33" s="1308"/>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B34" s="1288"/>
-      <c r="C34" s="1289"/>
-      <c r="D34" s="1290"/>
-      <c r="E34" s="1291"/>
-      <c r="F34" s="1292"/>
-      <c r="G34" s="1313" t="s">
-        <v>5</v>
-      </c>
-      <c r="H34" s="1314" t="s">
-        <v>145</v>
-      </c>
-      <c r="I34" s="1295"/>
-      <c r="J34" s="1296"/>
-      <c r="K34" s="1297" t="s">
-        <v>145</v>
-      </c>
-      <c r="L34" s="1298" t="s">
-        <v>28</v>
-      </c>
-      <c r="M34" s="1299"/>
-      <c r="N34" s="1300"/>
-      <c r="O34" s="1301"/>
-      <c r="P34" s="1302"/>
-      <c r="Q34" s="1317"/>
-      <c r="R34" s="1318"/>
-      <c r="S34" s="1319"/>
-      <c r="T34" s="1320"/>
-      <c r="U34" s="1307"/>
-      <c r="V34" s="1308"/>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B35" s="1288"/>
-      <c r="C35" s="1289"/>
-      <c r="D35" s="1290"/>
-      <c r="E35" s="1291"/>
-      <c r="F35" s="1292"/>
-      <c r="G35" s="1293"/>
-      <c r="H35" s="1294"/>
-      <c r="I35" s="1295"/>
-      <c r="J35" s="1296"/>
-      <c r="K35" s="1297" t="s">
-        <v>146</v>
-      </c>
-      <c r="L35" s="1298" t="s">
-        <v>145</v>
-      </c>
-      <c r="M35" s="1299"/>
-      <c r="N35" s="1300"/>
-      <c r="O35" s="1301"/>
-      <c r="P35" s="1302"/>
-      <c r="Q35" s="1303" t="s">
-        <v>146</v>
-      </c>
-      <c r="R35" s="1304" t="s">
-        <v>145</v>
-      </c>
-      <c r="S35" s="1305" t="s">
-        <v>146</v>
-      </c>
-      <c r="T35" s="1306" t="s">
-        <v>145</v>
-      </c>
-      <c r="U35" s="1307"/>
-      <c r="V35" s="1308"/>
-    </row>
-    <row r="36" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B36" s="1288"/>
-      <c r="C36" s="1415" t="s">
-        <v>147</v>
-      </c>
-      <c r="D36" s="1416" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="1291"/>
-      <c r="F36" s="1292"/>
-      <c r="G36" s="1293"/>
-      <c r="H36" s="1294"/>
-      <c r="I36" s="1295"/>
-      <c r="J36" s="1296"/>
-      <c r="K36" s="1311"/>
-      <c r="L36" s="1312"/>
-      <c r="M36" s="1299"/>
-      <c r="N36" s="1300"/>
-      <c r="O36" s="1301"/>
-      <c r="P36" s="1302"/>
-      <c r="Q36" s="1303" t="s">
-        <v>147</v>
-      </c>
-      <c r="R36" s="1304" t="s">
-        <v>148</v>
-      </c>
-      <c r="S36" s="1305" t="s">
-        <v>147</v>
-      </c>
-      <c r="T36" s="1306" t="s">
-        <v>148</v>
-      </c>
-      <c r="U36" s="1307"/>
-      <c r="V36" s="1308"/>
-      <c r="W36" s="1120" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B37" s="1288"/>
-      <c r="C37" s="1289"/>
-      <c r="D37" s="1290"/>
-      <c r="E37" s="1291"/>
-      <c r="F37" s="1292"/>
-      <c r="G37" s="1293"/>
-      <c r="H37" s="1294"/>
-      <c r="I37" s="1309" t="s">
-        <v>120</v>
-      </c>
-      <c r="J37" s="1310" t="s">
-        <v>149</v>
-      </c>
-      <c r="K37" s="1311"/>
-      <c r="L37" s="1312"/>
-      <c r="M37" s="1299"/>
-      <c r="N37" s="1300"/>
-      <c r="O37" s="1301"/>
-      <c r="P37" s="1302"/>
-      <c r="Q37" s="1303" t="s">
-        <v>120</v>
-      </c>
-      <c r="R37" s="1304" t="s">
-        <v>149</v>
-      </c>
-      <c r="S37" s="1305" t="s">
-        <v>120</v>
-      </c>
-      <c r="T37" s="1306" t="s">
-        <v>149</v>
-      </c>
-      <c r="U37" s="1307"/>
-      <c r="V37" s="1308"/>
-    </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B38" s="1288"/>
-      <c r="C38" s="1289"/>
-      <c r="D38" s="1290"/>
-      <c r="E38" s="1291"/>
-      <c r="F38" s="1292"/>
-      <c r="G38" s="1313" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" s="1314" t="s">
-        <v>150</v>
-      </c>
-      <c r="I38" s="1309" t="s">
-        <v>150</v>
-      </c>
-      <c r="J38" s="1310" t="s">
-        <v>28</v>
-      </c>
-      <c r="K38" s="1311"/>
-      <c r="L38" s="1312"/>
-      <c r="M38" s="1299"/>
-      <c r="N38" s="1300"/>
-      <c r="O38" s="1301"/>
-      <c r="P38" s="1302"/>
-      <c r="Q38" s="1317"/>
-      <c r="R38" s="1318"/>
-      <c r="S38" s="1319"/>
-      <c r="T38" s="1320"/>
-      <c r="U38" s="1307"/>
-      <c r="V38" s="1308"/>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B39" s="1288"/>
-      <c r="C39" s="1289"/>
-      <c r="D39" s="1290"/>
-      <c r="E39" s="1291"/>
-      <c r="F39" s="1292"/>
-      <c r="G39" s="1293"/>
-      <c r="H39" s="1294"/>
-      <c r="I39" s="1309" t="s">
-        <v>25</v>
-      </c>
-      <c r="J39" s="1310" t="s">
-        <v>151</v>
-      </c>
-      <c r="K39" s="1311"/>
-      <c r="L39" s="1312"/>
-      <c r="M39" s="1299"/>
-      <c r="N39" s="1300"/>
-      <c r="O39" s="1301"/>
-      <c r="P39" s="1302"/>
-      <c r="Q39" s="1303" t="s">
-        <v>25</v>
-      </c>
-      <c r="R39" s="1304" t="s">
-        <v>151</v>
-      </c>
-      <c r="S39" s="1305" t="s">
-        <v>25</v>
-      </c>
-      <c r="T39" s="1306" t="s">
-        <v>151</v>
-      </c>
-      <c r="U39" s="1307"/>
-      <c r="V39" s="1308"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B40" s="1288"/>
-      <c r="C40" s="1289"/>
-      <c r="D40" s="1290"/>
-      <c r="E40" s="1291"/>
-      <c r="F40" s="1292"/>
-      <c r="G40" s="1313" t="s">
-        <v>5</v>
-      </c>
-      <c r="H40" s="1314" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="1295"/>
-      <c r="J40" s="1296"/>
-      <c r="K40" s="1297" t="s">
-        <v>152</v>
-      </c>
-      <c r="L40" s="1298" t="s">
-        <v>28</v>
-      </c>
-      <c r="M40" s="1299"/>
-      <c r="N40" s="1300"/>
-      <c r="O40" s="1301"/>
-      <c r="P40" s="1302"/>
-      <c r="Q40" s="1317"/>
-      <c r="R40" s="1318"/>
-      <c r="S40" s="1319"/>
-      <c r="T40" s="1320"/>
-      <c r="U40" s="1307"/>
-      <c r="V40" s="1308"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B41" s="1288"/>
-      <c r="C41" s="1289"/>
-      <c r="D41" s="1290"/>
-      <c r="E41" s="1291"/>
-      <c r="F41" s="1292"/>
-      <c r="G41" s="1293"/>
-      <c r="H41" s="1294"/>
-      <c r="I41" s="1295"/>
-      <c r="J41" s="1296"/>
-      <c r="K41" s="1297" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="1298" t="s">
-        <v>152</v>
-      </c>
-      <c r="M41" s="1299"/>
-      <c r="N41" s="1300"/>
-      <c r="O41" s="1301"/>
-      <c r="P41" s="1302"/>
-      <c r="Q41" s="1303" t="s">
-        <v>46</v>
-      </c>
-      <c r="R41" s="1304" t="s">
-        <v>152</v>
-      </c>
-      <c r="S41" s="1305" t="s">
-        <v>46</v>
-      </c>
-      <c r="T41" s="1306" t="s">
-        <v>152</v>
-      </c>
-      <c r="U41" s="1307"/>
-      <c r="V41" s="1308"/>
-      <c r="W41" s="1120" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B42" s="1288"/>
-      <c r="C42" s="1289"/>
-      <c r="D42" s="1290"/>
-      <c r="E42" s="1291"/>
-      <c r="F42" s="1292"/>
-      <c r="G42" s="1293"/>
-      <c r="H42" s="1294"/>
-      <c r="I42" s="1309" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="1310" t="s">
-        <v>153</v>
-      </c>
-      <c r="K42" s="1311"/>
-      <c r="L42" s="1312"/>
-      <c r="M42" s="1299"/>
-      <c r="N42" s="1300"/>
-      <c r="O42" s="1301"/>
-      <c r="P42" s="1302"/>
-      <c r="Q42" s="1303" t="s">
-        <v>23</v>
-      </c>
-      <c r="R42" s="1304" t="s">
-        <v>153</v>
-      </c>
-      <c r="S42" s="1305" t="s">
-        <v>23</v>
-      </c>
-      <c r="T42" s="1306" t="s">
-        <v>153</v>
-      </c>
-      <c r="U42" s="1307"/>
-      <c r="V42" s="1308"/>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B43" s="1321"/>
-      <c r="C43" s="1417" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="1418" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" s="1419" t="s">
-        <v>103</v>
-      </c>
-      <c r="F43" s="1420" t="s">
-        <v>154</v>
-      </c>
-      <c r="G43" s="1326"/>
-      <c r="H43" s="1327"/>
-      <c r="I43" s="1328"/>
-      <c r="J43" s="1329"/>
-      <c r="K43" s="1421"/>
-      <c r="L43" s="1422"/>
-      <c r="M43" s="1332"/>
-      <c r="N43" s="1333"/>
-      <c r="O43" s="1334"/>
-      <c r="P43" s="1335"/>
-      <c r="Q43" s="1423"/>
-      <c r="R43" s="1424"/>
-      <c r="S43" s="1425"/>
-      <c r="T43" s="1426"/>
-      <c r="U43" s="1340"/>
-      <c r="V43" s="1341"/>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B44" s="1342" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" s="1343">
-        <v>75</v>
-      </c>
-      <c r="D44" s="1344"/>
-      <c r="E44" s="1345">
-        <v>60.8</v>
-      </c>
-      <c r="F44" s="1346"/>
-      <c r="G44" s="1347">
-        <v>9939.33</v>
-      </c>
-      <c r="H44" s="1348"/>
-      <c r="I44" s="1349">
-        <v>506.9</v>
-      </c>
-      <c r="J44" s="1350"/>
-      <c r="K44" s="1351">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1352"/>
-      <c r="M44" s="1353">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1354"/>
-      <c r="O44" s="1355">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1356"/>
-      <c r="Q44" s="1357">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1358">
-        <v>337.4</v>
-      </c>
-      <c r="S44" s="1359">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1360">
-        <v>337.4</v>
-      </c>
-      <c r="U44" s="1361">
-        <v>10582.03</v>
-      </c>
-      <c r="V44" s="1362" t="s">
+      <c r="C135" s="2082"/>
+      <c r="D135" s="2083"/>
+      <c r="E135" s="2084"/>
+      <c r="F135" s="2085"/>
+      <c r="G135" s="2086"/>
+      <c r="H135" s="2087"/>
+      <c r="I135" s="2088"/>
+      <c r="J135" s="2089"/>
+      <c r="K135" s="2090"/>
+      <c r="L135" s="2091"/>
+      <c r="M135" s="2092"/>
+      <c r="N135" s="2093"/>
+      <c r="O135" s="2094"/>
+      <c r="P135" s="2095"/>
+      <c r="Q135" s="2096">
+        <v>0</v>
+      </c>
+      <c r="R135" s="2097">
+        <v>2185.48</v>
+      </c>
+      <c r="S135" s="2098">
+        <v>3700</v>
+      </c>
+      <c r="T135" s="2099">
+        <v>2685.48</v>
+      </c>
+      <c r="U135" s="2100"/>
+      <c r="V135" s="2101"/>
+    </row>
+    <row r="136" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B136" s="2102" t="s">
+        <v>21</v>
+      </c>
+      <c r="C136" s="2103">
+        <v>60</v>
+      </c>
+      <c r="D136" s="2104" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B45" s="1363" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1364"/>
-      <c r="D45" s="1365"/>
-      <c r="E45" s="1366"/>
-      <c r="F45" s="1367"/>
-      <c r="G45" s="1368"/>
-      <c r="H45" s="1369"/>
-      <c r="I45" s="1370"/>
-      <c r="J45" s="1371"/>
-      <c r="K45" s="1372"/>
-      <c r="L45" s="1373"/>
-      <c r="M45" s="1374"/>
-      <c r="N45" s="1375"/>
-      <c r="O45" s="1376"/>
-      <c r="P45" s="1377"/>
-      <c r="Q45" s="1378">
-        <v>0</v>
-      </c>
-      <c r="R45" s="1379">
-        <v>738.8</v>
-      </c>
-      <c r="S45" s="1380">
-        <v>200</v>
-      </c>
-      <c r="T45" s="1381">
-        <v>738.8</v>
-      </c>
-      <c r="U45" s="1382"/>
-      <c r="V45" s="1383"/>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.25">
-      <c r="B46" s="1384" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="1385">
-        <v>75</v>
-      </c>
-      <c r="D46" s="1386" t="s">
+      <c r="E136" s="2105">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F136" s="2106" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="1387">
-        <v>60.8</v>
-      </c>
-      <c r="F46" s="1388" t="s">
+      <c r="G136" s="2107">
+        <v>11713.17</v>
+      </c>
+      <c r="H136" s="2108" t="s">
         <v>19</v>
       </c>
-      <c r="G46" s="1389">
-        <v>9939.33</v>
-      </c>
-      <c r="H46" s="1390" t="s">
+      <c r="I136" s="2109">
+        <v>280.89999999999998</v>
+      </c>
+      <c r="J136" s="2110" t="s">
         <v>19</v>
       </c>
-      <c r="I46" s="1391">
-        <v>506.9</v>
-      </c>
-      <c r="J46" s="1392" t="s">
+      <c r="K136" s="2111">
+        <v>0</v>
+      </c>
+      <c r="L136" s="2112" t="s">
         <v>19</v>
       </c>
-      <c r="K46" s="1393">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1394" t="s">
+      <c r="M136" s="2113">
+        <v>48.48</v>
+      </c>
+      <c r="N136" s="2114" t="s">
         <v>19</v>
       </c>
-      <c r="M46" s="1395">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1396" t="s">
+      <c r="O136" s="2115">
+        <v>0</v>
+      </c>
+      <c r="P136" s="2116" t="s">
         <v>19</v>
       </c>
-      <c r="O46" s="1397">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1398" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q46" s="1399"/>
-      <c r="R46" s="1400"/>
-      <c r="S46" s="1401"/>
-      <c r="T46" s="1402"/>
-      <c r="U46" s="1403">
-        <v>10582.03</v>
-      </c>
-      <c r="V46" s="1404" t="s">
+      <c r="Q136" s="2117"/>
+      <c r="R136" s="2118"/>
+      <c r="S136" s="2119"/>
+      <c r="T136" s="2120"/>
+      <c r="U136" s="2121">
+        <v>12135.35</v>
+      </c>
+      <c r="V136" s="2122" t="s">
         <v>19</v>
       </c>
     </row>
@@ -16313,6 +22489,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/output/2026/money/money.xlsx
+++ b/output/2026/money/money.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="211">
   <si>
     <t>Date</t>
   </si>
@@ -592,6 +592,69 @@
   <si>
     <t>70.5</t>
   </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>45.5</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>13.44</t>
+  </si>
+  <si>
+    <t>work</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27.13</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>18/07/2026</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>19.9</t>
+  </si>
+  <si>
+    <t>mini-food</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>piggy-play</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>Chinese Herbal Jelly</t>
+  </si>
 </sst>
 </file>
 
@@ -641,7 +704,7 @@
       <name val="Book Antiqua"/>
     </font>
   </fonts>
-  <fills count="143">
+  <fills count="173">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1364,8 +1427,158 @@
         <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5D9F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDD9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBDBD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="341">
+  <borders count="413">
     <border>
       <left/>
       <right/>
@@ -4297,6 +4510,1086 @@
     <border>
       <left/>
       <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -6470,7 +7763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2143">
+  <cellXfs count="2577">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -8774,60 +10067,494 @@
     <xf numFmtId="0" fontId="0" fillId="141" borderId="340" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="141" borderId="339" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="142" borderId="337" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="195" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="8" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="22" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="9" borderId="313" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="341" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="342" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="343" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="342" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="343" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="150" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="150" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="344" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="152" borderId="341" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="346" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="347" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="346" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="347" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="346" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="348" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="152" borderId="345" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="346" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="347" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="346" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="347" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="150" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="150" borderId="347" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="346" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="348" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="350" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="350" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="350" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="350" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="351" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="350" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="350" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="350" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="350" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="351" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="350" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="352" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="351" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="152" borderId="349" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="353" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="143" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="144" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="148" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="149" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="355" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="355" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="354" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="356" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="355" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="152" borderId="353" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="357" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="143" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="144" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="146" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="148" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="358" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="149" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="358" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="359" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="358" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="360" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="359" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="152" borderId="357" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="145" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="342" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="343" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="342" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="147" borderId="343" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="342" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="150" borderId="343" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="342" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="344" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="361" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="143" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="143" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="144" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="144" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="145" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="146" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="147" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="148" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="148" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="149" borderId="362" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="149" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="150" borderId="362" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="150" borderId="363" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="362" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="151" borderId="364" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="151" borderId="363" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="152" borderId="361" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="365" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="366" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="367" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="366" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="367" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="366" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="368" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="162" borderId="365" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="370" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="371" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="370" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="371" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="160" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="160" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="372" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="162" borderId="369" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="370" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="371" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="370" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="372" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="370" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="371" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="370" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="371" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="373" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="158" borderId="374" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="158" borderId="375" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="374" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="375" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="374" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="376" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="162" borderId="373" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="377" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="153" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="154" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="158" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="159" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="379" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="379" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="378" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="380" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="379" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="162" borderId="377" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="381" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="153" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="154" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="155" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="157" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="382" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="159" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="382" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="160" borderId="383" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="382" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="384" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="383" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="162" borderId="381" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="385" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="153" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="153" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="154" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="154" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="156" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="158" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="158" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="159" borderId="386" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="159" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="160" borderId="386" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="160" borderId="387" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="386" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="388" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="161" borderId="387" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="162" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="366" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="155" borderId="367" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="156" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="366" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="367" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="160" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="160" borderId="367" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="366" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="161" borderId="368" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="159" borderId="370" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="159" borderId="371" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="374" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="157" borderId="375" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="374" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="158" borderId="375" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="389" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="390" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="391" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="390" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="391" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="390" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="391" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="390" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="391" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="390" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="391" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="390" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="391" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="390" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="391" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="390" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="391" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="390" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="392" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="172" borderId="389" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="165" borderId="394" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="165" borderId="395" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="166" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="166" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="167" borderId="394" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="167" borderId="395" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="170" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="170" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="396" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="172" borderId="393" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="394" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="395" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="394" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="396" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="394" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="395" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="394" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="395" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="397" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="398" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="398" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="398" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="398" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="399" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="398" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="398" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="398" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="398" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="399" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="398" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="400" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="399" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="172" borderId="397" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="401" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="163" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="164" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="165" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="166" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="167" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="168" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="169" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="403" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="403" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="402" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="404" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="403" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="172" borderId="401" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="405" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="163" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="164" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="165" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="166" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="166" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="167" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="168" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="406" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="169" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="406" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="170" borderId="407" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="406" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="408" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="407" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="172" borderId="405" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="409" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="163" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="163" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="164" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="164" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="165" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="165" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="166" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="167" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="167" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="168" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="168" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="169" borderId="410" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="169" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="170" borderId="410" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="170" borderId="411" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="410" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="171" borderId="412" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="171" borderId="411" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="172" borderId="409" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="9" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="196" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="79" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="195" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="22" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="385" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="81" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="78" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="79" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="80" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="78" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="73" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="80" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="75" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="73" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="74" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="75" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="77" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="74" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="76" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="77" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="81" borderId="313" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="76" borderId="385" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -9151,8 +10878,8 @@
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.125" style="2" customWidth="1"/>
-    <col min="3" max="18" width="9" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="3" max="22" width="9" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:22" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -9160,43 +10887,43 @@
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2127" t="s">
+      <c r="C2" s="2563" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2124"/>
-      <c r="E2" s="2129" t="s">
+      <c r="D2" s="2559"/>
+      <c r="E2" s="2565" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2124"/>
-      <c r="G2" s="2128" t="s">
+      <c r="F2" s="2559"/>
+      <c r="G2" s="2564" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="2124"/>
-      <c r="I2" s="2131" t="s">
+      <c r="H2" s="2559"/>
+      <c r="I2" s="2567" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="2124"/>
-      <c r="K2" s="2130" t="s">
+      <c r="J2" s="2559"/>
+      <c r="K2" s="2566" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2124"/>
-      <c r="M2" s="2125" t="s">
+      <c r="L2" s="2559"/>
+      <c r="M2" s="2561" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="2124"/>
-      <c r="O2" s="2123" t="s">
+      <c r="N2" s="2559"/>
+      <c r="O2" s="2560" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="2124"/>
-      <c r="Q2" s="2126" t="s">
+      <c r="P2" s="2559"/>
+      <c r="Q2" s="2562" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="2124"/>
-      <c r="S2" s="2132" t="s">
+      <c r="R2" s="2559"/>
+      <c r="S2" s="2557" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="2133"/>
-      <c r="U2" s="2124"/>
+      <c r="T2" s="2558"/>
+      <c r="U2" s="2559"/>
       <c r="V2" s="4" t="s">
         <v>10</v>
       </c>
@@ -17433,57 +19160,57 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:W136"/>
+  <dimension ref="B2:W194"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="1098" customWidth="1"/>
     <col min="2" max="2" width="14.5" style="1098" customWidth="1"/>
     <col min="3" max="22" width="12" style="1098" customWidth="1"/>
-    <col min="23" max="27" width="9" style="1098" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="1098"/>
+    <col min="23" max="31" width="9" style="1098" customWidth="1"/>
+    <col min="32" max="16384" width="9" style="1098"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1096" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2137" t="s">
+      <c r="C2" s="2572" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2124"/>
-      <c r="E2" s="2139" t="s">
+      <c r="D2" s="2559"/>
+      <c r="E2" s="2574" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2124"/>
-      <c r="G2" s="2138" t="s">
+      <c r="F2" s="2559"/>
+      <c r="G2" s="2573" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="2124"/>
-      <c r="I2" s="2141" t="s">
+      <c r="H2" s="2559"/>
+      <c r="I2" s="2576" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="2124"/>
-      <c r="K2" s="2140" t="s">
+      <c r="J2" s="2559"/>
+      <c r="K2" s="2575" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="2124"/>
-      <c r="M2" s="2135" t="s">
+      <c r="L2" s="2559"/>
+      <c r="M2" s="2570" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="2124"/>
-      <c r="O2" s="2134" t="s">
+      <c r="N2" s="2559"/>
+      <c r="O2" s="2569" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="2124"/>
-      <c r="Q2" s="2136" t="s">
+      <c r="P2" s="2559"/>
+      <c r="Q2" s="2571" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="2124"/>
-      <c r="S2" s="2142" t="s">
+      <c r="R2" s="2559"/>
+      <c r="S2" s="2568" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="2133"/>
-      <c r="U2" s="2124"/>
+      <c r="T2" s="2558"/>
+      <c r="U2" s="2559"/>
       <c r="V2" s="1097" t="s">
         <v>10</v>
       </c>
@@ -22092,7 +23819,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" s="1987" t="s">
         <v>187</v>
       </c>
@@ -22125,7 +23852,7 @@
       <c r="U127" s="2006"/>
       <c r="V127" s="2007"/>
     </row>
-    <row r="128" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B128" s="2008"/>
       <c r="C128" s="2009"/>
       <c r="D128" s="2010"/>
@@ -22160,7 +23887,7 @@
       <c r="U128" s="2027"/>
       <c r="V128" s="2028"/>
     </row>
-    <row r="129" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B129" s="2008"/>
       <c r="C129" s="2009"/>
       <c r="D129" s="2010"/>
@@ -22194,8 +23921,11 @@
       </c>
       <c r="U129" s="2027"/>
       <c r="V129" s="2028"/>
-    </row>
-    <row r="130" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="W129" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B130" s="2008"/>
       <c r="C130" s="2009"/>
       <c r="D130" s="2010"/>
@@ -22230,7 +23960,7 @@
       <c r="U130" s="2027"/>
       <c r="V130" s="2028"/>
     </row>
-    <row r="131" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B131" s="2008"/>
       <c r="C131" s="2009"/>
       <c r="D131" s="2010"/>
@@ -22261,7 +23991,7 @@
       <c r="U131" s="2027"/>
       <c r="V131" s="2028"/>
     </row>
-    <row r="132" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B132" s="2008"/>
       <c r="C132" s="2009"/>
       <c r="D132" s="2010"/>
@@ -22299,7 +24029,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="133" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B133" s="2039"/>
       <c r="C133" s="2040"/>
       <c r="D133" s="2041"/>
@@ -22334,7 +24064,7 @@
       <c r="U133" s="2058"/>
       <c r="V133" s="2059"/>
     </row>
-    <row r="134" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B134" s="2060" t="s">
         <v>18</v>
       </c>
@@ -22385,7 +24115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="135" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B135" s="2081" t="s">
         <v>20</v>
       </c>
@@ -22418,7 +24148,7 @@
       <c r="U135" s="2100"/>
       <c r="V135" s="2101"/>
     </row>
-    <row r="136" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B136" s="2102" t="s">
         <v>21</v>
       </c>
@@ -22472,6 +24202,2166 @@
         <v>12135.35</v>
       </c>
       <c r="V136" s="2122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B137" s="2123" t="s">
+        <v>190</v>
+      </c>
+      <c r="C137" s="2124"/>
+      <c r="D137" s="2125"/>
+      <c r="E137" s="2126"/>
+      <c r="F137" s="2127"/>
+      <c r="G137" s="2128" t="s">
+        <v>5</v>
+      </c>
+      <c r="H137" s="2129" t="s">
+        <v>191</v>
+      </c>
+      <c r="I137" s="2130"/>
+      <c r="J137" s="2131"/>
+      <c r="K137" s="2132" t="s">
+        <v>191</v>
+      </c>
+      <c r="L137" s="2133" t="s">
+        <v>28</v>
+      </c>
+      <c r="M137" s="2134"/>
+      <c r="N137" s="2135"/>
+      <c r="O137" s="2136"/>
+      <c r="P137" s="2137"/>
+      <c r="Q137" s="2138"/>
+      <c r="R137" s="2139"/>
+      <c r="S137" s="2140"/>
+      <c r="T137" s="2141"/>
+      <c r="U137" s="2142"/>
+      <c r="V137" s="2143"/>
+    </row>
+    <row r="138" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B138" s="2144"/>
+      <c r="C138" s="2145"/>
+      <c r="D138" s="2146"/>
+      <c r="E138" s="2147"/>
+      <c r="F138" s="2148"/>
+      <c r="G138" s="2149"/>
+      <c r="H138" s="2150"/>
+      <c r="I138" s="2151"/>
+      <c r="J138" s="2152"/>
+      <c r="K138" s="2153" t="s">
+        <v>29</v>
+      </c>
+      <c r="L138" s="2154" t="s">
+        <v>191</v>
+      </c>
+      <c r="M138" s="2155"/>
+      <c r="N138" s="2156"/>
+      <c r="O138" s="2157"/>
+      <c r="P138" s="2158"/>
+      <c r="Q138" s="2159" t="s">
+        <v>29</v>
+      </c>
+      <c r="R138" s="2160" t="s">
+        <v>191</v>
+      </c>
+      <c r="S138" s="2161" t="s">
+        <v>29</v>
+      </c>
+      <c r="T138" s="2162" t="s">
+        <v>191</v>
+      </c>
+      <c r="U138" s="2163"/>
+      <c r="V138" s="2164"/>
+    </row>
+    <row r="139" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B139" s="2144"/>
+      <c r="C139" s="2145"/>
+      <c r="D139" s="2146"/>
+      <c r="E139" s="2147"/>
+      <c r="F139" s="2148"/>
+      <c r="G139" s="2149"/>
+      <c r="H139" s="2150"/>
+      <c r="I139" s="2165" t="s">
+        <v>50</v>
+      </c>
+      <c r="J139" s="2166" t="s">
+        <v>136</v>
+      </c>
+      <c r="K139" s="2167"/>
+      <c r="L139" s="2168"/>
+      <c r="M139" s="2155"/>
+      <c r="N139" s="2156"/>
+      <c r="O139" s="2157"/>
+      <c r="P139" s="2158"/>
+      <c r="Q139" s="2159" t="s">
+        <v>50</v>
+      </c>
+      <c r="R139" s="2160" t="s">
+        <v>136</v>
+      </c>
+      <c r="S139" s="2161" t="s">
+        <v>50</v>
+      </c>
+      <c r="T139" s="2162" t="s">
+        <v>136</v>
+      </c>
+      <c r="U139" s="2163"/>
+      <c r="V139" s="2164"/>
+    </row>
+    <row r="140" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B140" s="2144"/>
+      <c r="C140" s="2145"/>
+      <c r="D140" s="2146"/>
+      <c r="E140" s="2147"/>
+      <c r="F140" s="2148"/>
+      <c r="G140" s="2169" t="s">
+        <v>5</v>
+      </c>
+      <c r="H140" s="2170" t="s">
+        <v>192</v>
+      </c>
+      <c r="I140" s="2151"/>
+      <c r="J140" s="2152"/>
+      <c r="K140" s="2153" t="s">
+        <v>192</v>
+      </c>
+      <c r="L140" s="2154" t="s">
+        <v>28</v>
+      </c>
+      <c r="M140" s="2155"/>
+      <c r="N140" s="2156"/>
+      <c r="O140" s="2157"/>
+      <c r="P140" s="2158"/>
+      <c r="Q140" s="2171"/>
+      <c r="R140" s="2172"/>
+      <c r="S140" s="2173"/>
+      <c r="T140" s="2174"/>
+      <c r="U140" s="2163"/>
+      <c r="V140" s="2164"/>
+    </row>
+    <row r="141" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B141" s="2144"/>
+      <c r="C141" s="2145"/>
+      <c r="D141" s="2146"/>
+      <c r="E141" s="2147"/>
+      <c r="F141" s="2148"/>
+      <c r="G141" s="2149"/>
+      <c r="H141" s="2150"/>
+      <c r="I141" s="2151"/>
+      <c r="J141" s="2152"/>
+      <c r="K141" s="2153" t="s">
+        <v>46</v>
+      </c>
+      <c r="L141" s="2154" t="s">
+        <v>192</v>
+      </c>
+      <c r="M141" s="2155"/>
+      <c r="N141" s="2156"/>
+      <c r="O141" s="2157"/>
+      <c r="P141" s="2158"/>
+      <c r="Q141" s="2159" t="s">
+        <v>46</v>
+      </c>
+      <c r="R141" s="2160" t="s">
+        <v>192</v>
+      </c>
+      <c r="S141" s="2161" t="s">
+        <v>46</v>
+      </c>
+      <c r="T141" s="2162" t="s">
+        <v>192</v>
+      </c>
+      <c r="U141" s="2163"/>
+      <c r="V141" s="2164"/>
+    </row>
+    <row r="142" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B142" s="2144"/>
+      <c r="C142" s="2145"/>
+      <c r="D142" s="2146"/>
+      <c r="E142" s="2147"/>
+      <c r="F142" s="2148"/>
+      <c r="G142" s="2149"/>
+      <c r="H142" s="2150"/>
+      <c r="I142" s="2165" t="s">
+        <v>50</v>
+      </c>
+      <c r="J142" s="2166" t="s">
+        <v>165</v>
+      </c>
+      <c r="K142" s="2167"/>
+      <c r="L142" s="2168"/>
+      <c r="M142" s="2155"/>
+      <c r="N142" s="2156"/>
+      <c r="O142" s="2157"/>
+      <c r="P142" s="2158"/>
+      <c r="Q142" s="2159" t="s">
+        <v>50</v>
+      </c>
+      <c r="R142" s="2160" t="s">
+        <v>165</v>
+      </c>
+      <c r="S142" s="2161" t="s">
+        <v>50</v>
+      </c>
+      <c r="T142" s="2162" t="s">
+        <v>165</v>
+      </c>
+      <c r="U142" s="2163"/>
+      <c r="V142" s="2164"/>
+    </row>
+    <row r="143" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B143" s="2144"/>
+      <c r="C143" s="2145"/>
+      <c r="D143" s="2146"/>
+      <c r="E143" s="2147"/>
+      <c r="F143" s="2148"/>
+      <c r="G143" s="2149"/>
+      <c r="H143" s="2150"/>
+      <c r="I143" s="2165" t="s">
+        <v>94</v>
+      </c>
+      <c r="J143" s="2166" t="s">
+        <v>34</v>
+      </c>
+      <c r="K143" s="2167"/>
+      <c r="L143" s="2168"/>
+      <c r="M143" s="2155"/>
+      <c r="N143" s="2156"/>
+      <c r="O143" s="2157"/>
+      <c r="P143" s="2158"/>
+      <c r="Q143" s="2159" t="s">
+        <v>94</v>
+      </c>
+      <c r="R143" s="2160" t="s">
+        <v>34</v>
+      </c>
+      <c r="S143" s="2161" t="s">
+        <v>94</v>
+      </c>
+      <c r="T143" s="2162" t="s">
+        <v>34</v>
+      </c>
+      <c r="U143" s="2163"/>
+      <c r="V143" s="2164"/>
+    </row>
+    <row r="144" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B144" s="2144"/>
+      <c r="C144" s="2145"/>
+      <c r="D144" s="2146"/>
+      <c r="E144" s="2147"/>
+      <c r="F144" s="2148"/>
+      <c r="G144" s="2169" t="s">
+        <v>33</v>
+      </c>
+      <c r="H144" s="2170" t="s">
+        <v>193</v>
+      </c>
+      <c r="I144" s="2151"/>
+      <c r="J144" s="2152"/>
+      <c r="K144" s="2167"/>
+      <c r="L144" s="2168"/>
+      <c r="M144" s="2155"/>
+      <c r="N144" s="2156"/>
+      <c r="O144" s="2157"/>
+      <c r="P144" s="2158"/>
+      <c r="Q144" s="2159" t="s">
+        <v>33</v>
+      </c>
+      <c r="R144" s="2160" t="s">
+        <v>193</v>
+      </c>
+      <c r="S144" s="2161" t="s">
+        <v>33</v>
+      </c>
+      <c r="T144" s="2162" t="s">
+        <v>193</v>
+      </c>
+      <c r="U144" s="2163"/>
+      <c r="V144" s="2164"/>
+      <c r="W144" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B145" s="2175"/>
+      <c r="C145" s="2176"/>
+      <c r="D145" s="2177"/>
+      <c r="E145" s="2178"/>
+      <c r="F145" s="2179"/>
+      <c r="G145" s="2180"/>
+      <c r="H145" s="2181"/>
+      <c r="I145" s="2182" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" s="2183" t="s">
+        <v>48</v>
+      </c>
+      <c r="K145" s="2184"/>
+      <c r="L145" s="2185"/>
+      <c r="M145" s="2186"/>
+      <c r="N145" s="2187"/>
+      <c r="O145" s="2188"/>
+      <c r="P145" s="2189"/>
+      <c r="Q145" s="2190" t="s">
+        <v>23</v>
+      </c>
+      <c r="R145" s="2191" t="s">
+        <v>48</v>
+      </c>
+      <c r="S145" s="2192" t="s">
+        <v>23</v>
+      </c>
+      <c r="T145" s="2193" t="s">
+        <v>48</v>
+      </c>
+      <c r="U145" s="2194"/>
+      <c r="V145" s="2195"/>
+    </row>
+    <row r="146" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B146" s="2196" t="s">
+        <v>18</v>
+      </c>
+      <c r="C146" s="2197">
+        <v>60</v>
+      </c>
+      <c r="D146" s="2198"/>
+      <c r="E146" s="2199">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F146" s="2200"/>
+      <c r="G146" s="2201">
+        <v>11479.67</v>
+      </c>
+      <c r="H146" s="2202"/>
+      <c r="I146" s="2203">
+        <v>240</v>
+      </c>
+      <c r="J146" s="2204"/>
+      <c r="K146" s="2205">
+        <v>0</v>
+      </c>
+      <c r="L146" s="2206"/>
+      <c r="M146" s="2207">
+        <v>48.48</v>
+      </c>
+      <c r="N146" s="2208"/>
+      <c r="O146" s="2209">
+        <v>0</v>
+      </c>
+      <c r="P146" s="2210"/>
+      <c r="Q146" s="2211">
+        <v>0</v>
+      </c>
+      <c r="R146" s="2212">
+        <v>274.39999999999998</v>
+      </c>
+      <c r="S146" s="2213">
+        <v>0</v>
+      </c>
+      <c r="T146" s="2214">
+        <v>274.39999999999998</v>
+      </c>
+      <c r="U146" s="2215">
+        <v>11860.95</v>
+      </c>
+      <c r="V146" s="2216" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B147" s="2217" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" s="2218"/>
+      <c r="D147" s="2219"/>
+      <c r="E147" s="2220"/>
+      <c r="F147" s="2221"/>
+      <c r="G147" s="2222"/>
+      <c r="H147" s="2223"/>
+      <c r="I147" s="2224"/>
+      <c r="J147" s="2225"/>
+      <c r="K147" s="2226"/>
+      <c r="L147" s="2227"/>
+      <c r="M147" s="2228"/>
+      <c r="N147" s="2229"/>
+      <c r="O147" s="2230"/>
+      <c r="P147" s="2231"/>
+      <c r="Q147" s="2232">
+        <v>0</v>
+      </c>
+      <c r="R147" s="2233">
+        <v>2459.88</v>
+      </c>
+      <c r="S147" s="2234">
+        <v>3700</v>
+      </c>
+      <c r="T147" s="2235">
+        <v>2959.88</v>
+      </c>
+      <c r="U147" s="2236"/>
+      <c r="V147" s="2237"/>
+    </row>
+    <row r="148" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B148" s="2123" t="s">
+        <v>194</v>
+      </c>
+      <c r="C148" s="2124"/>
+      <c r="D148" s="2125"/>
+      <c r="E148" s="2126"/>
+      <c r="F148" s="2127"/>
+      <c r="G148" s="2238"/>
+      <c r="H148" s="2239"/>
+      <c r="I148" s="2240" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" s="2241" t="s">
+        <v>24</v>
+      </c>
+      <c r="K148" s="2242"/>
+      <c r="L148" s="2243"/>
+      <c r="M148" s="2134"/>
+      <c r="N148" s="2135"/>
+      <c r="O148" s="2136"/>
+      <c r="P148" s="2137"/>
+      <c r="Q148" s="2244" t="s">
+        <v>23</v>
+      </c>
+      <c r="R148" s="2245" t="s">
+        <v>24</v>
+      </c>
+      <c r="S148" s="2246" t="s">
+        <v>23</v>
+      </c>
+      <c r="T148" s="2247" t="s">
+        <v>24</v>
+      </c>
+      <c r="U148" s="2142"/>
+      <c r="V148" s="2143"/>
+    </row>
+    <row r="149" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B149" s="2144"/>
+      <c r="C149" s="2145"/>
+      <c r="D149" s="2146"/>
+      <c r="E149" s="2147"/>
+      <c r="F149" s="2148"/>
+      <c r="G149" s="2169" t="s">
+        <v>5</v>
+      </c>
+      <c r="H149" s="2170" t="s">
+        <v>92</v>
+      </c>
+      <c r="I149" s="2151"/>
+      <c r="J149" s="2152"/>
+      <c r="K149" s="2153" t="s">
+        <v>92</v>
+      </c>
+      <c r="L149" s="2154" t="s">
+        <v>28</v>
+      </c>
+      <c r="M149" s="2155"/>
+      <c r="N149" s="2156"/>
+      <c r="O149" s="2157"/>
+      <c r="P149" s="2158"/>
+      <c r="Q149" s="2171"/>
+      <c r="R149" s="2172"/>
+      <c r="S149" s="2173"/>
+      <c r="T149" s="2174"/>
+      <c r="U149" s="2163"/>
+      <c r="V149" s="2164"/>
+    </row>
+    <row r="150" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B150" s="2144"/>
+      <c r="C150" s="2145"/>
+      <c r="D150" s="2146"/>
+      <c r="E150" s="2147"/>
+      <c r="F150" s="2148"/>
+      <c r="G150" s="2149"/>
+      <c r="H150" s="2150"/>
+      <c r="I150" s="2151"/>
+      <c r="J150" s="2152"/>
+      <c r="K150" s="2153" t="s">
+        <v>93</v>
+      </c>
+      <c r="L150" s="2154" t="s">
+        <v>92</v>
+      </c>
+      <c r="M150" s="2155"/>
+      <c r="N150" s="2156"/>
+      <c r="O150" s="2157"/>
+      <c r="P150" s="2158"/>
+      <c r="Q150" s="2159" t="s">
+        <v>93</v>
+      </c>
+      <c r="R150" s="2160" t="s">
+        <v>92</v>
+      </c>
+      <c r="S150" s="2161" t="s">
+        <v>93</v>
+      </c>
+      <c r="T150" s="2162" t="s">
+        <v>92</v>
+      </c>
+      <c r="U150" s="2163"/>
+      <c r="V150" s="2164"/>
+    </row>
+    <row r="151" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B151" s="2144"/>
+      <c r="C151" s="2145"/>
+      <c r="D151" s="2146"/>
+      <c r="E151" s="2147"/>
+      <c r="F151" s="2148"/>
+      <c r="G151" s="2149"/>
+      <c r="H151" s="2150"/>
+      <c r="I151" s="2165" t="s">
+        <v>25</v>
+      </c>
+      <c r="J151" s="2166" t="s">
+        <v>26</v>
+      </c>
+      <c r="K151" s="2167"/>
+      <c r="L151" s="2168"/>
+      <c r="M151" s="2155"/>
+      <c r="N151" s="2156"/>
+      <c r="O151" s="2157"/>
+      <c r="P151" s="2158"/>
+      <c r="Q151" s="2159" t="s">
+        <v>25</v>
+      </c>
+      <c r="R151" s="2160" t="s">
+        <v>26</v>
+      </c>
+      <c r="S151" s="2161" t="s">
+        <v>25</v>
+      </c>
+      <c r="T151" s="2162" t="s">
+        <v>26</v>
+      </c>
+      <c r="U151" s="2163"/>
+      <c r="V151" s="2164"/>
+    </row>
+    <row r="152" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B152" s="2144"/>
+      <c r="C152" s="2145"/>
+      <c r="D152" s="2146"/>
+      <c r="E152" s="2147"/>
+      <c r="F152" s="2148"/>
+      <c r="G152" s="2169" t="s">
+        <v>5</v>
+      </c>
+      <c r="H152" s="2170" t="s">
+        <v>89</v>
+      </c>
+      <c r="I152" s="2151"/>
+      <c r="J152" s="2152"/>
+      <c r="K152" s="2153" t="s">
+        <v>89</v>
+      </c>
+      <c r="L152" s="2154" t="s">
+        <v>28</v>
+      </c>
+      <c r="M152" s="2155"/>
+      <c r="N152" s="2156"/>
+      <c r="O152" s="2157"/>
+      <c r="P152" s="2158"/>
+      <c r="Q152" s="2171"/>
+      <c r="R152" s="2172"/>
+      <c r="S152" s="2173"/>
+      <c r="T152" s="2174"/>
+      <c r="U152" s="2163"/>
+      <c r="V152" s="2164"/>
+    </row>
+    <row r="153" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B153" s="2144"/>
+      <c r="C153" s="2145"/>
+      <c r="D153" s="2146"/>
+      <c r="E153" s="2147"/>
+      <c r="F153" s="2148"/>
+      <c r="G153" s="2149"/>
+      <c r="H153" s="2150"/>
+      <c r="I153" s="2151"/>
+      <c r="J153" s="2152"/>
+      <c r="K153" s="2153" t="s">
+        <v>46</v>
+      </c>
+      <c r="L153" s="2154" t="s">
+        <v>89</v>
+      </c>
+      <c r="M153" s="2155"/>
+      <c r="N153" s="2156"/>
+      <c r="O153" s="2157"/>
+      <c r="P153" s="2158"/>
+      <c r="Q153" s="2159" t="s">
+        <v>46</v>
+      </c>
+      <c r="R153" s="2160" t="s">
+        <v>89</v>
+      </c>
+      <c r="S153" s="2161" t="s">
+        <v>46</v>
+      </c>
+      <c r="T153" s="2162" t="s">
+        <v>89</v>
+      </c>
+      <c r="U153" s="2163"/>
+      <c r="V153" s="2164"/>
+    </row>
+    <row r="154" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B154" s="2144"/>
+      <c r="C154" s="2145"/>
+      <c r="D154" s="2146"/>
+      <c r="E154" s="2147"/>
+      <c r="F154" s="2148"/>
+      <c r="G154" s="2169" t="s">
+        <v>5</v>
+      </c>
+      <c r="H154" s="2170" t="s">
+        <v>195</v>
+      </c>
+      <c r="I154" s="2151"/>
+      <c r="J154" s="2152"/>
+      <c r="K154" s="2153" t="s">
+        <v>195</v>
+      </c>
+      <c r="L154" s="2154" t="s">
+        <v>28</v>
+      </c>
+      <c r="M154" s="2155"/>
+      <c r="N154" s="2156"/>
+      <c r="O154" s="2157"/>
+      <c r="P154" s="2158"/>
+      <c r="Q154" s="2171"/>
+      <c r="R154" s="2172"/>
+      <c r="S154" s="2173"/>
+      <c r="T154" s="2174"/>
+      <c r="U154" s="2163"/>
+      <c r="V154" s="2164"/>
+    </row>
+    <row r="155" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B155" s="2144"/>
+      <c r="C155" s="2145"/>
+      <c r="D155" s="2146"/>
+      <c r="E155" s="2147"/>
+      <c r="F155" s="2148"/>
+      <c r="G155" s="2149"/>
+      <c r="H155" s="2150"/>
+      <c r="I155" s="2151"/>
+      <c r="J155" s="2152"/>
+      <c r="K155" s="2153" t="s">
+        <v>196</v>
+      </c>
+      <c r="L155" s="2154" t="s">
+        <v>195</v>
+      </c>
+      <c r="M155" s="2155"/>
+      <c r="N155" s="2156"/>
+      <c r="O155" s="2157"/>
+      <c r="P155" s="2158"/>
+      <c r="Q155" s="2159" t="s">
+        <v>196</v>
+      </c>
+      <c r="R155" s="2160" t="s">
+        <v>195</v>
+      </c>
+      <c r="S155" s="2161" t="s">
+        <v>196</v>
+      </c>
+      <c r="T155" s="2162" t="s">
+        <v>195</v>
+      </c>
+      <c r="U155" s="2163"/>
+      <c r="V155" s="2164"/>
+    </row>
+    <row r="156" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B156" s="2175"/>
+      <c r="C156" s="2176"/>
+      <c r="D156" s="2177"/>
+      <c r="E156" s="2178"/>
+      <c r="F156" s="2179"/>
+      <c r="G156" s="2180"/>
+      <c r="H156" s="2181"/>
+      <c r="I156" s="2182" t="s">
+        <v>25</v>
+      </c>
+      <c r="J156" s="2183" t="s">
+        <v>36</v>
+      </c>
+      <c r="K156" s="2184"/>
+      <c r="L156" s="2185"/>
+      <c r="M156" s="2186"/>
+      <c r="N156" s="2187"/>
+      <c r="O156" s="2188"/>
+      <c r="P156" s="2189"/>
+      <c r="Q156" s="2190" t="s">
+        <v>25</v>
+      </c>
+      <c r="R156" s="2191" t="s">
+        <v>36</v>
+      </c>
+      <c r="S156" s="2192" t="s">
+        <v>25</v>
+      </c>
+      <c r="T156" s="2193" t="s">
+        <v>36</v>
+      </c>
+      <c r="U156" s="2194"/>
+      <c r="V156" s="2195"/>
+    </row>
+    <row r="157" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B157" s="2196" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" s="2197">
+        <v>60</v>
+      </c>
+      <c r="D157" s="2198"/>
+      <c r="E157" s="2199">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F157" s="2200"/>
+      <c r="G157" s="2201">
+        <v>11422.73</v>
+      </c>
+      <c r="H157" s="2202"/>
+      <c r="I157" s="2203">
+        <v>218</v>
+      </c>
+      <c r="J157" s="2204"/>
+      <c r="K157" s="2205">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2206"/>
+      <c r="M157" s="2207">
+        <v>48.48</v>
+      </c>
+      <c r="N157" s="2208"/>
+      <c r="O157" s="2209">
+        <v>0</v>
+      </c>
+      <c r="P157" s="2210"/>
+      <c r="Q157" s="2211">
+        <v>0</v>
+      </c>
+      <c r="R157" s="2212">
+        <v>78.94</v>
+      </c>
+      <c r="S157" s="2213">
+        <v>0</v>
+      </c>
+      <c r="T157" s="2214">
+        <v>78.94</v>
+      </c>
+      <c r="U157" s="2215">
+        <v>11782.01</v>
+      </c>
+      <c r="V157" s="2216" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B158" s="2217" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" s="2218"/>
+      <c r="D158" s="2219"/>
+      <c r="E158" s="2220"/>
+      <c r="F158" s="2221"/>
+      <c r="G158" s="2222"/>
+      <c r="H158" s="2223"/>
+      <c r="I158" s="2224"/>
+      <c r="J158" s="2225"/>
+      <c r="K158" s="2226"/>
+      <c r="L158" s="2227"/>
+      <c r="M158" s="2228"/>
+      <c r="N158" s="2229"/>
+      <c r="O158" s="2230"/>
+      <c r="P158" s="2231"/>
+      <c r="Q158" s="2232">
+        <v>0</v>
+      </c>
+      <c r="R158" s="2233">
+        <v>2538.8200000000002</v>
+      </c>
+      <c r="S158" s="2234">
+        <v>3700</v>
+      </c>
+      <c r="T158" s="2235">
+        <v>3038.82</v>
+      </c>
+      <c r="U158" s="2236"/>
+      <c r="V158" s="2237"/>
+    </row>
+    <row r="159" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B159" s="2248" t="s">
+        <v>21</v>
+      </c>
+      <c r="C159" s="2249">
+        <v>60</v>
+      </c>
+      <c r="D159" s="2250" t="s">
+        <v>19</v>
+      </c>
+      <c r="E159" s="2251">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F159" s="2252" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159" s="2253">
+        <v>11422.73</v>
+      </c>
+      <c r="H159" s="2254" t="s">
+        <v>19</v>
+      </c>
+      <c r="I159" s="2255">
+        <v>218</v>
+      </c>
+      <c r="J159" s="2256" t="s">
+        <v>19</v>
+      </c>
+      <c r="K159" s="2257">
+        <v>0</v>
+      </c>
+      <c r="L159" s="2258" t="s">
+        <v>19</v>
+      </c>
+      <c r="M159" s="2259">
+        <v>48.48</v>
+      </c>
+      <c r="N159" s="2260" t="s">
+        <v>19</v>
+      </c>
+      <c r="O159" s="2261">
+        <v>0</v>
+      </c>
+      <c r="P159" s="2262" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q159" s="2263"/>
+      <c r="R159" s="2264"/>
+      <c r="S159" s="2265"/>
+      <c r="T159" s="2266"/>
+      <c r="U159" s="2267">
+        <v>11782.01</v>
+      </c>
+      <c r="V159" s="2268" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B160" s="2269" t="s">
+        <v>197</v>
+      </c>
+      <c r="C160" s="2270"/>
+      <c r="D160" s="2271"/>
+      <c r="E160" s="2272"/>
+      <c r="F160" s="2273"/>
+      <c r="G160" s="2274"/>
+      <c r="H160" s="2275"/>
+      <c r="I160" s="2276" t="s">
+        <v>50</v>
+      </c>
+      <c r="J160" s="2277" t="s">
+        <v>136</v>
+      </c>
+      <c r="K160" s="2278"/>
+      <c r="L160" s="2279"/>
+      <c r="M160" s="2280"/>
+      <c r="N160" s="2281"/>
+      <c r="O160" s="2282"/>
+      <c r="P160" s="2283"/>
+      <c r="Q160" s="2284" t="s">
+        <v>50</v>
+      </c>
+      <c r="R160" s="2285" t="s">
+        <v>136</v>
+      </c>
+      <c r="S160" s="2286" t="s">
+        <v>50</v>
+      </c>
+      <c r="T160" s="2287" t="s">
+        <v>136</v>
+      </c>
+      <c r="U160" s="2288"/>
+      <c r="V160" s="2289"/>
+    </row>
+    <row r="161" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B161" s="2290"/>
+      <c r="C161" s="2291"/>
+      <c r="D161" s="2292"/>
+      <c r="E161" s="2293"/>
+      <c r="F161" s="2294"/>
+      <c r="G161" s="2295" t="s">
+        <v>5</v>
+      </c>
+      <c r="H161" s="2296" t="s">
+        <v>198</v>
+      </c>
+      <c r="I161" s="2297"/>
+      <c r="J161" s="2298"/>
+      <c r="K161" s="2299" t="s">
+        <v>198</v>
+      </c>
+      <c r="L161" s="2300" t="s">
+        <v>28</v>
+      </c>
+      <c r="M161" s="2301"/>
+      <c r="N161" s="2302"/>
+      <c r="O161" s="2303"/>
+      <c r="P161" s="2304"/>
+      <c r="Q161" s="2305"/>
+      <c r="R161" s="2306"/>
+      <c r="S161" s="2307"/>
+      <c r="T161" s="2308"/>
+      <c r="U161" s="2309"/>
+      <c r="V161" s="2310"/>
+    </row>
+    <row r="162" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B162" s="2290"/>
+      <c r="C162" s="2291"/>
+      <c r="D162" s="2292"/>
+      <c r="E162" s="2293"/>
+      <c r="F162" s="2294"/>
+      <c r="G162" s="2311"/>
+      <c r="H162" s="2312"/>
+      <c r="I162" s="2297"/>
+      <c r="J162" s="2298"/>
+      <c r="K162" s="2299" t="s">
+        <v>46</v>
+      </c>
+      <c r="L162" s="2300" t="s">
+        <v>198</v>
+      </c>
+      <c r="M162" s="2301"/>
+      <c r="N162" s="2302"/>
+      <c r="O162" s="2303"/>
+      <c r="P162" s="2304"/>
+      <c r="Q162" s="2313" t="s">
+        <v>46</v>
+      </c>
+      <c r="R162" s="2314" t="s">
+        <v>198</v>
+      </c>
+      <c r="S162" s="2315" t="s">
+        <v>46</v>
+      </c>
+      <c r="T162" s="2316" t="s">
+        <v>198</v>
+      </c>
+      <c r="U162" s="2309"/>
+      <c r="V162" s="2310"/>
+    </row>
+    <row r="163" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B163" s="2290"/>
+      <c r="C163" s="2291"/>
+      <c r="D163" s="2292"/>
+      <c r="E163" s="2293"/>
+      <c r="F163" s="2294"/>
+      <c r="G163" s="2311"/>
+      <c r="H163" s="2312"/>
+      <c r="I163" s="2317" t="s">
+        <v>50</v>
+      </c>
+      <c r="J163" s="2318" t="s">
+        <v>165</v>
+      </c>
+      <c r="K163" s="2319"/>
+      <c r="L163" s="2320"/>
+      <c r="M163" s="2301"/>
+      <c r="N163" s="2302"/>
+      <c r="O163" s="2303"/>
+      <c r="P163" s="2304"/>
+      <c r="Q163" s="2313" t="s">
+        <v>50</v>
+      </c>
+      <c r="R163" s="2314" t="s">
+        <v>165</v>
+      </c>
+      <c r="S163" s="2315" t="s">
+        <v>50</v>
+      </c>
+      <c r="T163" s="2316" t="s">
+        <v>165</v>
+      </c>
+      <c r="U163" s="2309"/>
+      <c r="V163" s="2310"/>
+    </row>
+    <row r="164" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B164" s="2321"/>
+      <c r="C164" s="2322"/>
+      <c r="D164" s="2323"/>
+      <c r="E164" s="2324"/>
+      <c r="F164" s="2325"/>
+      <c r="G164" s="2326"/>
+      <c r="H164" s="2327"/>
+      <c r="I164" s="2328"/>
+      <c r="J164" s="2329"/>
+      <c r="K164" s="2330"/>
+      <c r="L164" s="2331"/>
+      <c r="M164" s="2332" t="s">
+        <v>65</v>
+      </c>
+      <c r="N164" s="2333" t="s">
+        <v>61</v>
+      </c>
+      <c r="O164" s="2334"/>
+      <c r="P164" s="2335"/>
+      <c r="Q164" s="2336" t="s">
+        <v>65</v>
+      </c>
+      <c r="R164" s="2337" t="s">
+        <v>61</v>
+      </c>
+      <c r="S164" s="2338" t="s">
+        <v>65</v>
+      </c>
+      <c r="T164" s="2339" t="s">
+        <v>61</v>
+      </c>
+      <c r="U164" s="2340"/>
+      <c r="V164" s="2341"/>
+    </row>
+    <row r="165" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B165" s="2342" t="s">
+        <v>18</v>
+      </c>
+      <c r="C165" s="2343">
+        <v>60</v>
+      </c>
+      <c r="D165" s="2344"/>
+      <c r="E165" s="2345">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F165" s="2346"/>
+      <c r="G165" s="2347">
+        <v>11339.73</v>
+      </c>
+      <c r="H165" s="2348"/>
+      <c r="I165" s="2349">
+        <v>192.2</v>
+      </c>
+      <c r="J165" s="2350"/>
+      <c r="K165" s="2351">
+        <v>0</v>
+      </c>
+      <c r="L165" s="2352"/>
+      <c r="M165" s="2353">
+        <v>0</v>
+      </c>
+      <c r="N165" s="2354"/>
+      <c r="O165" s="2355">
+        <v>0</v>
+      </c>
+      <c r="P165" s="2356"/>
+      <c r="Q165" s="2357">
+        <v>0</v>
+      </c>
+      <c r="R165" s="2358">
+        <v>157.28</v>
+      </c>
+      <c r="S165" s="2359">
+        <v>0</v>
+      </c>
+      <c r="T165" s="2360">
+        <v>157.28</v>
+      </c>
+      <c r="U165" s="2361">
+        <v>11624.73</v>
+      </c>
+      <c r="V165" s="2362" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B166" s="2363" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" s="2364"/>
+      <c r="D166" s="2365"/>
+      <c r="E166" s="2366"/>
+      <c r="F166" s="2367"/>
+      <c r="G166" s="2368"/>
+      <c r="H166" s="2369"/>
+      <c r="I166" s="2370"/>
+      <c r="J166" s="2371"/>
+      <c r="K166" s="2372"/>
+      <c r="L166" s="2373"/>
+      <c r="M166" s="2374"/>
+      <c r="N166" s="2375"/>
+      <c r="O166" s="2376"/>
+      <c r="P166" s="2377"/>
+      <c r="Q166" s="2378">
+        <v>0</v>
+      </c>
+      <c r="R166" s="2379">
+        <v>2696.1</v>
+      </c>
+      <c r="S166" s="2380">
+        <v>3700</v>
+      </c>
+      <c r="T166" s="2381">
+        <v>3196.1</v>
+      </c>
+      <c r="U166" s="2382"/>
+      <c r="V166" s="2383"/>
+    </row>
+    <row r="167" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B167" s="2384" t="s">
+        <v>21</v>
+      </c>
+      <c r="C167" s="2385">
+        <v>60</v>
+      </c>
+      <c r="D167" s="2386" t="s">
+        <v>19</v>
+      </c>
+      <c r="E167" s="2387">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F167" s="2388" t="s">
+        <v>19</v>
+      </c>
+      <c r="G167" s="2389">
+        <v>11339.73</v>
+      </c>
+      <c r="H167" s="2390" t="s">
+        <v>19</v>
+      </c>
+      <c r="I167" s="2391">
+        <v>192.2</v>
+      </c>
+      <c r="J167" s="2392" t="s">
+        <v>19</v>
+      </c>
+      <c r="K167" s="2393">
+        <v>0</v>
+      </c>
+      <c r="L167" s="2394" t="s">
+        <v>19</v>
+      </c>
+      <c r="M167" s="2395">
+        <v>0</v>
+      </c>
+      <c r="N167" s="2396" t="s">
+        <v>19</v>
+      </c>
+      <c r="O167" s="2397">
+        <v>0</v>
+      </c>
+      <c r="P167" s="2398" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q167" s="2399"/>
+      <c r="R167" s="2400"/>
+      <c r="S167" s="2401"/>
+      <c r="T167" s="2402"/>
+      <c r="U167" s="2403">
+        <v>11624.73</v>
+      </c>
+      <c r="V167" s="2404" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B168" s="2269" t="s">
+        <v>199</v>
+      </c>
+      <c r="C168" s="2270"/>
+      <c r="D168" s="2271"/>
+      <c r="E168" s="2272"/>
+      <c r="F168" s="2273"/>
+      <c r="G168" s="2405" t="s">
+        <v>5</v>
+      </c>
+      <c r="H168" s="2406" t="s">
+        <v>200</v>
+      </c>
+      <c r="I168" s="2407"/>
+      <c r="J168" s="2408"/>
+      <c r="K168" s="2409" t="s">
+        <v>200</v>
+      </c>
+      <c r="L168" s="2410" t="s">
+        <v>28</v>
+      </c>
+      <c r="M168" s="2280"/>
+      <c r="N168" s="2281"/>
+      <c r="O168" s="2282"/>
+      <c r="P168" s="2283"/>
+      <c r="Q168" s="2411"/>
+      <c r="R168" s="2412"/>
+      <c r="S168" s="2413"/>
+      <c r="T168" s="2414"/>
+      <c r="U168" s="2288"/>
+      <c r="V168" s="2289"/>
+    </row>
+    <row r="169" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B169" s="2290"/>
+      <c r="C169" s="2291"/>
+      <c r="D169" s="2292"/>
+      <c r="E169" s="2293"/>
+      <c r="F169" s="2294"/>
+      <c r="G169" s="2311"/>
+      <c r="H169" s="2312"/>
+      <c r="I169" s="2297"/>
+      <c r="J169" s="2298"/>
+      <c r="K169" s="2299" t="s">
+        <v>29</v>
+      </c>
+      <c r="L169" s="2300" t="s">
+        <v>200</v>
+      </c>
+      <c r="M169" s="2301"/>
+      <c r="N169" s="2302"/>
+      <c r="O169" s="2303"/>
+      <c r="P169" s="2304"/>
+      <c r="Q169" s="2313" t="s">
+        <v>29</v>
+      </c>
+      <c r="R169" s="2314" t="s">
+        <v>200</v>
+      </c>
+      <c r="S169" s="2315" t="s">
+        <v>29</v>
+      </c>
+      <c r="T169" s="2316" t="s">
+        <v>200</v>
+      </c>
+      <c r="U169" s="2309"/>
+      <c r="V169" s="2310"/>
+    </row>
+    <row r="170" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B170" s="2290"/>
+      <c r="C170" s="2291"/>
+      <c r="D170" s="2292"/>
+      <c r="E170" s="2293"/>
+      <c r="F170" s="2294"/>
+      <c r="G170" s="2295" t="s">
+        <v>138</v>
+      </c>
+      <c r="H170" s="2296" t="s">
+        <v>201</v>
+      </c>
+      <c r="I170" s="2297"/>
+      <c r="J170" s="2298"/>
+      <c r="K170" s="2319"/>
+      <c r="L170" s="2320"/>
+      <c r="M170" s="2301"/>
+      <c r="N170" s="2302"/>
+      <c r="O170" s="2415" t="s">
+        <v>201</v>
+      </c>
+      <c r="P170" s="2416" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q170" s="2305"/>
+      <c r="R170" s="2306"/>
+      <c r="S170" s="2307"/>
+      <c r="T170" s="2308"/>
+      <c r="U170" s="2309"/>
+      <c r="V170" s="2310"/>
+    </row>
+    <row r="171" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B171" s="2290"/>
+      <c r="C171" s="2291"/>
+      <c r="D171" s="2292"/>
+      <c r="E171" s="2293"/>
+      <c r="F171" s="2294"/>
+      <c r="G171" s="2311"/>
+      <c r="H171" s="2312"/>
+      <c r="I171" s="2297"/>
+      <c r="J171" s="2298"/>
+      <c r="K171" s="2319"/>
+      <c r="L171" s="2320"/>
+      <c r="M171" s="2301"/>
+      <c r="N171" s="2302"/>
+      <c r="O171" s="2415" t="s">
+        <v>46</v>
+      </c>
+      <c r="P171" s="2416" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q171" s="2313" t="s">
+        <v>46</v>
+      </c>
+      <c r="R171" s="2314" t="s">
+        <v>201</v>
+      </c>
+      <c r="S171" s="2315" t="s">
+        <v>46</v>
+      </c>
+      <c r="T171" s="2316" t="s">
+        <v>201</v>
+      </c>
+      <c r="U171" s="2309"/>
+      <c r="V171" s="2310"/>
+    </row>
+    <row r="172" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B172" s="2290"/>
+      <c r="C172" s="2291"/>
+      <c r="D172" s="2292"/>
+      <c r="E172" s="2293"/>
+      <c r="F172" s="2294"/>
+      <c r="G172" s="2311"/>
+      <c r="H172" s="2312"/>
+      <c r="I172" s="2317" t="s">
+        <v>50</v>
+      </c>
+      <c r="J172" s="2318" t="s">
+        <v>136</v>
+      </c>
+      <c r="K172" s="2319"/>
+      <c r="L172" s="2320"/>
+      <c r="M172" s="2301"/>
+      <c r="N172" s="2302"/>
+      <c r="O172" s="2303"/>
+      <c r="P172" s="2304"/>
+      <c r="Q172" s="2313" t="s">
+        <v>50</v>
+      </c>
+      <c r="R172" s="2314" t="s">
+        <v>136</v>
+      </c>
+      <c r="S172" s="2315" t="s">
+        <v>50</v>
+      </c>
+      <c r="T172" s="2316" t="s">
+        <v>136</v>
+      </c>
+      <c r="U172" s="2309"/>
+      <c r="V172" s="2310"/>
+    </row>
+    <row r="173" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B173" s="2290"/>
+      <c r="C173" s="2291"/>
+      <c r="D173" s="2292"/>
+      <c r="E173" s="2293"/>
+      <c r="F173" s="2294"/>
+      <c r="G173" s="2295" t="s">
+        <v>138</v>
+      </c>
+      <c r="H173" s="2296" t="s">
+        <v>173</v>
+      </c>
+      <c r="I173" s="2297"/>
+      <c r="J173" s="2298"/>
+      <c r="K173" s="2319"/>
+      <c r="L173" s="2320"/>
+      <c r="M173" s="2301"/>
+      <c r="N173" s="2302"/>
+      <c r="O173" s="2415" t="s">
+        <v>173</v>
+      </c>
+      <c r="P173" s="2416" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q173" s="2305"/>
+      <c r="R173" s="2306"/>
+      <c r="S173" s="2307"/>
+      <c r="T173" s="2308"/>
+      <c r="U173" s="2309"/>
+      <c r="V173" s="2310"/>
+    </row>
+    <row r="174" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B174" s="2290"/>
+      <c r="C174" s="2291"/>
+      <c r="D174" s="2292"/>
+      <c r="E174" s="2293"/>
+      <c r="F174" s="2294"/>
+      <c r="G174" s="2311"/>
+      <c r="H174" s="2312"/>
+      <c r="I174" s="2297"/>
+      <c r="J174" s="2298"/>
+      <c r="K174" s="2319"/>
+      <c r="L174" s="2320"/>
+      <c r="M174" s="2301"/>
+      <c r="N174" s="2302"/>
+      <c r="O174" s="2415" t="s">
+        <v>46</v>
+      </c>
+      <c r="P174" s="2416" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q174" s="2313" t="s">
+        <v>46</v>
+      </c>
+      <c r="R174" s="2314" t="s">
+        <v>173</v>
+      </c>
+      <c r="S174" s="2315" t="s">
+        <v>46</v>
+      </c>
+      <c r="T174" s="2316" t="s">
+        <v>173</v>
+      </c>
+      <c r="U174" s="2309"/>
+      <c r="V174" s="2310"/>
+    </row>
+    <row r="175" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B175" s="2290"/>
+      <c r="C175" s="2291"/>
+      <c r="D175" s="2292"/>
+      <c r="E175" s="2293"/>
+      <c r="F175" s="2294"/>
+      <c r="G175" s="2311"/>
+      <c r="H175" s="2312"/>
+      <c r="I175" s="2317" t="s">
+        <v>50</v>
+      </c>
+      <c r="J175" s="2318" t="s">
+        <v>165</v>
+      </c>
+      <c r="K175" s="2319"/>
+      <c r="L175" s="2320"/>
+      <c r="M175" s="2301"/>
+      <c r="N175" s="2302"/>
+      <c r="O175" s="2303"/>
+      <c r="P175" s="2304"/>
+      <c r="Q175" s="2313" t="s">
+        <v>50</v>
+      </c>
+      <c r="R175" s="2314" t="s">
+        <v>165</v>
+      </c>
+      <c r="S175" s="2315" t="s">
+        <v>50</v>
+      </c>
+      <c r="T175" s="2316" t="s">
+        <v>165</v>
+      </c>
+      <c r="U175" s="2309"/>
+      <c r="V175" s="2310"/>
+    </row>
+    <row r="176" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B176" s="2290"/>
+      <c r="C176" s="2291"/>
+      <c r="D176" s="2292"/>
+      <c r="E176" s="2293"/>
+      <c r="F176" s="2294"/>
+      <c r="G176" s="2295" t="s">
+        <v>5</v>
+      </c>
+      <c r="H176" s="2296" t="s">
+        <v>202</v>
+      </c>
+      <c r="I176" s="2297"/>
+      <c r="J176" s="2298"/>
+      <c r="K176" s="2299" t="s">
+        <v>202</v>
+      </c>
+      <c r="L176" s="2300" t="s">
+        <v>28</v>
+      </c>
+      <c r="M176" s="2301"/>
+      <c r="N176" s="2302"/>
+      <c r="O176" s="2303"/>
+      <c r="P176" s="2304"/>
+      <c r="Q176" s="2305"/>
+      <c r="R176" s="2306"/>
+      <c r="S176" s="2307"/>
+      <c r="T176" s="2308"/>
+      <c r="U176" s="2309"/>
+      <c r="V176" s="2310"/>
+    </row>
+    <row r="177" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B177" s="2321"/>
+      <c r="C177" s="2322"/>
+      <c r="D177" s="2323"/>
+      <c r="E177" s="2324"/>
+      <c r="F177" s="2325"/>
+      <c r="G177" s="2326"/>
+      <c r="H177" s="2327"/>
+      <c r="I177" s="2328"/>
+      <c r="J177" s="2329"/>
+      <c r="K177" s="2417" t="s">
+        <v>33</v>
+      </c>
+      <c r="L177" s="2418" t="s">
+        <v>202</v>
+      </c>
+      <c r="M177" s="2419"/>
+      <c r="N177" s="2420"/>
+      <c r="O177" s="2334"/>
+      <c r="P177" s="2335"/>
+      <c r="Q177" s="2336" t="s">
+        <v>33</v>
+      </c>
+      <c r="R177" s="2337" t="s">
+        <v>202</v>
+      </c>
+      <c r="S177" s="2338" t="s">
+        <v>33</v>
+      </c>
+      <c r="T177" s="2339" t="s">
+        <v>202</v>
+      </c>
+      <c r="U177" s="2340"/>
+      <c r="V177" s="2341"/>
+      <c r="W177" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="178" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B178" s="2342" t="s">
+        <v>18</v>
+      </c>
+      <c r="C178" s="2343">
+        <v>60</v>
+      </c>
+      <c r="D178" s="2344"/>
+      <c r="E178" s="2345">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F178" s="2346"/>
+      <c r="G178" s="2347">
+        <v>11113.6</v>
+      </c>
+      <c r="H178" s="2348"/>
+      <c r="I178" s="2349">
+        <v>166.4</v>
+      </c>
+      <c r="J178" s="2350"/>
+      <c r="K178" s="2351">
+        <v>0</v>
+      </c>
+      <c r="L178" s="2352"/>
+      <c r="M178" s="2353">
+        <v>0</v>
+      </c>
+      <c r="N178" s="2354"/>
+      <c r="O178" s="2355">
+        <v>0</v>
+      </c>
+      <c r="P178" s="2356"/>
+      <c r="Q178" s="2357">
+        <v>0</v>
+      </c>
+      <c r="R178" s="2358">
+        <v>251.93</v>
+      </c>
+      <c r="S178" s="2359">
+        <v>0</v>
+      </c>
+      <c r="T178" s="2360">
+        <v>251.93</v>
+      </c>
+      <c r="U178" s="2361">
+        <v>11372.8</v>
+      </c>
+      <c r="V178" s="2362" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B179" s="2363" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179" s="2364"/>
+      <c r="D179" s="2365"/>
+      <c r="E179" s="2366"/>
+      <c r="F179" s="2367"/>
+      <c r="G179" s="2368"/>
+      <c r="H179" s="2369"/>
+      <c r="I179" s="2370"/>
+      <c r="J179" s="2371"/>
+      <c r="K179" s="2372"/>
+      <c r="L179" s="2373"/>
+      <c r="M179" s="2374"/>
+      <c r="N179" s="2375"/>
+      <c r="O179" s="2376"/>
+      <c r="P179" s="2377"/>
+      <c r="Q179" s="2378">
+        <v>0</v>
+      </c>
+      <c r="R179" s="2379">
+        <v>2948.03</v>
+      </c>
+      <c r="S179" s="2380">
+        <v>3700</v>
+      </c>
+      <c r="T179" s="2381">
+        <v>3448.03</v>
+      </c>
+      <c r="U179" s="2382"/>
+      <c r="V179" s="2383"/>
+    </row>
+    <row r="180" spans="2:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B180" s="2384" t="s">
+        <v>21</v>
+      </c>
+      <c r="C180" s="2385">
+        <v>60</v>
+      </c>
+      <c r="D180" s="2386" t="s">
+        <v>19</v>
+      </c>
+      <c r="E180" s="2387">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F180" s="2388" t="s">
+        <v>19</v>
+      </c>
+      <c r="G180" s="2389">
+        <v>11113.6</v>
+      </c>
+      <c r="H180" s="2390" t="s">
+        <v>19</v>
+      </c>
+      <c r="I180" s="2391">
+        <v>166.4</v>
+      </c>
+      <c r="J180" s="2392" t="s">
+        <v>19</v>
+      </c>
+      <c r="K180" s="2393">
+        <v>0</v>
+      </c>
+      <c r="L180" s="2394" t="s">
+        <v>19</v>
+      </c>
+      <c r="M180" s="2395">
+        <v>0</v>
+      </c>
+      <c r="N180" s="2396" t="s">
+        <v>19</v>
+      </c>
+      <c r="O180" s="2397">
+        <v>0</v>
+      </c>
+      <c r="P180" s="2398" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q180" s="2399"/>
+      <c r="R180" s="2400"/>
+      <c r="S180" s="2401"/>
+      <c r="T180" s="2402"/>
+      <c r="U180" s="2403">
+        <v>11372.8</v>
+      </c>
+      <c r="V180" s="2404" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B181" s="2421" t="s">
+        <v>203</v>
+      </c>
+      <c r="C181" s="2422"/>
+      <c r="D181" s="2423"/>
+      <c r="E181" s="2424"/>
+      <c r="F181" s="2425"/>
+      <c r="G181" s="2426"/>
+      <c r="H181" s="2427"/>
+      <c r="I181" s="2428" t="s">
+        <v>23</v>
+      </c>
+      <c r="J181" s="2429" t="s">
+        <v>48</v>
+      </c>
+      <c r="K181" s="2430"/>
+      <c r="L181" s="2431"/>
+      <c r="M181" s="2432"/>
+      <c r="N181" s="2433"/>
+      <c r="O181" s="2434"/>
+      <c r="P181" s="2435"/>
+      <c r="Q181" s="2436" t="s">
+        <v>23</v>
+      </c>
+      <c r="R181" s="2437" t="s">
+        <v>48</v>
+      </c>
+      <c r="S181" s="2438" t="s">
+        <v>23</v>
+      </c>
+      <c r="T181" s="2439" t="s">
+        <v>48</v>
+      </c>
+      <c r="U181" s="2440"/>
+      <c r="V181" s="2441"/>
+    </row>
+    <row r="182" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B182" s="2442"/>
+      <c r="C182" s="2443"/>
+      <c r="D182" s="2444"/>
+      <c r="E182" s="2445"/>
+      <c r="F182" s="2446"/>
+      <c r="G182" s="2447" t="s">
+        <v>5</v>
+      </c>
+      <c r="H182" s="2448" t="s">
+        <v>204</v>
+      </c>
+      <c r="I182" s="2449"/>
+      <c r="J182" s="2450"/>
+      <c r="K182" s="2451" t="s">
+        <v>204</v>
+      </c>
+      <c r="L182" s="2452" t="s">
+        <v>28</v>
+      </c>
+      <c r="M182" s="2453"/>
+      <c r="N182" s="2454"/>
+      <c r="O182" s="2455"/>
+      <c r="P182" s="2456"/>
+      <c r="Q182" s="2457"/>
+      <c r="R182" s="2458"/>
+      <c r="S182" s="2459"/>
+      <c r="T182" s="2460"/>
+      <c r="U182" s="2461"/>
+      <c r="V182" s="2462"/>
+    </row>
+    <row r="183" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B183" s="2442"/>
+      <c r="C183" s="2443"/>
+      <c r="D183" s="2444"/>
+      <c r="E183" s="2445"/>
+      <c r="F183" s="2446"/>
+      <c r="G183" s="2463"/>
+      <c r="H183" s="2464"/>
+      <c r="I183" s="2449"/>
+      <c r="J183" s="2450"/>
+      <c r="K183" s="2451" t="s">
+        <v>46</v>
+      </c>
+      <c r="L183" s="2452" t="s">
+        <v>204</v>
+      </c>
+      <c r="M183" s="2453"/>
+      <c r="N183" s="2454"/>
+      <c r="O183" s="2455"/>
+      <c r="P183" s="2456"/>
+      <c r="Q183" s="2465" t="s">
+        <v>46</v>
+      </c>
+      <c r="R183" s="2466" t="s">
+        <v>204</v>
+      </c>
+      <c r="S183" s="2467" t="s">
+        <v>46</v>
+      </c>
+      <c r="T183" s="2468" t="s">
+        <v>204</v>
+      </c>
+      <c r="U183" s="2461"/>
+      <c r="V183" s="2462"/>
+      <c r="W183" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="184" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B184" s="2442"/>
+      <c r="C184" s="2443"/>
+      <c r="D184" s="2444"/>
+      <c r="E184" s="2445"/>
+      <c r="F184" s="2446"/>
+      <c r="G184" s="2447" t="s">
+        <v>5</v>
+      </c>
+      <c r="H184" s="2448" t="s">
+        <v>205</v>
+      </c>
+      <c r="I184" s="2449"/>
+      <c r="J184" s="2450"/>
+      <c r="K184" s="2451" t="s">
+        <v>205</v>
+      </c>
+      <c r="L184" s="2452" t="s">
+        <v>28</v>
+      </c>
+      <c r="M184" s="2453"/>
+      <c r="N184" s="2454"/>
+      <c r="O184" s="2455"/>
+      <c r="P184" s="2456"/>
+      <c r="Q184" s="2457"/>
+      <c r="R184" s="2458"/>
+      <c r="S184" s="2459"/>
+      <c r="T184" s="2460"/>
+      <c r="U184" s="2461"/>
+      <c r="V184" s="2462"/>
+    </row>
+    <row r="185" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B185" s="2442"/>
+      <c r="C185" s="2443"/>
+      <c r="D185" s="2444"/>
+      <c r="E185" s="2445"/>
+      <c r="F185" s="2446"/>
+      <c r="G185" s="2463"/>
+      <c r="H185" s="2464"/>
+      <c r="I185" s="2449"/>
+      <c r="J185" s="2450"/>
+      <c r="K185" s="2451" t="s">
+        <v>206</v>
+      </c>
+      <c r="L185" s="2452" t="s">
+        <v>205</v>
+      </c>
+      <c r="M185" s="2453"/>
+      <c r="N185" s="2454"/>
+      <c r="O185" s="2455"/>
+      <c r="P185" s="2456"/>
+      <c r="Q185" s="2465" t="s">
+        <v>206</v>
+      </c>
+      <c r="R185" s="2466" t="s">
+        <v>205</v>
+      </c>
+      <c r="S185" s="2467" t="s">
+        <v>206</v>
+      </c>
+      <c r="T185" s="2468" t="s">
+        <v>205</v>
+      </c>
+      <c r="U185" s="2461"/>
+      <c r="V185" s="2462"/>
+      <c r="W185" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="186" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B186" s="2442"/>
+      <c r="C186" s="2443"/>
+      <c r="D186" s="2444"/>
+      <c r="E186" s="2445"/>
+      <c r="F186" s="2446"/>
+      <c r="G186" s="2447" t="s">
+        <v>5</v>
+      </c>
+      <c r="H186" s="2448" t="s">
+        <v>207</v>
+      </c>
+      <c r="I186" s="2449"/>
+      <c r="J186" s="2450"/>
+      <c r="K186" s="2451" t="s">
+        <v>207</v>
+      </c>
+      <c r="L186" s="2452" t="s">
+        <v>28</v>
+      </c>
+      <c r="M186" s="2453"/>
+      <c r="N186" s="2454"/>
+      <c r="O186" s="2455"/>
+      <c r="P186" s="2456"/>
+      <c r="Q186" s="2457"/>
+      <c r="R186" s="2458"/>
+      <c r="S186" s="2459"/>
+      <c r="T186" s="2460"/>
+      <c r="U186" s="2461"/>
+      <c r="V186" s="2462"/>
+    </row>
+    <row r="187" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B187" s="2442"/>
+      <c r="C187" s="2443"/>
+      <c r="D187" s="2444"/>
+      <c r="E187" s="2445"/>
+      <c r="F187" s="2446"/>
+      <c r="G187" s="2463"/>
+      <c r="H187" s="2464"/>
+      <c r="I187" s="2449"/>
+      <c r="J187" s="2450"/>
+      <c r="K187" s="2451" t="s">
+        <v>35</v>
+      </c>
+      <c r="L187" s="2452" t="s">
+        <v>207</v>
+      </c>
+      <c r="M187" s="2453"/>
+      <c r="N187" s="2454"/>
+      <c r="O187" s="2455"/>
+      <c r="P187" s="2456"/>
+      <c r="Q187" s="2465" t="s">
+        <v>35</v>
+      </c>
+      <c r="R187" s="2466" t="s">
+        <v>207</v>
+      </c>
+      <c r="S187" s="2467" t="s">
+        <v>35</v>
+      </c>
+      <c r="T187" s="2468" t="s">
+        <v>207</v>
+      </c>
+      <c r="U187" s="2461"/>
+      <c r="V187" s="2462"/>
+      <c r="W187" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="188" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B188" s="2442"/>
+      <c r="C188" s="2443"/>
+      <c r="D188" s="2444"/>
+      <c r="E188" s="2445"/>
+      <c r="F188" s="2446"/>
+      <c r="G188" s="2463"/>
+      <c r="H188" s="2464"/>
+      <c r="I188" s="2469" t="s">
+        <v>208</v>
+      </c>
+      <c r="J188" s="2470" t="s">
+        <v>150</v>
+      </c>
+      <c r="K188" s="2471"/>
+      <c r="L188" s="2472"/>
+      <c r="M188" s="2453"/>
+      <c r="N188" s="2454"/>
+      <c r="O188" s="2455"/>
+      <c r="P188" s="2456"/>
+      <c r="Q188" s="2465" t="s">
+        <v>208</v>
+      </c>
+      <c r="R188" s="2466" t="s">
+        <v>150</v>
+      </c>
+      <c r="S188" s="2467" t="s">
+        <v>208</v>
+      </c>
+      <c r="T188" s="2468" t="s">
+        <v>150</v>
+      </c>
+      <c r="U188" s="2461"/>
+      <c r="V188" s="2462"/>
+      <c r="W188" s="1098" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="189" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B189" s="2442"/>
+      <c r="C189" s="2443"/>
+      <c r="D189" s="2444"/>
+      <c r="E189" s="2445"/>
+      <c r="F189" s="2446"/>
+      <c r="G189" s="2447" t="s">
+        <v>5</v>
+      </c>
+      <c r="H189" s="2448" t="s">
+        <v>209</v>
+      </c>
+      <c r="I189" s="2449"/>
+      <c r="J189" s="2450"/>
+      <c r="K189" s="2451" t="s">
+        <v>209</v>
+      </c>
+      <c r="L189" s="2452" t="s">
+        <v>28</v>
+      </c>
+      <c r="M189" s="2453"/>
+      <c r="N189" s="2454"/>
+      <c r="O189" s="2455"/>
+      <c r="P189" s="2456"/>
+      <c r="Q189" s="2457"/>
+      <c r="R189" s="2458"/>
+      <c r="S189" s="2459"/>
+      <c r="T189" s="2460"/>
+      <c r="U189" s="2461"/>
+      <c r="V189" s="2462"/>
+    </row>
+    <row r="190" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B190" s="2442"/>
+      <c r="C190" s="2443"/>
+      <c r="D190" s="2444"/>
+      <c r="E190" s="2445"/>
+      <c r="F190" s="2446"/>
+      <c r="G190" s="2463"/>
+      <c r="H190" s="2464"/>
+      <c r="I190" s="2449"/>
+      <c r="J190" s="2450"/>
+      <c r="K190" s="2451" t="s">
+        <v>210</v>
+      </c>
+      <c r="L190" s="2452" t="s">
+        <v>209</v>
+      </c>
+      <c r="M190" s="2453"/>
+      <c r="N190" s="2454"/>
+      <c r="O190" s="2455"/>
+      <c r="P190" s="2456"/>
+      <c r="Q190" s="2465" t="s">
+        <v>210</v>
+      </c>
+      <c r="R190" s="2466" t="s">
+        <v>209</v>
+      </c>
+      <c r="S190" s="2467" t="s">
+        <v>210</v>
+      </c>
+      <c r="T190" s="2468" t="s">
+        <v>209</v>
+      </c>
+      <c r="U190" s="2461"/>
+      <c r="V190" s="2462"/>
+    </row>
+    <row r="191" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B191" s="2473"/>
+      <c r="C191" s="2474"/>
+      <c r="D191" s="2475"/>
+      <c r="E191" s="2476"/>
+      <c r="F191" s="2477"/>
+      <c r="G191" s="2478"/>
+      <c r="H191" s="2479"/>
+      <c r="I191" s="2480" t="s">
+        <v>23</v>
+      </c>
+      <c r="J191" s="2481" t="s">
+        <v>48</v>
+      </c>
+      <c r="K191" s="2482"/>
+      <c r="L191" s="2483"/>
+      <c r="M191" s="2484"/>
+      <c r="N191" s="2485"/>
+      <c r="O191" s="2486"/>
+      <c r="P191" s="2487"/>
+      <c r="Q191" s="2488" t="s">
+        <v>23</v>
+      </c>
+      <c r="R191" s="2489" t="s">
+        <v>48</v>
+      </c>
+      <c r="S191" s="2490" t="s">
+        <v>23</v>
+      </c>
+      <c r="T191" s="2491" t="s">
+        <v>48</v>
+      </c>
+      <c r="U191" s="2492"/>
+      <c r="V191" s="2493"/>
+    </row>
+    <row r="192" spans="2:23" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B192" s="2494" t="s">
+        <v>18</v>
+      </c>
+      <c r="C192" s="2495">
+        <v>60</v>
+      </c>
+      <c r="D192" s="2496"/>
+      <c r="E192" s="2497">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F192" s="2498"/>
+      <c r="G192" s="2499">
+        <v>10898.7</v>
+      </c>
+      <c r="H192" s="2500"/>
+      <c r="I192" s="2501">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="J192" s="2502"/>
+      <c r="K192" s="2503">
+        <v>0</v>
+      </c>
+      <c r="L192" s="2504"/>
+      <c r="M192" s="2505">
+        <v>0</v>
+      </c>
+      <c r="N192" s="2506"/>
+      <c r="O192" s="2507">
+        <v>0</v>
+      </c>
+      <c r="P192" s="2508"/>
+      <c r="Q192" s="2509">
+        <v>0</v>
+      </c>
+      <c r="R192" s="2510">
+        <v>240.1</v>
+      </c>
+      <c r="S192" s="2511">
+        <v>0</v>
+      </c>
+      <c r="T192" s="2512">
+        <v>240.1</v>
+      </c>
+      <c r="U192" s="2513">
+        <v>11132.7</v>
+      </c>
+      <c r="V192" s="2514" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="193" spans="2:22" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B193" s="2515" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" s="2516"/>
+      <c r="D193" s="2517"/>
+      <c r="E193" s="2518"/>
+      <c r="F193" s="2519"/>
+      <c r="G193" s="2520"/>
+      <c r="H193" s="2521"/>
+      <c r="I193" s="2522"/>
+      <c r="J193" s="2523"/>
+      <c r="K193" s="2524"/>
+      <c r="L193" s="2525"/>
+      <c r="M193" s="2526"/>
+      <c r="N193" s="2527"/>
+      <c r="O193" s="2528"/>
+      <c r="P193" s="2529"/>
+      <c r="Q193" s="2530">
+        <v>0</v>
+      </c>
+      <c r="R193" s="2531">
+        <v>3188.13</v>
+      </c>
+      <c r="S193" s="2532">
+        <v>3700</v>
+      </c>
+      <c r="T193" s="2533">
+        <v>3688.13</v>
+      </c>
+      <c r="U193" s="2534"/>
+      <c r="V193" s="2535"/>
+    </row>
+    <row r="194" spans="2:22" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="B194" s="2536" t="s">
+        <v>21</v>
+      </c>
+      <c r="C194" s="2537">
+        <v>60</v>
+      </c>
+      <c r="D194" s="2538" t="s">
+        <v>19</v>
+      </c>
+      <c r="E194" s="2539">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="F194" s="2540" t="s">
+        <v>19</v>
+      </c>
+      <c r="G194" s="2541">
+        <v>10898.7</v>
+      </c>
+      <c r="H194" s="2542" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" s="2543">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="J194" s="2544" t="s">
+        <v>19</v>
+      </c>
+      <c r="K194" s="2545">
+        <v>0</v>
+      </c>
+      <c r="L194" s="2546" t="s">
+        <v>19</v>
+      </c>
+      <c r="M194" s="2547">
+        <v>0</v>
+      </c>
+      <c r="N194" s="2548" t="s">
+        <v>19</v>
+      </c>
+      <c r="O194" s="2549">
+        <v>0</v>
+      </c>
+      <c r="P194" s="2550" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q194" s="2551"/>
+      <c r="R194" s="2552"/>
+      <c r="S194" s="2553"/>
+      <c r="T194" s="2554"/>
+      <c r="U194" s="2555">
+        <v>11132.7</v>
+      </c>
+      <c r="V194" s="2556" t="s">
         <v>19</v>
       </c>
     </row>
